--- a/client/public/samples/sales-orders.xlsx
+++ b/client/public/samples/sales-orders.xlsx
@@ -438,7 +438,7 @@
         <v>SO-10001</v>
       </c>
       <c r="B2" s="1" t="d">
-        <v>2025-04-01T05:30:00.000Z</v>
+        <v>2025-04-01T00:00:00.000Z</v>
       </c>
       <c r="C2" t="str">
         <v>Joshi Enterprises</v>
@@ -470,7 +470,7 @@
         <v>SO-10002</v>
       </c>
       <c r="B3" s="1" t="d">
-        <v>2025-04-03T05:30:00.000Z</v>
+        <v>2025-04-03T00:00:00.000Z</v>
       </c>
       <c r="C3" t="str">
         <v>Sharma Solutions</v>
@@ -502,7 +502,7 @@
         <v>SO-10003</v>
       </c>
       <c r="B4" s="1" t="d">
-        <v>2025-04-03T05:30:00.000Z</v>
+        <v>2025-04-03T00:00:00.000Z</v>
       </c>
       <c r="C4" t="str">
         <v>Desai Enterprises</v>
@@ -534,7 +534,7 @@
         <v>SO-10004</v>
       </c>
       <c r="B5" s="1" t="d">
-        <v>2025-04-04T05:30:00.000Z</v>
+        <v>2025-04-04T00:00:00.000Z</v>
       </c>
       <c r="C5" t="str">
         <v>Desai Stores</v>
@@ -566,7 +566,7 @@
         <v>SO-10005</v>
       </c>
       <c r="B6" s="1" t="d">
-        <v>2025-04-04T05:30:00.000Z</v>
+        <v>2025-04-04T00:00:00.000Z</v>
       </c>
       <c r="C6" t="str">
         <v>Sharma Retail</v>
@@ -598,7 +598,7 @@
         <v>SO-10006</v>
       </c>
       <c r="B7" s="1" t="d">
-        <v>2025-04-04T05:30:00.000Z</v>
+        <v>2025-04-04T00:00:00.000Z</v>
       </c>
       <c r="C7" t="str">
         <v>Gupta Stores</v>
@@ -630,7 +630,7 @@
         <v>SO-10007</v>
       </c>
       <c r="B8" s="1" t="d">
-        <v>2025-04-06T05:30:00.000Z</v>
+        <v>2025-04-06T00:00:00.000Z</v>
       </c>
       <c r="C8" t="str">
         <v>Gupta Stores</v>
@@ -662,7 +662,7 @@
         <v>SO-10008</v>
       </c>
       <c r="B9" s="1" t="d">
-        <v>2025-04-05T05:30:00.000Z</v>
+        <v>2025-04-05T00:00:00.000Z</v>
       </c>
       <c r="C9" t="str">
         <v>Sharma Traders</v>
@@ -694,7 +694,7 @@
         <v>SO-10009</v>
       </c>
       <c r="B10" s="1" t="d">
-        <v>2025-04-07T05:30:00.000Z</v>
+        <v>2025-04-07T00:00:00.000Z</v>
       </c>
       <c r="C10" t="str">
         <v>Kulkarni Traders</v>
@@ -726,7 +726,7 @@
         <v>SO-10010</v>
       </c>
       <c r="B11" s="1" t="d">
-        <v>2025-04-07T05:30:00.000Z</v>
+        <v>2025-04-07T00:00:00.000Z</v>
       </c>
       <c r="C11" t="str">
         <v>Patil Enterprises</v>
@@ -758,7 +758,7 @@
         <v>SO-10011</v>
       </c>
       <c r="B12" s="1" t="d">
-        <v>2025-04-09T05:30:00.000Z</v>
+        <v>2025-04-09T00:00:00.000Z</v>
       </c>
       <c r="C12" t="str">
         <v>Pillai Stores</v>
@@ -790,7 +790,7 @@
         <v>SO-10012</v>
       </c>
       <c r="B13" s="1" t="d">
-        <v>2025-04-09T05:30:00.000Z</v>
+        <v>2025-04-09T00:00:00.000Z</v>
       </c>
       <c r="C13" t="str">
         <v>Mehta Enterprises</v>
@@ -822,7 +822,7 @@
         <v>SO-10013</v>
       </c>
       <c r="B14" s="1" t="d">
-        <v>2025-04-09T05:30:00.000Z</v>
+        <v>2025-04-09T00:00:00.000Z</v>
       </c>
       <c r="C14" t="str">
         <v>Joshi Retail</v>
@@ -854,7 +854,7 @@
         <v>SO-10014</v>
       </c>
       <c r="B15" s="1" t="d">
-        <v>2025-04-10T05:30:00.000Z</v>
+        <v>2025-04-10T00:00:00.000Z</v>
       </c>
       <c r="C15" t="str">
         <v>Pillai Stores</v>
@@ -886,7 +886,7 @@
         <v>SO-10015</v>
       </c>
       <c r="B16" s="1" t="d">
-        <v>2025-04-10T05:30:00.000Z</v>
+        <v>2025-04-10T00:00:00.000Z</v>
       </c>
       <c r="C16" t="str">
         <v>Mehta Stores</v>
@@ -918,7 +918,7 @@
         <v>SO-10016</v>
       </c>
       <c r="B17" s="1" t="d">
-        <v>2025-04-10T05:30:00.000Z</v>
+        <v>2025-04-10T00:00:00.000Z</v>
       </c>
       <c r="C17" t="str">
         <v>Iyer Stores</v>
@@ -950,7 +950,7 @@
         <v>SO-10017</v>
       </c>
       <c r="B18" s="1" t="d">
-        <v>2025-04-11T05:30:00.000Z</v>
+        <v>2025-04-11T00:00:00.000Z</v>
       </c>
       <c r="C18" t="str">
         <v>Kulkarni Traders</v>
@@ -982,7 +982,7 @@
         <v>SO-10018</v>
       </c>
       <c r="B19" s="1" t="d">
-        <v>2025-04-13T05:30:00.000Z</v>
+        <v>2025-04-13T00:00:00.000Z</v>
       </c>
       <c r="C19" t="str">
         <v>Nair Traders</v>
@@ -1014,7 +1014,7 @@
         <v>SO-10019</v>
       </c>
       <c r="B20" s="1" t="d">
-        <v>2025-04-12T05:30:00.000Z</v>
+        <v>2025-04-12T00:00:00.000Z</v>
       </c>
       <c r="C20" t="str">
         <v>Nair Solutions</v>
@@ -1046,7 +1046,7 @@
         <v>SO-10020</v>
       </c>
       <c r="B21" s="1" t="d">
-        <v>2025-04-12T05:30:00.000Z</v>
+        <v>2025-04-12T00:00:00.000Z</v>
       </c>
       <c r="C21" t="str">
         <v>Iyer Retail</v>
@@ -1078,7 +1078,7 @@
         <v>SO-10021</v>
       </c>
       <c r="B22" s="1" t="d">
-        <v>2025-04-14T05:30:00.000Z</v>
+        <v>2025-04-14T00:00:00.000Z</v>
       </c>
       <c r="C22" t="str">
         <v>Kulkarni Labs</v>
@@ -1110,7 +1110,7 @@
         <v>SO-10022</v>
       </c>
       <c r="B23" s="1" t="d">
-        <v>2025-04-15T05:30:00.000Z</v>
+        <v>2025-04-15T00:00:00.000Z</v>
       </c>
       <c r="C23" t="str">
         <v>Rao Solutions</v>
@@ -1142,7 +1142,7 @@
         <v>SO-10023</v>
       </c>
       <c r="B24" s="1" t="d">
-        <v>2025-04-13T05:30:00.000Z</v>
+        <v>2025-04-13T00:00:00.000Z</v>
       </c>
       <c r="C24" t="str">
         <v>Desai Stores</v>
@@ -1174,7 +1174,7 @@
         <v>SO-10024</v>
       </c>
       <c r="B25" s="1" t="d">
-        <v>2025-04-16T05:30:00.000Z</v>
+        <v>2025-04-16T00:00:00.000Z</v>
       </c>
       <c r="C25" t="str">
         <v>Patil Labs</v>
@@ -1206,7 +1206,7 @@
         <v>SO-10025</v>
       </c>
       <c r="B26" s="1" t="d">
-        <v>2025-04-17T05:30:00.000Z</v>
+        <v>2025-04-17T00:00:00.000Z</v>
       </c>
       <c r="C26" t="str">
         <v>Joshi Stores</v>
@@ -1238,7 +1238,7 @@
         <v>SO-10026</v>
       </c>
       <c r="B27" s="1" t="d">
-        <v>2025-04-17T05:30:00.000Z</v>
+        <v>2025-04-17T00:00:00.000Z</v>
       </c>
       <c r="C27" t="str">
         <v>Iyer Enterprises</v>
@@ -1270,7 +1270,7 @@
         <v>SO-10027</v>
       </c>
       <c r="B28" s="1" t="d">
-        <v>2025-04-18T05:30:00.000Z</v>
+        <v>2025-04-18T00:00:00.000Z</v>
       </c>
       <c r="C28" t="str">
         <v>Desai Stores</v>
@@ -1302,7 +1302,7 @@
         <v>SO-10028</v>
       </c>
       <c r="B29" s="1" t="d">
-        <v>2025-04-18T05:30:00.000Z</v>
+        <v>2025-04-18T00:00:00.000Z</v>
       </c>
       <c r="C29" t="str">
         <v>Joshi Solutions</v>
@@ -1334,7 +1334,7 @@
         <v>SO-10029</v>
       </c>
       <c r="B30" s="1" t="d">
-        <v>2025-04-19T05:30:00.000Z</v>
+        <v>2025-04-19T00:00:00.000Z</v>
       </c>
       <c r="C30" t="str">
         <v>Pillai Traders</v>
@@ -1366,7 +1366,7 @@
         <v>SO-10030</v>
       </c>
       <c r="B31" s="1" t="d">
-        <v>2025-04-18T05:30:00.000Z</v>
+        <v>2025-04-18T00:00:00.000Z</v>
       </c>
       <c r="C31" t="str">
         <v>Patil Labs</v>
@@ -1398,7 +1398,7 @@
         <v>SO-10031</v>
       </c>
       <c r="B32" s="1" t="d">
-        <v>2025-04-20T05:30:00.000Z</v>
+        <v>2025-04-20T00:00:00.000Z</v>
       </c>
       <c r="C32" t="str">
         <v>Sharma Retail</v>
@@ -1430,7 +1430,7 @@
         <v>SO-10032</v>
       </c>
       <c r="B33" s="1" t="d">
-        <v>2025-04-21T05:30:00.000Z</v>
+        <v>2025-04-21T00:00:00.000Z</v>
       </c>
       <c r="C33" t="str">
         <v>Desai Labs</v>
@@ -1462,7 +1462,7 @@
         <v>SO-10033</v>
       </c>
       <c r="B34" s="1" t="d">
-        <v>2025-04-20T05:30:00.000Z</v>
+        <v>2025-04-20T00:00:00.000Z</v>
       </c>
       <c r="C34" t="str">
         <v>Iyer Retail</v>
@@ -1494,7 +1494,7 @@
         <v>SO-10034</v>
       </c>
       <c r="B35" s="1" t="d">
-        <v>2025-04-22T05:30:00.000Z</v>
+        <v>2025-04-22T00:00:00.000Z</v>
       </c>
       <c r="C35" t="str">
         <v>Nair Traders</v>
@@ -1526,7 +1526,7 @@
         <v>SO-10035</v>
       </c>
       <c r="B36" s="1" t="d">
-        <v>2025-04-22T05:30:00.000Z</v>
+        <v>2025-04-22T00:00:00.000Z</v>
       </c>
       <c r="C36" t="str">
         <v>Desai Solutions</v>
@@ -1558,7 +1558,7 @@
         <v>SO-10036</v>
       </c>
       <c r="B37" s="1" t="d">
-        <v>2025-04-21T05:30:00.000Z</v>
+        <v>2025-04-21T00:00:00.000Z</v>
       </c>
       <c r="C37" t="str">
         <v>Rao Labs</v>
@@ -1590,7 +1590,7 @@
         <v>SO-10037</v>
       </c>
       <c r="B38" s="1" t="d">
-        <v>2025-04-22T05:30:00.000Z</v>
+        <v>2025-04-22T00:00:00.000Z</v>
       </c>
       <c r="C38" t="str">
         <v>Iyer Labs</v>
@@ -1622,7 +1622,7 @@
         <v>SO-10038</v>
       </c>
       <c r="B39" s="1" t="d">
-        <v>2025-04-22T05:30:00.000Z</v>
+        <v>2025-04-22T00:00:00.000Z</v>
       </c>
       <c r="C39" t="str">
         <v>Sharma Retail</v>
@@ -1654,7 +1654,7 @@
         <v>SO-10039</v>
       </c>
       <c r="B40" s="1" t="d">
-        <v>2025-04-25T05:30:00.000Z</v>
+        <v>2025-04-25T00:00:00.000Z</v>
       </c>
       <c r="C40" t="str">
         <v>Rao Labs</v>
@@ -1686,7 +1686,7 @@
         <v>SO-10040</v>
       </c>
       <c r="B41" s="1" t="d">
-        <v>2025-04-26T05:30:00.000Z</v>
+        <v>2025-04-26T00:00:00.000Z</v>
       </c>
       <c r="C41" t="str">
         <v>Joshi Enterprises</v>
@@ -1718,7 +1718,7 @@
         <v>SO-10041</v>
       </c>
       <c r="B42" s="1" t="d">
-        <v>2025-04-26T05:30:00.000Z</v>
+        <v>2025-04-26T00:00:00.000Z</v>
       </c>
       <c r="C42" t="str">
         <v>Gupta Enterprises</v>
@@ -1750,7 +1750,7 @@
         <v>SO-10042</v>
       </c>
       <c r="B43" s="1" t="d">
-        <v>2025-04-24T05:30:00.000Z</v>
+        <v>2025-04-24T00:00:00.000Z</v>
       </c>
       <c r="C43" t="str">
         <v>Patil Labs</v>
@@ -1782,7 +1782,7 @@
         <v>SO-10043</v>
       </c>
       <c r="B44" s="1" t="d">
-        <v>2025-04-26T05:30:00.000Z</v>
+        <v>2025-04-26T00:00:00.000Z</v>
       </c>
       <c r="C44" t="str">
         <v>Desai Enterprises</v>
@@ -1814,7 +1814,7 @@
         <v>SO-10044</v>
       </c>
       <c r="B45" s="1" t="d">
-        <v>2025-04-26T05:30:00.000Z</v>
+        <v>2025-04-26T00:00:00.000Z</v>
       </c>
       <c r="C45" t="str">
         <v>Pillai Stores</v>
@@ -1846,7 +1846,7 @@
         <v>SO-10045</v>
       </c>
       <c r="B46" s="1" t="d">
-        <v>2025-04-26T05:30:00.000Z</v>
+        <v>2025-04-26T00:00:00.000Z</v>
       </c>
       <c r="C46" t="str">
         <v>Joshi Retail</v>
@@ -1878,7 +1878,7 @@
         <v>SO-10046</v>
       </c>
       <c r="B47" s="1" t="d">
-        <v>2025-04-27T05:30:00.000Z</v>
+        <v>2025-04-27T00:00:00.000Z</v>
       </c>
       <c r="C47" t="str">
         <v>Kulkarni Labs</v>
@@ -1910,7 +1910,7 @@
         <v>SO-10047</v>
       </c>
       <c r="B48" s="1" t="d">
-        <v>2025-04-28T05:30:00.000Z</v>
+        <v>2025-04-28T00:00:00.000Z</v>
       </c>
       <c r="C48" t="str">
         <v>Patil Stores</v>
@@ -1942,7 +1942,7 @@
         <v>SO-10048</v>
       </c>
       <c r="B49" s="1" t="d">
-        <v>2025-04-28T05:30:00.000Z</v>
+        <v>2025-04-28T00:00:00.000Z</v>
       </c>
       <c r="C49" t="str">
         <v>Sharma Solutions</v>
@@ -1974,7 +1974,7 @@
         <v>SO-10049</v>
       </c>
       <c r="B50" s="1" t="d">
-        <v>2025-04-29T05:30:00.000Z</v>
+        <v>2025-04-29T00:00:00.000Z</v>
       </c>
       <c r="C50" t="str">
         <v>Sharma Enterprises</v>
@@ -2006,7 +2006,7 @@
         <v>SO-10050</v>
       </c>
       <c r="B51" s="1" t="d">
-        <v>2025-05-01T05:30:00.000Z</v>
+        <v>2025-05-01T00:00:00.000Z</v>
       </c>
       <c r="C51" t="str">
         <v>Rao Enterprises</v>
@@ -2038,7 +2038,7 @@
         <v>SO-10051</v>
       </c>
       <c r="B52" s="1" t="d">
-        <v>2025-04-29T05:30:00.000Z</v>
+        <v>2025-04-29T00:00:00.000Z</v>
       </c>
       <c r="C52" t="str">
         <v>Pillai Traders</v>
@@ -2070,7 +2070,7 @@
         <v>SO-10052</v>
       </c>
       <c r="B53" s="1" t="d">
-        <v>2025-05-02T05:30:00.000Z</v>
+        <v>2025-05-02T00:00:00.000Z</v>
       </c>
       <c r="C53" t="str">
         <v>Mehta Stores</v>
@@ -2102,7 +2102,7 @@
         <v>SO-10053</v>
       </c>
       <c r="B54" s="1" t="d">
-        <v>2025-04-30T05:30:00.000Z</v>
+        <v>2025-04-30T00:00:00.000Z</v>
       </c>
       <c r="C54" t="str">
         <v>Patil Retail</v>
@@ -2134,7 +2134,7 @@
         <v>SO-10054</v>
       </c>
       <c r="B55" s="1" t="d">
-        <v>2025-05-02T05:30:00.000Z</v>
+        <v>2025-05-02T00:00:00.000Z</v>
       </c>
       <c r="C55" t="str">
         <v>Kulkarni Stores</v>
@@ -2166,7 +2166,7 @@
         <v>SO-10055</v>
       </c>
       <c r="B56" s="1" t="d">
-        <v>2025-05-03T05:30:00.000Z</v>
+        <v>2025-05-03T00:00:00.000Z</v>
       </c>
       <c r="C56" t="str">
         <v>Iyer Enterprises</v>
@@ -2198,7 +2198,7 @@
         <v>SO-10056</v>
       </c>
       <c r="B57" s="1" t="d">
-        <v>2025-05-04T05:30:00.000Z</v>
+        <v>2025-05-04T00:00:00.000Z</v>
       </c>
       <c r="C57" t="str">
         <v>Rao Solutions</v>
@@ -2230,7 +2230,7 @@
         <v>SO-10057</v>
       </c>
       <c r="B58" s="1" t="d">
-        <v>2025-05-03T05:30:00.000Z</v>
+        <v>2025-05-03T00:00:00.000Z</v>
       </c>
       <c r="C58" t="str">
         <v>Desai Stores</v>
@@ -2262,7 +2262,7 @@
         <v>SO-10058</v>
       </c>
       <c r="B59" s="1" t="d">
-        <v>2025-05-03T05:30:00.000Z</v>
+        <v>2025-05-03T00:00:00.000Z</v>
       </c>
       <c r="C59" t="str">
         <v>Rao Retail</v>
@@ -2294,7 +2294,7 @@
         <v>SO-10059</v>
       </c>
       <c r="B60" s="1" t="d">
-        <v>2025-05-05T05:30:00.000Z</v>
+        <v>2025-05-05T00:00:00.000Z</v>
       </c>
       <c r="C60" t="str">
         <v>Sharma Enterprises</v>
@@ -2326,7 +2326,7 @@
         <v>SO-10060</v>
       </c>
       <c r="B61" s="1" t="d">
-        <v>2025-05-06T05:30:00.000Z</v>
+        <v>2025-05-06T00:00:00.000Z</v>
       </c>
       <c r="C61" t="str">
         <v>Joshi Labs</v>
@@ -2358,7 +2358,7 @@
         <v>SO-10061</v>
       </c>
       <c r="B62" s="1" t="d">
-        <v>2025-05-05T05:30:00.000Z</v>
+        <v>2025-05-05T00:00:00.000Z</v>
       </c>
       <c r="C62" t="str">
         <v>Patil Traders</v>
@@ -2390,7 +2390,7 @@
         <v>SO-10062</v>
       </c>
       <c r="B63" s="1" t="d">
-        <v>2025-05-08T05:30:00.000Z</v>
+        <v>2025-05-08T00:00:00.000Z</v>
       </c>
       <c r="C63" t="str">
         <v>Rao Retail</v>
@@ -2422,7 +2422,7 @@
         <v>SO-10063</v>
       </c>
       <c r="B64" s="1" t="d">
-        <v>2025-05-06T05:30:00.000Z</v>
+        <v>2025-05-06T00:00:00.000Z</v>
       </c>
       <c r="C64" t="str">
         <v>Sharma Retail</v>
@@ -2454,7 +2454,7 @@
         <v>SO-10064</v>
       </c>
       <c r="B65" s="1" t="d">
-        <v>2025-05-07T05:30:00.000Z</v>
+        <v>2025-05-07T00:00:00.000Z</v>
       </c>
       <c r="C65" t="str">
         <v>Patil Enterprises</v>
@@ -2486,7 +2486,7 @@
         <v>SO-10065</v>
       </c>
       <c r="B66" s="1" t="d">
-        <v>2025-05-07T05:30:00.000Z</v>
+        <v>2025-05-07T00:00:00.000Z</v>
       </c>
       <c r="C66" t="str">
         <v>Joshi Retail</v>
@@ -2518,7 +2518,7 @@
         <v>SO-10066</v>
       </c>
       <c r="B67" s="1" t="d">
-        <v>2025-05-08T05:30:00.000Z</v>
+        <v>2025-05-08T00:00:00.000Z</v>
       </c>
       <c r="C67" t="str">
         <v>Joshi Enterprises</v>
@@ -2550,7 +2550,7 @@
         <v>SO-10067</v>
       </c>
       <c r="B68" s="1" t="d">
-        <v>2025-05-10T05:30:00.000Z</v>
+        <v>2025-05-10T00:00:00.000Z</v>
       </c>
       <c r="C68" t="str">
         <v>Mehta Traders</v>
@@ -2582,7 +2582,7 @@
         <v>SO-10068</v>
       </c>
       <c r="B69" s="1" t="d">
-        <v>2025-05-10T05:30:00.000Z</v>
+        <v>2025-05-10T00:00:00.000Z</v>
       </c>
       <c r="C69" t="str">
         <v>Sharma Enterprises</v>
@@ -2614,7 +2614,7 @@
         <v>SO-10069</v>
       </c>
       <c r="B70" s="1" t="d">
-        <v>2025-05-12T05:30:00.000Z</v>
+        <v>2025-05-12T00:00:00.000Z</v>
       </c>
       <c r="C70" t="str">
         <v>Mehta Stores</v>
@@ -2646,7 +2646,7 @@
         <v>SO-10070</v>
       </c>
       <c r="B71" s="1" t="d">
-        <v>2025-05-12T05:30:00.000Z</v>
+        <v>2025-05-12T00:00:00.000Z</v>
       </c>
       <c r="C71" t="str">
         <v>Desai Stores</v>
@@ -2678,7 +2678,7 @@
         <v>SO-10071</v>
       </c>
       <c r="B72" s="1" t="d">
-        <v>2025-05-13T05:30:00.000Z</v>
+        <v>2025-05-13T00:00:00.000Z</v>
       </c>
       <c r="C72" t="str">
         <v>Sharma Enterprises</v>
@@ -2710,7 +2710,7 @@
         <v>SO-10072</v>
       </c>
       <c r="B73" s="1" t="d">
-        <v>2025-05-13T05:30:00.000Z</v>
+        <v>2025-05-13T00:00:00.000Z</v>
       </c>
       <c r="C73" t="str">
         <v>Mehta Traders</v>
@@ -2742,7 +2742,7 @@
         <v>SO-10073</v>
       </c>
       <c r="B74" s="1" t="d">
-        <v>2025-05-14T05:30:00.000Z</v>
+        <v>2025-05-14T00:00:00.000Z</v>
       </c>
       <c r="C74" t="str">
         <v>Pillai Stores</v>
@@ -2774,7 +2774,7 @@
         <v>SO-10074</v>
       </c>
       <c r="B75" s="1" t="d">
-        <v>2025-05-15T05:30:00.000Z</v>
+        <v>2025-05-15T00:00:00.000Z</v>
       </c>
       <c r="C75" t="str">
         <v>Desai Labs</v>
@@ -2806,7 +2806,7 @@
         <v>SO-10075</v>
       </c>
       <c r="B76" s="1" t="d">
-        <v>2025-05-13T05:30:00.000Z</v>
+        <v>2025-05-13T00:00:00.000Z</v>
       </c>
       <c r="C76" t="str">
         <v>Rao Labs</v>
@@ -2838,7 +2838,7 @@
         <v>SO-10076</v>
       </c>
       <c r="B77" s="1" t="d">
-        <v>2025-05-16T05:30:00.000Z</v>
+        <v>2025-05-16T00:00:00.000Z</v>
       </c>
       <c r="C77" t="str">
         <v>Nair Labs</v>
@@ -2870,7 +2870,7 @@
         <v>SO-10077</v>
       </c>
       <c r="B78" s="1" t="d">
-        <v>2025-05-16T05:30:00.000Z</v>
+        <v>2025-05-16T00:00:00.000Z</v>
       </c>
       <c r="C78" t="str">
         <v>Kulkarni Labs</v>
@@ -2902,7 +2902,7 @@
         <v>SO-10078</v>
       </c>
       <c r="B79" s="1" t="d">
-        <v>2025-05-15T05:30:00.000Z</v>
+        <v>2025-05-15T00:00:00.000Z</v>
       </c>
       <c r="C79" t="str">
         <v>Rao Retail</v>
@@ -2934,7 +2934,7 @@
         <v>SO-10079</v>
       </c>
       <c r="B80" s="1" t="d">
-        <v>2025-05-16T05:30:00.000Z</v>
+        <v>2025-05-16T00:00:00.000Z</v>
       </c>
       <c r="C80" t="str">
         <v>Sharma Traders</v>
@@ -2966,7 +2966,7 @@
         <v>SO-10080</v>
       </c>
       <c r="B81" s="1" t="d">
-        <v>2025-05-17T05:30:00.000Z</v>
+        <v>2025-05-17T00:00:00.000Z</v>
       </c>
       <c r="C81" t="str">
         <v>Sharma Traders</v>
@@ -2998,7 +2998,7 @@
         <v>SO-10081</v>
       </c>
       <c r="B82" s="1" t="d">
-        <v>2025-05-19T05:30:00.000Z</v>
+        <v>2025-05-19T00:00:00.000Z</v>
       </c>
       <c r="C82" t="str">
         <v>Kulkarni Enterprises</v>
@@ -3030,7 +3030,7 @@
         <v>SO-10082</v>
       </c>
       <c r="B83" s="1" t="d">
-        <v>2025-05-19T05:30:00.000Z</v>
+        <v>2025-05-19T00:00:00.000Z</v>
       </c>
       <c r="C83" t="str">
         <v>Patil Traders</v>
@@ -3062,7 +3062,7 @@
         <v>SO-10083</v>
       </c>
       <c r="B84" s="1" t="d">
-        <v>2025-05-18T05:30:00.000Z</v>
+        <v>2025-05-18T00:00:00.000Z</v>
       </c>
       <c r="C84" t="str">
         <v>Nair Traders</v>
@@ -3094,7 +3094,7 @@
         <v>SO-10084</v>
       </c>
       <c r="B85" s="1" t="d">
-        <v>2025-05-19T05:30:00.000Z</v>
+        <v>2025-05-19T00:00:00.000Z</v>
       </c>
       <c r="C85" t="str">
         <v>Desai Labs</v>
@@ -3126,7 +3126,7 @@
         <v>SO-10085</v>
       </c>
       <c r="B86" s="1" t="d">
-        <v>2025-05-20T05:30:00.000Z</v>
+        <v>2025-05-20T00:00:00.000Z</v>
       </c>
       <c r="C86" t="str">
         <v>Khan Enterprises</v>
@@ -3158,7 +3158,7 @@
         <v>SO-10086</v>
       </c>
       <c r="B87" s="1" t="d">
-        <v>2025-05-19T05:30:00.000Z</v>
+        <v>2025-05-19T00:00:00.000Z</v>
       </c>
       <c r="C87" t="str">
         <v>Sharma Enterprises</v>
@@ -3190,7 +3190,7 @@
         <v>SO-10087</v>
       </c>
       <c r="B88" s="1" t="d">
-        <v>2025-05-20T05:30:00.000Z</v>
+        <v>2025-05-20T00:00:00.000Z</v>
       </c>
       <c r="C88" t="str">
         <v>Iyer Stores</v>
@@ -3222,7 +3222,7 @@
         <v>SO-10088</v>
       </c>
       <c r="B89" s="1" t="d">
-        <v>2025-05-22T05:30:00.000Z</v>
+        <v>2025-05-22T00:00:00.000Z</v>
       </c>
       <c r="C89" t="str">
         <v>Pillai Solutions</v>
@@ -3254,7 +3254,7 @@
         <v>SO-10089</v>
       </c>
       <c r="B90" s="1" t="d">
-        <v>2025-05-23T05:30:00.000Z</v>
+        <v>2025-05-23T00:00:00.000Z</v>
       </c>
       <c r="C90" t="str">
         <v>Patil Retail</v>
@@ -3286,7 +3286,7 @@
         <v>SO-10090</v>
       </c>
       <c r="B91" s="1" t="d">
-        <v>2025-05-23T05:30:00.000Z</v>
+        <v>2025-05-23T00:00:00.000Z</v>
       </c>
       <c r="C91" t="str">
         <v>Joshi Retail</v>
@@ -3318,7 +3318,7 @@
         <v>SO-10091</v>
       </c>
       <c r="B92" s="1" t="d">
-        <v>2025-05-24T05:30:00.000Z</v>
+        <v>2025-05-24T00:00:00.000Z</v>
       </c>
       <c r="C92" t="str">
         <v>Rao Solutions</v>
@@ -3350,7 +3350,7 @@
         <v>SO-10092</v>
       </c>
       <c r="B93" s="1" t="d">
-        <v>2025-05-24T05:30:00.000Z</v>
+        <v>2025-05-24T00:00:00.000Z</v>
       </c>
       <c r="C93" t="str">
         <v>Desai Labs</v>
@@ -3382,7 +3382,7 @@
         <v>SO-10093</v>
       </c>
       <c r="B94" s="1" t="d">
-        <v>2025-05-24T05:30:00.000Z</v>
+        <v>2025-05-24T00:00:00.000Z</v>
       </c>
       <c r="C94" t="str">
         <v>Khan Stores</v>
@@ -3414,7 +3414,7 @@
         <v>SO-10094</v>
       </c>
       <c r="B95" s="1" t="d">
-        <v>2025-05-27T05:30:00.000Z</v>
+        <v>2025-05-27T00:00:00.000Z</v>
       </c>
       <c r="C95" t="str">
         <v>Desai Enterprises</v>
@@ -3446,7 +3446,7 @@
         <v>SO-10095</v>
       </c>
       <c r="B96" s="1" t="d">
-        <v>2025-05-25T05:30:00.000Z</v>
+        <v>2025-05-25T00:00:00.000Z</v>
       </c>
       <c r="C96" t="str">
         <v>Rao Stores</v>
@@ -3478,7 +3478,7 @@
         <v>SO-10096</v>
       </c>
       <c r="B97" s="1" t="d">
-        <v>2025-05-28T05:30:00.000Z</v>
+        <v>2025-05-28T00:00:00.000Z</v>
       </c>
       <c r="C97" t="str">
         <v>Desai Enterprises</v>
@@ -3510,7 +3510,7 @@
         <v>SO-10097</v>
       </c>
       <c r="B98" s="1" t="d">
-        <v>2025-05-26T05:30:00.000Z</v>
+        <v>2025-05-26T00:00:00.000Z</v>
       </c>
       <c r="C98" t="str">
         <v>Kulkarni Traders</v>
@@ -3542,7 +3542,7 @@
         <v>SO-10098</v>
       </c>
       <c r="B99" s="1" t="d">
-        <v>2025-05-28T05:30:00.000Z</v>
+        <v>2025-05-28T00:00:00.000Z</v>
       </c>
       <c r="C99" t="str">
         <v>Sharma Retail</v>
@@ -3574,7 +3574,7 @@
         <v>SO-10099</v>
       </c>
       <c r="B100" s="1" t="d">
-        <v>2025-05-29T05:30:00.000Z</v>
+        <v>2025-05-29T00:00:00.000Z</v>
       </c>
       <c r="C100" t="str">
         <v>Pillai Stores</v>
@@ -3606,7 +3606,7 @@
         <v>SO-10100</v>
       </c>
       <c r="B101" s="1" t="d">
-        <v>2025-05-29T05:30:00.000Z</v>
+        <v>2025-05-29T00:00:00.000Z</v>
       </c>
       <c r="C101" t="str">
         <v>Khan Stores</v>
@@ -3638,7 +3638,7 @@
         <v>SO-10101</v>
       </c>
       <c r="B102" s="1" t="d">
-        <v>2025-05-30T05:30:00.000Z</v>
+        <v>2025-05-30T00:00:00.000Z</v>
       </c>
       <c r="C102" t="str">
         <v>Kulkarni Enterprises</v>
@@ -3670,7 +3670,7 @@
         <v>SO-10102</v>
       </c>
       <c r="B103" s="1" t="d">
-        <v>2025-05-30T05:30:00.000Z</v>
+        <v>2025-05-30T00:00:00.000Z</v>
       </c>
       <c r="C103" t="str">
         <v>Kulkarni Traders</v>
@@ -3702,7 +3702,7 @@
         <v>SO-10103</v>
       </c>
       <c r="B104" s="1" t="d">
-        <v>2025-05-29T05:30:00.000Z</v>
+        <v>2025-05-29T00:00:00.000Z</v>
       </c>
       <c r="C104" t="str">
         <v>Desai Labs</v>
@@ -3734,7 +3734,7 @@
         <v>SO-10104</v>
       </c>
       <c r="B105" s="1" t="d">
-        <v>2025-06-01T05:30:00.000Z</v>
+        <v>2025-06-01T00:00:00.000Z</v>
       </c>
       <c r="C105" t="str">
         <v>Patil Labs</v>
@@ -3766,7 +3766,7 @@
         <v>SO-10105</v>
       </c>
       <c r="B106" s="1" t="d">
-        <v>2025-06-02T05:30:00.000Z</v>
+        <v>2025-06-02T00:00:00.000Z</v>
       </c>
       <c r="C106" t="str">
         <v>Rao Labs</v>
@@ -3798,7 +3798,7 @@
         <v>SO-10106</v>
       </c>
       <c r="B107" s="1" t="d">
-        <v>2025-05-31T05:30:00.000Z</v>
+        <v>2025-05-31T00:00:00.000Z</v>
       </c>
       <c r="C107" t="str">
         <v>Sharma Traders</v>
@@ -3830,7 +3830,7 @@
         <v>SO-10107</v>
       </c>
       <c r="B108" s="1" t="d">
-        <v>2025-05-31T05:30:00.000Z</v>
+        <v>2025-05-31T00:00:00.000Z</v>
       </c>
       <c r="C108" t="str">
         <v>Kulkarni Labs</v>
@@ -3862,7 +3862,7 @@
         <v>SO-10108</v>
       </c>
       <c r="B109" s="1" t="d">
-        <v>2025-06-03T05:30:00.000Z</v>
+        <v>2025-06-03T00:00:00.000Z</v>
       </c>
       <c r="C109" t="str">
         <v>Khan Retail</v>
@@ -3894,7 +3894,7 @@
         <v>SO-10109</v>
       </c>
       <c r="B110" s="1" t="d">
-        <v>2025-06-03T05:30:00.000Z</v>
+        <v>2025-06-03T00:00:00.000Z</v>
       </c>
       <c r="C110" t="str">
         <v>Kulkarni Labs</v>
@@ -3926,7 +3926,7 @@
         <v>SO-10110</v>
       </c>
       <c r="B111" s="1" t="d">
-        <v>2025-06-02T05:30:00.000Z</v>
+        <v>2025-06-02T00:00:00.000Z</v>
       </c>
       <c r="C111" t="str">
         <v>Nair Labs</v>
@@ -3958,7 +3958,7 @@
         <v>SO-10111</v>
       </c>
       <c r="B112" s="1" t="d">
-        <v>2025-06-04T05:30:00.000Z</v>
+        <v>2025-06-04T00:00:00.000Z</v>
       </c>
       <c r="C112" t="str">
         <v>Joshi Labs</v>
@@ -3990,7 +3990,7 @@
         <v>SO-10112</v>
       </c>
       <c r="B113" s="1" t="d">
-        <v>2025-06-03T05:30:00.000Z</v>
+        <v>2025-06-03T00:00:00.000Z</v>
       </c>
       <c r="C113" t="str">
         <v>Patil Stores</v>
@@ -4022,7 +4022,7 @@
         <v>SO-10113</v>
       </c>
       <c r="B114" s="1" t="d">
-        <v>2025-06-04T05:30:00.000Z</v>
+        <v>2025-06-04T00:00:00.000Z</v>
       </c>
       <c r="C114" t="str">
         <v>Rao Enterprises</v>
@@ -4054,7 +4054,7 @@
         <v>SO-10114</v>
       </c>
       <c r="B115" s="1" t="d">
-        <v>2025-06-07T05:30:00.000Z</v>
+        <v>2025-06-07T00:00:00.000Z</v>
       </c>
       <c r="C115" t="str">
         <v>Patil Traders</v>
@@ -4086,7 +4086,7 @@
         <v>SO-10115</v>
       </c>
       <c r="B116" s="1" t="d">
-        <v>2025-06-06T05:30:00.000Z</v>
+        <v>2025-06-06T00:00:00.000Z</v>
       </c>
       <c r="C116" t="str">
         <v>Nair Solutions</v>
@@ -4118,7 +4118,7 @@
         <v>SO-10116</v>
       </c>
       <c r="B117" s="1" t="d">
-        <v>2025-06-07T05:30:00.000Z</v>
+        <v>2025-06-07T00:00:00.000Z</v>
       </c>
       <c r="C117" t="str">
         <v>Pillai Stores</v>
@@ -4150,7 +4150,7 @@
         <v>SO-10117</v>
       </c>
       <c r="B118" s="1" t="d">
-        <v>2025-06-06T05:30:00.000Z</v>
+        <v>2025-06-06T00:00:00.000Z</v>
       </c>
       <c r="C118" t="str">
         <v>Desai Solutions</v>
@@ -4182,7 +4182,7 @@
         <v>SO-10118</v>
       </c>
       <c r="B119" s="1" t="d">
-        <v>2025-06-08T05:30:00.000Z</v>
+        <v>2025-06-08T00:00:00.000Z</v>
       </c>
       <c r="C119" t="str">
         <v>Desai Traders</v>
@@ -4214,7 +4214,7 @@
         <v>SO-10119</v>
       </c>
       <c r="B120" s="1" t="d">
-        <v>2025-06-09T05:30:00.000Z</v>
+        <v>2025-06-09T00:00:00.000Z</v>
       </c>
       <c r="C120" t="str">
         <v>Joshi Stores</v>
@@ -4246,7 +4246,7 @@
         <v>SO-10120</v>
       </c>
       <c r="B121" s="1" t="d">
-        <v>2025-06-08T05:30:00.000Z</v>
+        <v>2025-06-08T00:00:00.000Z</v>
       </c>
       <c r="C121" t="str">
         <v>Kulkarni Enterprises</v>
@@ -4278,7 +4278,7 @@
         <v>SO-10121</v>
       </c>
       <c r="B122" s="1" t="d">
-        <v>2025-06-11T05:30:00.000Z</v>
+        <v>2025-06-11T00:00:00.000Z</v>
       </c>
       <c r="C122" t="str">
         <v>Joshi Solutions</v>
@@ -4310,7 +4310,7 @@
         <v>SO-10122</v>
       </c>
       <c r="B123" s="1" t="d">
-        <v>2025-06-10T05:30:00.000Z</v>
+        <v>2025-06-10T00:00:00.000Z</v>
       </c>
       <c r="C123" t="str">
         <v>Patil Enterprises</v>
@@ -4342,7 +4342,7 @@
         <v>SO-10123</v>
       </c>
       <c r="B124" s="1" t="d">
-        <v>2025-06-12T05:30:00.000Z</v>
+        <v>2025-06-12T00:00:00.000Z</v>
       </c>
       <c r="C124" t="str">
         <v>Patil Stores</v>
@@ -4374,7 +4374,7 @@
         <v>SO-10124</v>
       </c>
       <c r="B125" s="1" t="d">
-        <v>2025-06-12T05:30:00.000Z</v>
+        <v>2025-06-12T00:00:00.000Z</v>
       </c>
       <c r="C125" t="str">
         <v>Nair Traders</v>
@@ -4406,7 +4406,7 @@
         <v>SO-10125</v>
       </c>
       <c r="B126" s="1" t="d">
-        <v>2025-06-11T05:30:00.000Z</v>
+        <v>2025-06-11T00:00:00.000Z</v>
       </c>
       <c r="C126" t="str">
         <v>Desai Solutions</v>
@@ -4438,7 +4438,7 @@
         <v>SO-10126</v>
       </c>
       <c r="B127" s="1" t="d">
-        <v>2025-06-12T05:30:00.000Z</v>
+        <v>2025-06-12T00:00:00.000Z</v>
       </c>
       <c r="C127" t="str">
         <v>Joshi Labs</v>
@@ -4470,7 +4470,7 @@
         <v>SO-10127</v>
       </c>
       <c r="B128" s="1" t="d">
-        <v>2025-06-14T05:30:00.000Z</v>
+        <v>2025-06-14T00:00:00.000Z</v>
       </c>
       <c r="C128" t="str">
         <v>Nair Traders</v>
@@ -4502,7 +4502,7 @@
         <v>SO-10128</v>
       </c>
       <c r="B129" s="1" t="d">
-        <v>2025-06-13T05:30:00.000Z</v>
+        <v>2025-06-13T00:00:00.000Z</v>
       </c>
       <c r="C129" t="str">
         <v>Patil Labs</v>
@@ -4534,7 +4534,7 @@
         <v>SO-10129</v>
       </c>
       <c r="B130" s="1" t="d">
-        <v>2025-06-13T05:30:00.000Z</v>
+        <v>2025-06-13T00:00:00.000Z</v>
       </c>
       <c r="C130" t="str">
         <v>Nair Enterprises</v>
@@ -4566,7 +4566,7 @@
         <v>SO-10130</v>
       </c>
       <c r="B131" s="1" t="d">
-        <v>2025-06-15T05:30:00.000Z</v>
+        <v>2025-06-15T00:00:00.000Z</v>
       </c>
       <c r="C131" t="str">
         <v>Patil Traders</v>
@@ -4598,7 +4598,7 @@
         <v>SO-10131</v>
       </c>
       <c r="B132" s="1" t="d">
-        <v>2025-06-15T05:30:00.000Z</v>
+        <v>2025-06-15T00:00:00.000Z</v>
       </c>
       <c r="C132" t="str">
         <v>Gupta Stores</v>
@@ -4630,7 +4630,7 @@
         <v>SO-10132</v>
       </c>
       <c r="B133" s="1" t="d">
-        <v>2025-06-15T05:30:00.000Z</v>
+        <v>2025-06-15T00:00:00.000Z</v>
       </c>
       <c r="C133" t="str">
         <v>Nair Stores</v>
@@ -4662,7 +4662,7 @@
         <v>SO-10133</v>
       </c>
       <c r="B134" s="1" t="d">
-        <v>2025-06-17T05:30:00.000Z</v>
+        <v>2025-06-17T00:00:00.000Z</v>
       </c>
       <c r="C134" t="str">
         <v>Desai Retail</v>
@@ -4694,7 +4694,7 @@
         <v>SO-10134</v>
       </c>
       <c r="B135" s="1" t="d">
-        <v>2025-06-16T05:30:00.000Z</v>
+        <v>2025-06-16T00:00:00.000Z</v>
       </c>
       <c r="C135" t="str">
         <v>Patil Enterprises</v>
@@ -4726,7 +4726,7 @@
         <v>SO-10135</v>
       </c>
       <c r="B136" s="1" t="d">
-        <v>2025-06-18T05:30:00.000Z</v>
+        <v>2025-06-18T00:00:00.000Z</v>
       </c>
       <c r="C136" t="str">
         <v>Rao Stores</v>
@@ -4758,7 +4758,7 @@
         <v>SO-10136</v>
       </c>
       <c r="B137" s="1" t="d">
-        <v>2025-06-19T05:30:00.000Z</v>
+        <v>2025-06-19T00:00:00.000Z</v>
       </c>
       <c r="C137" t="str">
         <v>Sharma Retail</v>
@@ -4790,7 +4790,7 @@
         <v>SO-10137</v>
       </c>
       <c r="B138" s="1" t="d">
-        <v>2025-06-20T05:30:00.000Z</v>
+        <v>2025-06-20T00:00:00.000Z</v>
       </c>
       <c r="C138" t="str">
         <v>Kulkarni Stores</v>
@@ -4822,7 +4822,7 @@
         <v>SO-10138</v>
       </c>
       <c r="B139" s="1" t="d">
-        <v>2025-06-18T05:30:00.000Z</v>
+        <v>2025-06-18T00:00:00.000Z</v>
       </c>
       <c r="C139" t="str">
         <v>Desai Stores</v>
@@ -4854,7 +4854,7 @@
         <v>SO-10139</v>
       </c>
       <c r="B140" s="1" t="d">
-        <v>2025-06-19T05:30:00.000Z</v>
+        <v>2025-06-19T00:00:00.000Z</v>
       </c>
       <c r="C140" t="str">
         <v>Pillai Enterprises</v>
@@ -4886,7 +4886,7 @@
         <v>SO-10140</v>
       </c>
       <c r="B141" s="1" t="d">
-        <v>2025-06-19T05:30:00.000Z</v>
+        <v>2025-06-19T00:00:00.000Z</v>
       </c>
       <c r="C141" t="str">
         <v>Pillai Stores</v>
@@ -4918,7 +4918,7 @@
         <v>SO-10141</v>
       </c>
       <c r="B142" s="1" t="d">
-        <v>2025-06-20T05:30:00.000Z</v>
+        <v>2025-06-20T00:00:00.000Z</v>
       </c>
       <c r="C142" t="str">
         <v>Iyer Labs</v>
@@ -4950,7 +4950,7 @@
         <v>SO-10142</v>
       </c>
       <c r="B143" s="1" t="d">
-        <v>2025-06-20T05:30:00.000Z</v>
+        <v>2025-06-20T00:00:00.000Z</v>
       </c>
       <c r="C143" t="str">
         <v>Sharma Enterprises</v>
@@ -4982,7 +4982,7 @@
         <v>SO-10143</v>
       </c>
       <c r="B144" s="1" t="d">
-        <v>2025-06-23T05:30:00.000Z</v>
+        <v>2025-06-23T00:00:00.000Z</v>
       </c>
       <c r="C144" t="str">
         <v>Khan Labs</v>
@@ -5014,7 +5014,7 @@
         <v>SO-10144</v>
       </c>
       <c r="B145" s="1" t="d">
-        <v>2025-06-22T05:30:00.000Z</v>
+        <v>2025-06-22T00:00:00.000Z</v>
       </c>
       <c r="C145" t="str">
         <v>Patil Enterprises</v>
@@ -5046,7 +5046,7 @@
         <v>SO-10145</v>
       </c>
       <c r="B146" s="1" t="d">
-        <v>2025-06-24T05:30:00.000Z</v>
+        <v>2025-06-24T00:00:00.000Z</v>
       </c>
       <c r="C146" t="str">
         <v>Patil Enterprises</v>
@@ -5078,7 +5078,7 @@
         <v>SO-10146</v>
       </c>
       <c r="B147" s="1" t="d">
-        <v>2025-06-24T05:30:00.000Z</v>
+        <v>2025-06-24T00:00:00.000Z</v>
       </c>
       <c r="C147" t="str">
         <v>Mehta Stores</v>
@@ -5110,7 +5110,7 @@
         <v>SO-10147</v>
       </c>
       <c r="B148" s="1" t="d">
-        <v>2025-06-26T05:30:00.000Z</v>
+        <v>2025-06-26T00:00:00.000Z</v>
       </c>
       <c r="C148" t="str">
         <v>Patil Traders</v>
@@ -5142,7 +5142,7 @@
         <v>SO-10148</v>
       </c>
       <c r="B149" s="1" t="d">
-        <v>2025-06-24T05:30:00.000Z</v>
+        <v>2025-06-24T00:00:00.000Z</v>
       </c>
       <c r="C149" t="str">
         <v>Nair Labs</v>
@@ -5174,7 +5174,7 @@
         <v>SO-10149</v>
       </c>
       <c r="B150" s="1" t="d">
-        <v>2025-06-25T05:30:00.000Z</v>
+        <v>2025-06-25T00:00:00.000Z</v>
       </c>
       <c r="C150" t="str">
         <v>Kulkarni Traders</v>
@@ -5206,7 +5206,7 @@
         <v>SO-10150</v>
       </c>
       <c r="B151" s="1" t="d">
-        <v>2025-06-27T05:30:00.000Z</v>
+        <v>2025-06-27T00:00:00.000Z</v>
       </c>
       <c r="C151" t="str">
         <v>Mehta Traders</v>
@@ -5238,7 +5238,7 @@
         <v>SO-10151</v>
       </c>
       <c r="B152" s="1" t="d">
-        <v>2025-06-26T05:30:00.000Z</v>
+        <v>2025-06-26T00:00:00.000Z</v>
       </c>
       <c r="C152" t="str">
         <v>Joshi Stores</v>
@@ -5270,7 +5270,7 @@
         <v>SO-10152</v>
       </c>
       <c r="B153" s="1" t="d">
-        <v>2025-06-28T05:30:00.000Z</v>
+        <v>2025-06-28T00:00:00.000Z</v>
       </c>
       <c r="C153" t="str">
         <v>Kulkarni Traders</v>
@@ -5302,7 +5302,7 @@
         <v>SO-10153</v>
       </c>
       <c r="B154" s="1" t="d">
-        <v>2025-06-29T05:30:00.000Z</v>
+        <v>2025-06-29T00:00:00.000Z</v>
       </c>
       <c r="C154" t="str">
         <v>Sharma Solutions</v>
@@ -5334,7 +5334,7 @@
         <v>SO-10154</v>
       </c>
       <c r="B155" s="1" t="d">
-        <v>2025-06-28T05:30:00.000Z</v>
+        <v>2025-06-28T00:00:00.000Z</v>
       </c>
       <c r="C155" t="str">
         <v>Patil Retail</v>
@@ -5366,7 +5366,7 @@
         <v>SO-10155</v>
       </c>
       <c r="B156" s="1" t="d">
-        <v>2025-06-30T05:30:00.000Z</v>
+        <v>2025-06-30T00:00:00.000Z</v>
       </c>
       <c r="C156" t="str">
         <v>Kulkarni Enterprises</v>
@@ -5398,7 +5398,7 @@
         <v>SO-10156</v>
       </c>
       <c r="B157" s="1" t="d">
-        <v>2025-06-30T05:30:00.000Z</v>
+        <v>2025-06-30T00:00:00.000Z</v>
       </c>
       <c r="C157" t="str">
         <v>Pillai Solutions</v>
@@ -5430,7 +5430,7 @@
         <v>SO-10157</v>
       </c>
       <c r="B158" s="1" t="d">
-        <v>2025-06-29T05:30:00.000Z</v>
+        <v>2025-06-29T00:00:00.000Z</v>
       </c>
       <c r="C158" t="str">
         <v>Pillai Stores</v>
@@ -5462,7 +5462,7 @@
         <v>SO-10158</v>
       </c>
       <c r="B159" s="1" t="d">
-        <v>2025-06-29T05:30:00.000Z</v>
+        <v>2025-06-29T00:00:00.000Z</v>
       </c>
       <c r="C159" t="str">
         <v>Rao Labs</v>
@@ -5494,7 +5494,7 @@
         <v>SO-10159</v>
       </c>
       <c r="B160" s="1" t="d">
-        <v>2025-07-02T05:30:00.000Z</v>
+        <v>2025-07-02T00:00:00.000Z</v>
       </c>
       <c r="C160" t="str">
         <v>Patil Traders</v>
@@ -5526,7 +5526,7 @@
         <v>SO-10160</v>
       </c>
       <c r="B161" s="1" t="d">
-        <v>2025-07-01T05:30:00.000Z</v>
+        <v>2025-07-01T00:00:00.000Z</v>
       </c>
       <c r="C161" t="str">
         <v>Nair Retail</v>
@@ -5558,7 +5558,7 @@
         <v>SO-10161</v>
       </c>
       <c r="B162" s="1" t="d">
-        <v>2025-07-03T05:30:00.000Z</v>
+        <v>2025-07-03T00:00:00.000Z</v>
       </c>
       <c r="C162" t="str">
         <v>Joshi Traders</v>
@@ -5590,7 +5590,7 @@
         <v>SO-10162</v>
       </c>
       <c r="B163" s="1" t="d">
-        <v>2025-07-02T05:30:00.000Z</v>
+        <v>2025-07-02T00:00:00.000Z</v>
       </c>
       <c r="C163" t="str">
         <v>Khan Stores</v>
@@ -5622,7 +5622,7 @@
         <v>SO-10163</v>
       </c>
       <c r="B164" s="1" t="d">
-        <v>2025-07-04T05:30:00.000Z</v>
+        <v>2025-07-04T00:00:00.000Z</v>
       </c>
       <c r="C164" t="str">
         <v>Mehta Stores</v>
@@ -5654,7 +5654,7 @@
         <v>SO-10164</v>
       </c>
       <c r="B165" s="1" t="d">
-        <v>2025-07-03T05:30:00.000Z</v>
+        <v>2025-07-03T00:00:00.000Z</v>
       </c>
       <c r="C165" t="str">
         <v>Sharma Enterprises</v>
@@ -5686,7 +5686,7 @@
         <v>SO-10165</v>
       </c>
       <c r="B166" s="1" t="d">
-        <v>2025-07-05T05:30:00.000Z</v>
+        <v>2025-07-05T00:00:00.000Z</v>
       </c>
       <c r="C166" t="str">
         <v>Kulkarni Traders</v>
@@ -5718,7 +5718,7 @@
         <v>SO-10166</v>
       </c>
       <c r="B167" s="1" t="d">
-        <v>2025-07-04T05:30:00.000Z</v>
+        <v>2025-07-04T00:00:00.000Z</v>
       </c>
       <c r="C167" t="str">
         <v>Patil Labs</v>
@@ -5750,7 +5750,7 @@
         <v>SO-10167</v>
       </c>
       <c r="B168" s="1" t="d">
-        <v>2025-07-05T05:30:00.000Z</v>
+        <v>2025-07-05T00:00:00.000Z</v>
       </c>
       <c r="C168" t="str">
         <v>Gupta Enterprises</v>
@@ -5782,7 +5782,7 @@
         <v>SO-10168</v>
       </c>
       <c r="B169" s="1" t="d">
-        <v>2025-07-05T05:30:00.000Z</v>
+        <v>2025-07-05T00:00:00.000Z</v>
       </c>
       <c r="C169" t="str">
         <v>Patil Stores</v>
@@ -5814,7 +5814,7 @@
         <v>SO-10169</v>
       </c>
       <c r="B170" s="1" t="d">
-        <v>2025-07-06T05:30:00.000Z</v>
+        <v>2025-07-06T00:00:00.000Z</v>
       </c>
       <c r="C170" t="str">
         <v>Khan Solutions</v>
@@ -5846,7 +5846,7 @@
         <v>SO-10170</v>
       </c>
       <c r="B171" s="1" t="d">
-        <v>2025-07-08T05:30:00.000Z</v>
+        <v>2025-07-08T00:00:00.000Z</v>
       </c>
       <c r="C171" t="str">
         <v>Pillai Stores</v>
@@ -5878,7 +5878,7 @@
         <v>SO-10171</v>
       </c>
       <c r="B172" s="1" t="d">
-        <v>2025-07-09T05:30:00.000Z</v>
+        <v>2025-07-09T00:00:00.000Z</v>
       </c>
       <c r="C172" t="str">
         <v>Khan Retail</v>
@@ -5910,7 +5910,7 @@
         <v>SO-10172</v>
       </c>
       <c r="B173" s="1" t="d">
-        <v>2025-07-08T05:30:00.000Z</v>
+        <v>2025-07-08T00:00:00.000Z</v>
       </c>
       <c r="C173" t="str">
         <v>Pillai Retail</v>
@@ -5942,7 +5942,7 @@
         <v>SO-10173</v>
       </c>
       <c r="B174" s="1" t="d">
-        <v>2025-07-10T05:30:00.000Z</v>
+        <v>2025-07-10T00:00:00.000Z</v>
       </c>
       <c r="C174" t="str">
         <v>Khan Stores</v>
@@ -5974,7 +5974,7 @@
         <v>SO-10174</v>
       </c>
       <c r="B175" s="1" t="d">
-        <v>2025-07-10T05:30:00.000Z</v>
+        <v>2025-07-10T00:00:00.000Z</v>
       </c>
       <c r="C175" t="str">
         <v>Joshi Labs</v>
@@ -6006,7 +6006,7 @@
         <v>SO-10175</v>
       </c>
       <c r="B176" s="1" t="d">
-        <v>2025-07-11T05:30:00.000Z</v>
+        <v>2025-07-11T00:00:00.000Z</v>
       </c>
       <c r="C176" t="str">
         <v>Nair Traders</v>
@@ -6038,7 +6038,7 @@
         <v>SO-10176</v>
       </c>
       <c r="B177" s="1" t="d">
-        <v>2025-07-12T05:30:00.000Z</v>
+        <v>2025-07-12T00:00:00.000Z</v>
       </c>
       <c r="C177" t="str">
         <v>Joshi Labs</v>
@@ -6070,7 +6070,7 @@
         <v>SO-10177</v>
       </c>
       <c r="B178" s="1" t="d">
-        <v>2025-07-11T05:30:00.000Z</v>
+        <v>2025-07-11T00:00:00.000Z</v>
       </c>
       <c r="C178" t="str">
         <v>Khan Retail</v>
@@ -6102,7 +6102,7 @@
         <v>SO-10178</v>
       </c>
       <c r="B179" s="1" t="d">
-        <v>2025-07-11T05:30:00.000Z</v>
+        <v>2025-07-11T00:00:00.000Z</v>
       </c>
       <c r="C179" t="str">
         <v>Khan Traders</v>
@@ -6134,7 +6134,7 @@
         <v>SO-10179</v>
       </c>
       <c r="B180" s="1" t="d">
-        <v>2025-07-14T05:30:00.000Z</v>
+        <v>2025-07-14T00:00:00.000Z</v>
       </c>
       <c r="C180" t="str">
         <v>Patil Labs</v>
@@ -6166,7 +6166,7 @@
         <v>SO-10180</v>
       </c>
       <c r="B181" s="1" t="d">
-        <v>2025-07-14T05:30:00.000Z</v>
+        <v>2025-07-14T00:00:00.000Z</v>
       </c>
       <c r="C181" t="str">
         <v>Rao Labs</v>
@@ -6198,7 +6198,7 @@
         <v>SO-10181</v>
       </c>
       <c r="B182" s="1" t="d">
-        <v>2025-07-13T05:30:00.000Z</v>
+        <v>2025-07-13T00:00:00.000Z</v>
       </c>
       <c r="C182" t="str">
         <v>Pillai Stores</v>
@@ -6230,7 +6230,7 @@
         <v>SO-10182</v>
       </c>
       <c r="B183" s="1" t="d">
-        <v>2025-07-14T05:30:00.000Z</v>
+        <v>2025-07-14T00:00:00.000Z</v>
       </c>
       <c r="C183" t="str">
         <v>Rao Enterprises</v>
@@ -6262,7 +6262,7 @@
         <v>SO-10183</v>
       </c>
       <c r="B184" s="1" t="d">
-        <v>2025-07-14T05:30:00.000Z</v>
+        <v>2025-07-14T00:00:00.000Z</v>
       </c>
       <c r="C184" t="str">
         <v>Patil Enterprises</v>
@@ -6294,7 +6294,7 @@
         <v>SO-10184</v>
       </c>
       <c r="B185" s="1" t="d">
-        <v>2025-07-14T05:30:00.000Z</v>
+        <v>2025-07-14T00:00:00.000Z</v>
       </c>
       <c r="C185" t="str">
         <v>Patil Labs</v>
@@ -6326,7 +6326,7 @@
         <v>SO-10185</v>
       </c>
       <c r="B186" s="1" t="d">
-        <v>2025-07-16T05:30:00.000Z</v>
+        <v>2025-07-16T00:00:00.000Z</v>
       </c>
       <c r="C186" t="str">
         <v>Joshi Retail</v>
@@ -6358,7 +6358,7 @@
         <v>SO-10186</v>
       </c>
       <c r="B187" s="1" t="d">
-        <v>2025-07-17T05:30:00.000Z</v>
+        <v>2025-07-17T00:00:00.000Z</v>
       </c>
       <c r="C187" t="str">
         <v>Desai Traders</v>
@@ -6390,7 +6390,7 @@
         <v>SO-10187</v>
       </c>
       <c r="B188" s="1" t="d">
-        <v>2025-07-18T05:30:00.000Z</v>
+        <v>2025-07-18T00:00:00.000Z</v>
       </c>
       <c r="C188" t="str">
         <v>Iyer Traders</v>
@@ -6422,7 +6422,7 @@
         <v>SO-10188</v>
       </c>
       <c r="B189" s="1" t="d">
-        <v>2025-07-17T05:30:00.000Z</v>
+        <v>2025-07-17T00:00:00.000Z</v>
       </c>
       <c r="C189" t="str">
         <v>Mehta Traders</v>
@@ -6454,7 +6454,7 @@
         <v>SO-10189</v>
       </c>
       <c r="B190" s="1" t="d">
-        <v>2025-07-18T05:30:00.000Z</v>
+        <v>2025-07-18T00:00:00.000Z</v>
       </c>
       <c r="C190" t="str">
         <v>Joshi Solutions</v>
@@ -6486,7 +6486,7 @@
         <v>SO-10190</v>
       </c>
       <c r="B191" s="1" t="d">
-        <v>2025-07-18T05:30:00.000Z</v>
+        <v>2025-07-18T00:00:00.000Z</v>
       </c>
       <c r="C191" t="str">
         <v>Sharma Enterprises</v>
@@ -6518,7 +6518,7 @@
         <v>SO-10191</v>
       </c>
       <c r="B192" s="1" t="d">
-        <v>2025-07-19T05:30:00.000Z</v>
+        <v>2025-07-19T00:00:00.000Z</v>
       </c>
       <c r="C192" t="str">
         <v>Mehta Stores</v>
@@ -6550,7 +6550,7 @@
         <v>SO-10192</v>
       </c>
       <c r="B193" s="1" t="d">
-        <v>2025-07-21T05:30:00.000Z</v>
+        <v>2025-07-21T00:00:00.000Z</v>
       </c>
       <c r="C193" t="str">
         <v>Sharma Retail</v>
@@ -6582,7 +6582,7 @@
         <v>SO-10193</v>
       </c>
       <c r="B194" s="1" t="d">
-        <v>2025-07-22T05:30:00.000Z</v>
+        <v>2025-07-22T00:00:00.000Z</v>
       </c>
       <c r="C194" t="str">
         <v>Iyer Retail</v>
@@ -6614,7 +6614,7 @@
         <v>SO-10194</v>
       </c>
       <c r="B195" s="1" t="d">
-        <v>2025-07-21T05:30:00.000Z</v>
+        <v>2025-07-21T00:00:00.000Z</v>
       </c>
       <c r="C195" t="str">
         <v>Iyer Labs</v>
@@ -6646,7 +6646,7 @@
         <v>SO-10195</v>
       </c>
       <c r="B196" s="1" t="d">
-        <v>2025-07-22T05:30:00.000Z</v>
+        <v>2025-07-22T00:00:00.000Z</v>
       </c>
       <c r="C196" t="str">
         <v>Khan Retail</v>
@@ -6678,7 +6678,7 @@
         <v>SO-10196</v>
       </c>
       <c r="B197" s="1" t="d">
-        <v>2025-07-22T05:30:00.000Z</v>
+        <v>2025-07-22T00:00:00.000Z</v>
       </c>
       <c r="C197" t="str">
         <v>Kulkarni Stores</v>
@@ -6710,7 +6710,7 @@
         <v>SO-10197</v>
       </c>
       <c r="B198" s="1" t="d">
-        <v>2025-07-22T05:30:00.000Z</v>
+        <v>2025-07-22T00:00:00.000Z</v>
       </c>
       <c r="C198" t="str">
         <v>Khan Retail</v>
@@ -6742,7 +6742,7 @@
         <v>SO-10198</v>
       </c>
       <c r="B199" s="1" t="d">
-        <v>2025-07-22T05:30:00.000Z</v>
+        <v>2025-07-22T00:00:00.000Z</v>
       </c>
       <c r="C199" t="str">
         <v>Pillai Traders</v>
@@ -6774,7 +6774,7 @@
         <v>SO-10199</v>
       </c>
       <c r="B200" s="1" t="d">
-        <v>2025-07-23T05:30:00.000Z</v>
+        <v>2025-07-23T00:00:00.000Z</v>
       </c>
       <c r="C200" t="str">
         <v>Sharma Traders</v>
@@ -6806,7 +6806,7 @@
         <v>SO-10200</v>
       </c>
       <c r="B201" s="1" t="d">
-        <v>2025-07-25T05:30:00.000Z</v>
+        <v>2025-07-25T00:00:00.000Z</v>
       </c>
       <c r="C201" t="str">
         <v>Patil Labs</v>
@@ -6838,7 +6838,7 @@
         <v>SO-10201</v>
       </c>
       <c r="B202" s="1" t="d">
-        <v>2025-07-25T05:30:00.000Z</v>
+        <v>2025-07-25T00:00:00.000Z</v>
       </c>
       <c r="C202" t="str">
         <v>Kulkarni Traders</v>
@@ -6870,7 +6870,7 @@
         <v>SO-10202</v>
       </c>
       <c r="B203" s="1" t="d">
-        <v>2025-07-27T05:30:00.000Z</v>
+        <v>2025-07-27T00:00:00.000Z</v>
       </c>
       <c r="C203" t="str">
         <v>Patil Retail</v>
@@ -6902,7 +6902,7 @@
         <v>SO-10203</v>
       </c>
       <c r="B204" s="1" t="d">
-        <v>2025-07-26T05:30:00.000Z</v>
+        <v>2025-07-26T00:00:00.000Z</v>
       </c>
       <c r="C204" t="str">
         <v>Patil Enterprises</v>
@@ -6934,7 +6934,7 @@
         <v>SO-10204</v>
       </c>
       <c r="B205" s="1" t="d">
-        <v>2025-07-28T05:30:00.000Z</v>
+        <v>2025-07-28T00:00:00.000Z</v>
       </c>
       <c r="C205" t="str">
         <v>Nair Labs</v>
@@ -6966,7 +6966,7 @@
         <v>SO-10205</v>
       </c>
       <c r="B206" s="1" t="d">
-        <v>2025-07-26T05:30:00.000Z</v>
+        <v>2025-07-26T00:00:00.000Z</v>
       </c>
       <c r="C206" t="str">
         <v>Desai Traders</v>
@@ -6998,7 +6998,7 @@
         <v>SO-10206</v>
       </c>
       <c r="B207" s="1" t="d">
-        <v>2025-07-29T05:30:00.000Z</v>
+        <v>2025-07-29T00:00:00.000Z</v>
       </c>
       <c r="C207" t="str">
         <v>Desai Stores</v>
@@ -7030,7 +7030,7 @@
         <v>SO-10207</v>
       </c>
       <c r="B208" s="1" t="d">
-        <v>2025-07-29T05:30:00.000Z</v>
+        <v>2025-07-29T00:00:00.000Z</v>
       </c>
       <c r="C208" t="str">
         <v>Pillai Retail</v>
@@ -7062,7 +7062,7 @@
         <v>SO-10208</v>
       </c>
       <c r="B209" s="1" t="d">
-        <v>2025-07-28T05:30:00.000Z</v>
+        <v>2025-07-28T00:00:00.000Z</v>
       </c>
       <c r="C209" t="str">
         <v>Joshi Traders</v>
@@ -7094,7 +7094,7 @@
         <v>SO-10209</v>
       </c>
       <c r="B210" s="1" t="d">
-        <v>2025-07-29T05:30:00.000Z</v>
+        <v>2025-07-29T00:00:00.000Z</v>
       </c>
       <c r="C210" t="str">
         <v>Joshi Labs</v>
@@ -7126,7 +7126,7 @@
         <v>SO-10210</v>
       </c>
       <c r="B211" s="1" t="d">
-        <v>2025-07-30T05:30:00.000Z</v>
+        <v>2025-07-30T00:00:00.000Z</v>
       </c>
       <c r="C211" t="str">
         <v>Sharma Labs</v>
@@ -7158,7 +7158,7 @@
         <v>SO-10211</v>
       </c>
       <c r="B212" s="1" t="d">
-        <v>2025-07-30T05:30:00.000Z</v>
+        <v>2025-07-30T00:00:00.000Z</v>
       </c>
       <c r="C212" t="str">
         <v>Patil Retail</v>
@@ -7190,7 +7190,7 @@
         <v>SO-10212</v>
       </c>
       <c r="B213" s="1" t="d">
-        <v>2025-08-01T05:30:00.000Z</v>
+        <v>2025-08-01T00:00:00.000Z</v>
       </c>
       <c r="C213" t="str">
         <v>Patil Traders</v>
@@ -7222,7 +7222,7 @@
         <v>SO-10213</v>
       </c>
       <c r="B214" s="1" t="d">
-        <v>2025-08-02T05:30:00.000Z</v>
+        <v>2025-08-02T00:00:00.000Z</v>
       </c>
       <c r="C214" t="str">
         <v>Patil Enterprises</v>
@@ -7254,7 +7254,7 @@
         <v>SO-10214</v>
       </c>
       <c r="B215" s="1" t="d">
-        <v>2025-07-31T05:30:00.000Z</v>
+        <v>2025-07-31T00:00:00.000Z</v>
       </c>
       <c r="C215" t="str">
         <v>Sharma Labs</v>
@@ -7286,7 +7286,7 @@
         <v>SO-10215</v>
       </c>
       <c r="B216" s="1" t="d">
-        <v>2025-08-02T05:30:00.000Z</v>
+        <v>2025-08-02T00:00:00.000Z</v>
       </c>
       <c r="C216" t="str">
         <v>Nair Solutions</v>
@@ -7318,7 +7318,7 @@
         <v>SO-10216</v>
       </c>
       <c r="B217" s="1" t="d">
-        <v>2025-08-02T05:30:00.000Z</v>
+        <v>2025-08-02T00:00:00.000Z</v>
       </c>
       <c r="C217" t="str">
         <v>Desai Traders</v>
@@ -7350,7 +7350,7 @@
         <v>SO-10217</v>
       </c>
       <c r="B218" s="1" t="d">
-        <v>2025-08-05T05:30:00.000Z</v>
+        <v>2025-08-05T00:00:00.000Z</v>
       </c>
       <c r="C218" t="str">
         <v>Gupta Enterprises</v>
@@ -7382,7 +7382,7 @@
         <v>SO-10218</v>
       </c>
       <c r="B219" s="1" t="d">
-        <v>2025-08-03T05:30:00.000Z</v>
+        <v>2025-08-03T00:00:00.000Z</v>
       </c>
       <c r="C219" t="str">
         <v>Kulkarni Labs</v>
@@ -7414,7 +7414,7 @@
         <v>SO-10219</v>
       </c>
       <c r="B220" s="1" t="d">
-        <v>2025-08-06T05:30:00.000Z</v>
+        <v>2025-08-06T00:00:00.000Z</v>
       </c>
       <c r="C220" t="str">
         <v>Mehta Stores</v>
@@ -7446,7 +7446,7 @@
         <v>SO-10220</v>
       </c>
       <c r="B221" s="1" t="d">
-        <v>2025-08-06T05:30:00.000Z</v>
+        <v>2025-08-06T00:00:00.000Z</v>
       </c>
       <c r="C221" t="str">
         <v>Nair Traders</v>
@@ -7478,7 +7478,7 @@
         <v>SO-10221</v>
       </c>
       <c r="B222" s="1" t="d">
-        <v>2025-08-06T05:30:00.000Z</v>
+        <v>2025-08-06T00:00:00.000Z</v>
       </c>
       <c r="C222" t="str">
         <v>Pillai Solutions</v>
@@ -7510,7 +7510,7 @@
         <v>SO-10222</v>
       </c>
       <c r="B223" s="1" t="d">
-        <v>2025-08-06T05:30:00.000Z</v>
+        <v>2025-08-06T00:00:00.000Z</v>
       </c>
       <c r="C223" t="str">
         <v>Iyer Traders</v>
@@ -7542,7 +7542,7 @@
         <v>SO-10223</v>
       </c>
       <c r="B224" s="1" t="d">
-        <v>2025-08-08T05:30:00.000Z</v>
+        <v>2025-08-08T00:00:00.000Z</v>
       </c>
       <c r="C224" t="str">
         <v>Patil Labs</v>
@@ -7574,7 +7574,7 @@
         <v>SO-10224</v>
       </c>
       <c r="B225" s="1" t="d">
-        <v>2025-08-06T05:30:00.000Z</v>
+        <v>2025-08-06T00:00:00.000Z</v>
       </c>
       <c r="C225" t="str">
         <v>Rao Retail</v>
@@ -7606,7 +7606,7 @@
         <v>SO-10225</v>
       </c>
       <c r="B226" s="1" t="d">
-        <v>2025-08-07T05:30:00.000Z</v>
+        <v>2025-08-07T00:00:00.000Z</v>
       </c>
       <c r="C226" t="str">
         <v>Iyer Stores</v>
@@ -7638,7 +7638,7 @@
         <v>SO-10226</v>
       </c>
       <c r="B227" s="1" t="d">
-        <v>2025-08-09T05:30:00.000Z</v>
+        <v>2025-08-09T00:00:00.000Z</v>
       </c>
       <c r="C227" t="str">
         <v>Pillai Enterprises</v>
@@ -7670,7 +7670,7 @@
         <v>SO-10227</v>
       </c>
       <c r="B228" s="1" t="d">
-        <v>2025-08-10T05:30:00.000Z</v>
+        <v>2025-08-10T00:00:00.000Z</v>
       </c>
       <c r="C228" t="str">
         <v>Rao Labs</v>
@@ -7702,7 +7702,7 @@
         <v>SO-10228</v>
       </c>
       <c r="B229" s="1" t="d">
-        <v>2025-08-11T05:30:00.000Z</v>
+        <v>2025-08-11T00:00:00.000Z</v>
       </c>
       <c r="C229" t="str">
         <v>Joshi Stores</v>
@@ -7734,7 +7734,7 @@
         <v>SO-10229</v>
       </c>
       <c r="B230" s="1" t="d">
-        <v>2025-08-11T05:30:00.000Z</v>
+        <v>2025-08-11T00:00:00.000Z</v>
       </c>
       <c r="C230" t="str">
         <v>Sharma Solutions</v>
@@ -7766,7 +7766,7 @@
         <v>SO-10230</v>
       </c>
       <c r="B231" s="1" t="d">
-        <v>2025-08-10T05:30:00.000Z</v>
+        <v>2025-08-10T00:00:00.000Z</v>
       </c>
       <c r="C231" t="str">
         <v>Patil Traders</v>
@@ -7798,7 +7798,7 @@
         <v>SO-10231</v>
       </c>
       <c r="B232" s="1" t="d">
-        <v>2025-08-12T05:30:00.000Z</v>
+        <v>2025-08-12T00:00:00.000Z</v>
       </c>
       <c r="C232" t="str">
         <v>Iyer Traders</v>
@@ -7830,7 +7830,7 @@
         <v>SO-10232</v>
       </c>
       <c r="B233" s="1" t="d">
-        <v>2025-08-10T05:30:00.000Z</v>
+        <v>2025-08-10T00:00:00.000Z</v>
       </c>
       <c r="C233" t="str">
         <v>Pillai Retail</v>
@@ -7862,7 +7862,7 @@
         <v>SO-10233</v>
       </c>
       <c r="B234" s="1" t="d">
-        <v>2025-08-11T05:30:00.000Z</v>
+        <v>2025-08-11T00:00:00.000Z</v>
       </c>
       <c r="C234" t="str">
         <v>Patil Enterprises</v>
@@ -7894,7 +7894,7 @@
         <v>SO-10234</v>
       </c>
       <c r="B235" s="1" t="d">
-        <v>2025-08-12T05:30:00.000Z</v>
+        <v>2025-08-12T00:00:00.000Z</v>
       </c>
       <c r="C235" t="str">
         <v>Pillai Traders</v>
@@ -7926,7 +7926,7 @@
         <v>SO-10235</v>
       </c>
       <c r="B236" s="1" t="d">
-        <v>2025-08-15T05:30:00.000Z</v>
+        <v>2025-08-15T00:00:00.000Z</v>
       </c>
       <c r="C236" t="str">
         <v>Patil Traders</v>
@@ -7958,7 +7958,7 @@
         <v>SO-10236</v>
       </c>
       <c r="B237" s="1" t="d">
-        <v>2025-08-14T05:30:00.000Z</v>
+        <v>2025-08-14T00:00:00.000Z</v>
       </c>
       <c r="C237" t="str">
         <v>Joshi Labs</v>
@@ -7990,7 +7990,7 @@
         <v>SO-10237</v>
       </c>
       <c r="B238" s="1" t="d">
-        <v>2025-08-14T05:30:00.000Z</v>
+        <v>2025-08-14T00:00:00.000Z</v>
       </c>
       <c r="C238" t="str">
         <v>Patil Stores</v>
@@ -8022,7 +8022,7 @@
         <v>SO-10238</v>
       </c>
       <c r="B239" s="1" t="d">
-        <v>2025-08-16T05:30:00.000Z</v>
+        <v>2025-08-16T00:00:00.000Z</v>
       </c>
       <c r="C239" t="str">
         <v>Joshi Stores</v>
@@ -8054,7 +8054,7 @@
         <v>SO-10239</v>
       </c>
       <c r="B240" s="1" t="d">
-        <v>2025-08-17T05:30:00.000Z</v>
+        <v>2025-08-17T00:00:00.000Z</v>
       </c>
       <c r="C240" t="str">
         <v>Joshi Retail</v>
@@ -8086,7 +8086,7 @@
         <v>SO-10240</v>
       </c>
       <c r="B241" s="1" t="d">
-        <v>2025-08-17T05:30:00.000Z</v>
+        <v>2025-08-17T00:00:00.000Z</v>
       </c>
       <c r="C241" t="str">
         <v>Gupta Enterprises</v>
@@ -8118,7 +8118,7 @@
         <v>SO-10241</v>
       </c>
       <c r="B242" s="1" t="d">
-        <v>2025-08-18T05:30:00.000Z</v>
+        <v>2025-08-18T00:00:00.000Z</v>
       </c>
       <c r="C242" t="str">
         <v>Nair Solutions</v>
@@ -8150,7 +8150,7 @@
         <v>SO-10242</v>
       </c>
       <c r="B243" s="1" t="d">
-        <v>2025-08-17T05:30:00.000Z</v>
+        <v>2025-08-17T00:00:00.000Z</v>
       </c>
       <c r="C243" t="str">
         <v>Pillai Retail</v>
@@ -8182,7 +8182,7 @@
         <v>SO-10243</v>
       </c>
       <c r="B244" s="1" t="d">
-        <v>2025-08-18T05:30:00.000Z</v>
+        <v>2025-08-18T00:00:00.000Z</v>
       </c>
       <c r="C244" t="str">
         <v>Pillai Retail</v>
@@ -8214,7 +8214,7 @@
         <v>SO-10244</v>
       </c>
       <c r="B245" s="1" t="d">
-        <v>2025-08-18T05:30:00.000Z</v>
+        <v>2025-08-18T00:00:00.000Z</v>
       </c>
       <c r="C245" t="str">
         <v>Gupta Stores</v>
@@ -8246,7 +8246,7 @@
         <v>SO-10245</v>
       </c>
       <c r="B246" s="1" t="d">
-        <v>2025-08-18T05:30:00.000Z</v>
+        <v>2025-08-18T00:00:00.000Z</v>
       </c>
       <c r="C246" t="str">
         <v>Kulkarni Enterprises</v>
@@ -8278,7 +8278,7 @@
         <v>SO-10246</v>
       </c>
       <c r="B247" s="1" t="d">
-        <v>2025-08-20T05:30:00.000Z</v>
+        <v>2025-08-20T00:00:00.000Z</v>
       </c>
       <c r="C247" t="str">
         <v>Kulkarni Enterprises</v>
@@ -8310,7 +8310,7 @@
         <v>SO-10247</v>
       </c>
       <c r="B248" s="1" t="d">
-        <v>2025-08-20T05:30:00.000Z</v>
+        <v>2025-08-20T00:00:00.000Z</v>
       </c>
       <c r="C248" t="str">
         <v>Kulkarni Stores</v>
@@ -8342,7 +8342,7 @@
         <v>SO-10248</v>
       </c>
       <c r="B249" s="1" t="d">
-        <v>2025-08-20T05:30:00.000Z</v>
+        <v>2025-08-20T00:00:00.000Z</v>
       </c>
       <c r="C249" t="str">
         <v>Patil Labs</v>
@@ -8374,7 +8374,7 @@
         <v>SO-10249</v>
       </c>
       <c r="B250" s="1" t="d">
-        <v>2025-08-20T05:30:00.000Z</v>
+        <v>2025-08-20T00:00:00.000Z</v>
       </c>
       <c r="C250" t="str">
         <v>Rao Enterprises</v>
@@ -8406,7 +8406,7 @@
         <v>SO-10250</v>
       </c>
       <c r="B251" s="1" t="d">
-        <v>2025-08-21T05:30:00.000Z</v>
+        <v>2025-08-21T00:00:00.000Z</v>
       </c>
       <c r="C251" t="str">
         <v>Sharma Solutions</v>
@@ -8438,7 +8438,7 @@
         <v>SO-10251</v>
       </c>
       <c r="B252" s="1" t="d">
-        <v>2025-08-23T05:30:00.000Z</v>
+        <v>2025-08-23T00:00:00.000Z</v>
       </c>
       <c r="C252" t="str">
         <v>Desai Labs</v>
@@ -8470,7 +8470,7 @@
         <v>SO-10252</v>
       </c>
       <c r="B253" s="1" t="d">
-        <v>2025-08-24T05:30:00.000Z</v>
+        <v>2025-08-24T00:00:00.000Z</v>
       </c>
       <c r="C253" t="str">
         <v>Sharma Solutions</v>
@@ -8502,7 +8502,7 @@
         <v>SO-10253</v>
       </c>
       <c r="B254" s="1" t="d">
-        <v>2025-08-23T05:30:00.000Z</v>
+        <v>2025-08-23T00:00:00.000Z</v>
       </c>
       <c r="C254" t="str">
         <v>Pillai Solutions</v>
@@ -8534,7 +8534,7 @@
         <v>SO-10254</v>
       </c>
       <c r="B255" s="1" t="d">
-        <v>2025-08-23T05:30:00.000Z</v>
+        <v>2025-08-23T00:00:00.000Z</v>
       </c>
       <c r="C255" t="str">
         <v>Pillai Stores</v>
@@ -8566,7 +8566,7 @@
         <v>SO-10255</v>
       </c>
       <c r="B256" s="1" t="d">
-        <v>2025-08-25T05:30:00.000Z</v>
+        <v>2025-08-25T00:00:00.000Z</v>
       </c>
       <c r="C256" t="str">
         <v>Kulkarni Labs</v>
@@ -8598,7 +8598,7 @@
         <v>SO-10256</v>
       </c>
       <c r="B257" s="1" t="d">
-        <v>2025-08-24T05:30:00.000Z</v>
+        <v>2025-08-24T00:00:00.000Z</v>
       </c>
       <c r="C257" t="str">
         <v>Pillai Retail</v>
@@ -8630,7 +8630,7 @@
         <v>SO-10257</v>
       </c>
       <c r="B258" s="1" t="d">
-        <v>2025-08-26T05:30:00.000Z</v>
+        <v>2025-08-26T00:00:00.000Z</v>
       </c>
       <c r="C258" t="str">
         <v>Kulkarni Stores</v>
@@ -8662,7 +8662,7 @@
         <v>SO-10258</v>
       </c>
       <c r="B259" s="1" t="d">
-        <v>2025-08-25T05:30:00.000Z</v>
+        <v>2025-08-25T00:00:00.000Z</v>
       </c>
       <c r="C259" t="str">
         <v>Pillai Stores</v>
@@ -8694,7 +8694,7 @@
         <v>SO-10259</v>
       </c>
       <c r="B260" s="1" t="d">
-        <v>2025-08-28T05:30:00.000Z</v>
+        <v>2025-08-28T00:00:00.000Z</v>
       </c>
       <c r="C260" t="str">
         <v>Patil Enterprises</v>
@@ -8726,7 +8726,7 @@
         <v>SO-10260</v>
       </c>
       <c r="B261" s="1" t="d">
-        <v>2025-08-28T05:30:00.000Z</v>
+        <v>2025-08-28T00:00:00.000Z</v>
       </c>
       <c r="C261" t="str">
         <v>Rao Stores</v>
@@ -8758,7 +8758,7 @@
         <v>SO-10261</v>
       </c>
       <c r="B262" s="1" t="d">
-        <v>2025-08-27T05:30:00.000Z</v>
+        <v>2025-08-27T00:00:00.000Z</v>
       </c>
       <c r="C262" t="str">
         <v>Khan Retail</v>
@@ -8790,7 +8790,7 @@
         <v>SO-10262</v>
       </c>
       <c r="B263" s="1" t="d">
-        <v>2025-08-29T05:30:00.000Z</v>
+        <v>2025-08-29T00:00:00.000Z</v>
       </c>
       <c r="C263" t="str">
         <v>Patil Retail</v>
@@ -8822,7 +8822,7 @@
         <v>SO-10263</v>
       </c>
       <c r="B264" s="1" t="d">
-        <v>2025-08-30T05:30:00.000Z</v>
+        <v>2025-08-30T00:00:00.000Z</v>
       </c>
       <c r="C264" t="str">
         <v>Rao Solutions</v>
@@ -8854,7 +8854,7 @@
         <v>SO-10264</v>
       </c>
       <c r="B265" s="1" t="d">
-        <v>2025-08-31T05:30:00.000Z</v>
+        <v>2025-08-31T00:00:00.000Z</v>
       </c>
       <c r="C265" t="str">
         <v>Pillai Enterprises</v>
@@ -8886,7 +8886,7 @@
         <v>SO-10265</v>
       </c>
       <c r="B266" s="1" t="d">
-        <v>2025-09-01T05:30:00.000Z</v>
+        <v>2025-09-01T00:00:00.000Z</v>
       </c>
       <c r="C266" t="str">
         <v>Pillai Labs</v>
@@ -8918,7 +8918,7 @@
         <v>SO-10266</v>
       </c>
       <c r="B267" s="1" t="d">
-        <v>2025-08-31T05:30:00.000Z</v>
+        <v>2025-08-31T00:00:00.000Z</v>
       </c>
       <c r="C267" t="str">
         <v>Joshi Solutions</v>
@@ -8950,7 +8950,7 @@
         <v>SO-10267</v>
       </c>
       <c r="B268" s="1" t="d">
-        <v>2025-08-31T05:30:00.000Z</v>
+        <v>2025-08-31T00:00:00.000Z</v>
       </c>
       <c r="C268" t="str">
         <v>Sharma Enterprises</v>
@@ -8982,7 +8982,7 @@
         <v>SO-10268</v>
       </c>
       <c r="B269" s="1" t="d">
-        <v>2025-09-03T05:30:00.000Z</v>
+        <v>2025-09-03T00:00:00.000Z</v>
       </c>
       <c r="C269" t="str">
         <v>Sharma Traders</v>
@@ -9014,7 +9014,7 @@
         <v>SO-10269</v>
       </c>
       <c r="B270" s="1" t="d">
-        <v>2025-09-01T05:30:00.000Z</v>
+        <v>2025-09-01T00:00:00.000Z</v>
       </c>
       <c r="C270" t="str">
         <v>Patil Solutions</v>
@@ -9046,7 +9046,7 @@
         <v>SO-10270</v>
       </c>
       <c r="B271" s="1" t="d">
-        <v>2025-09-01T05:30:00.000Z</v>
+        <v>2025-09-01T00:00:00.000Z</v>
       </c>
       <c r="C271" t="str">
         <v>Desai Stores</v>
@@ -9078,7 +9078,7 @@
         <v>SO-10271</v>
       </c>
       <c r="B272" s="1" t="d">
-        <v>2025-09-02T05:30:00.000Z</v>
+        <v>2025-09-02T00:00:00.000Z</v>
       </c>
       <c r="C272" t="str">
         <v>Joshi Traders</v>
@@ -9110,7 +9110,7 @@
         <v>SO-10272</v>
       </c>
       <c r="B273" s="1" t="d">
-        <v>2025-09-05T05:30:00.000Z</v>
+        <v>2025-09-05T00:00:00.000Z</v>
       </c>
       <c r="C273" t="str">
         <v>Mehta Traders</v>
@@ -9142,7 +9142,7 @@
         <v>SO-10273</v>
       </c>
       <c r="B274" s="1" t="d">
-        <v>2025-09-06T05:30:00.000Z</v>
+        <v>2025-09-06T00:00:00.000Z</v>
       </c>
       <c r="C274" t="str">
         <v>Kulkarni Stores</v>
@@ -9174,7 +9174,7 @@
         <v>SO-10274</v>
       </c>
       <c r="B275" s="1" t="d">
-        <v>2025-09-05T05:30:00.000Z</v>
+        <v>2025-09-05T00:00:00.000Z</v>
       </c>
       <c r="C275" t="str">
         <v>Pillai Stores</v>
@@ -9206,7 +9206,7 @@
         <v>SO-10275</v>
       </c>
       <c r="B276" s="1" t="d">
-        <v>2025-09-04T05:30:00.000Z</v>
+        <v>2025-09-04T00:00:00.000Z</v>
       </c>
       <c r="C276" t="str">
         <v>Patil Retail</v>
@@ -9238,7 +9238,7 @@
         <v>SO-10276</v>
       </c>
       <c r="B277" s="1" t="d">
-        <v>2025-09-07T05:30:00.000Z</v>
+        <v>2025-09-07T00:00:00.000Z</v>
       </c>
       <c r="C277" t="str">
         <v>Kulkarni Traders</v>
@@ -9270,7 +9270,7 @@
         <v>SO-10277</v>
       </c>
       <c r="B278" s="1" t="d">
-        <v>2025-09-07T05:30:00.000Z</v>
+        <v>2025-09-07T00:00:00.000Z</v>
       </c>
       <c r="C278" t="str">
         <v>Patil Retail</v>
@@ -9302,7 +9302,7 @@
         <v>SO-10278</v>
       </c>
       <c r="B279" s="1" t="d">
-        <v>2025-09-06T05:30:00.000Z</v>
+        <v>2025-09-06T00:00:00.000Z</v>
       </c>
       <c r="C279" t="str">
         <v>Patil Retail</v>
@@ -9334,7 +9334,7 @@
         <v>SO-10279</v>
       </c>
       <c r="B280" s="1" t="d">
-        <v>2025-09-06T05:30:00.000Z</v>
+        <v>2025-09-06T00:00:00.000Z</v>
       </c>
       <c r="C280" t="str">
         <v>Sharma Labs</v>
@@ -9366,7 +9366,7 @@
         <v>SO-10280</v>
       </c>
       <c r="B281" s="1" t="d">
-        <v>2025-09-08T05:30:00.000Z</v>
+        <v>2025-09-08T00:00:00.000Z</v>
       </c>
       <c r="C281" t="str">
         <v>Nair Enterprises</v>
@@ -9398,7 +9398,7 @@
         <v>SO-10281</v>
       </c>
       <c r="B282" s="1" t="d">
-        <v>2025-09-08T05:30:00.000Z</v>
+        <v>2025-09-08T00:00:00.000Z</v>
       </c>
       <c r="C282" t="str">
         <v>Kulkarni Retail</v>
@@ -9430,7 +9430,7 @@
         <v>SO-10282</v>
       </c>
       <c r="B283" s="1" t="d">
-        <v>2025-09-09T05:30:00.000Z</v>
+        <v>2025-09-09T00:00:00.000Z</v>
       </c>
       <c r="C283" t="str">
         <v>Sharma Enterprises</v>
@@ -9462,7 +9462,7 @@
         <v>SO-10283</v>
       </c>
       <c r="B284" s="1" t="d">
-        <v>2025-09-10T05:30:00.000Z</v>
+        <v>2025-09-10T00:00:00.000Z</v>
       </c>
       <c r="C284" t="str">
         <v>Iyer Enterprises</v>
@@ -9494,7 +9494,7 @@
         <v>SO-10284</v>
       </c>
       <c r="B285" s="1" t="d">
-        <v>2025-09-09T05:30:00.000Z</v>
+        <v>2025-09-09T00:00:00.000Z</v>
       </c>
       <c r="C285" t="str">
         <v>Iyer Labs</v>
@@ -9526,7 +9526,7 @@
         <v>SO-10285</v>
       </c>
       <c r="B286" s="1" t="d">
-        <v>2025-09-11T05:30:00.000Z</v>
+        <v>2025-09-11T00:00:00.000Z</v>
       </c>
       <c r="C286" t="str">
         <v>Patil Stores</v>
@@ -9558,7 +9558,7 @@
         <v>SO-10286</v>
       </c>
       <c r="B287" s="1" t="d">
-        <v>2025-09-10T05:30:00.000Z</v>
+        <v>2025-09-10T00:00:00.000Z</v>
       </c>
       <c r="C287" t="str">
         <v>Patil Enterprises</v>
@@ -9590,7 +9590,7 @@
         <v>SO-10287</v>
       </c>
       <c r="B288" s="1" t="d">
-        <v>2025-09-12T05:30:00.000Z</v>
+        <v>2025-09-12T00:00:00.000Z</v>
       </c>
       <c r="C288" t="str">
         <v>Nair Enterprises</v>
@@ -9622,7 +9622,7 @@
         <v>SO-10288</v>
       </c>
       <c r="B289" s="1" t="d">
-        <v>2025-09-12T05:30:00.000Z</v>
+        <v>2025-09-12T00:00:00.000Z</v>
       </c>
       <c r="C289" t="str">
         <v>Sharma Enterprises</v>
@@ -9654,7 +9654,7 @@
         <v>SO-10289</v>
       </c>
       <c r="B290" s="1" t="d">
-        <v>2025-09-15T05:30:00.000Z</v>
+        <v>2025-09-15T00:00:00.000Z</v>
       </c>
       <c r="C290" t="str">
         <v>Nair Labs</v>
@@ -9686,7 +9686,7 @@
         <v>SO-10290</v>
       </c>
       <c r="B291" s="1" t="d">
-        <v>2025-09-14T05:30:00.000Z</v>
+        <v>2025-09-14T00:00:00.000Z</v>
       </c>
       <c r="C291" t="str">
         <v>Sharma Retail</v>
@@ -9718,7 +9718,7 @@
         <v>SO-10291</v>
       </c>
       <c r="B292" s="1" t="d">
-        <v>2025-09-14T05:30:00.000Z</v>
+        <v>2025-09-14T00:00:00.000Z</v>
       </c>
       <c r="C292" t="str">
         <v>Nair Solutions</v>
@@ -9750,7 +9750,7 @@
         <v>SO-10292</v>
       </c>
       <c r="B293" s="1" t="d">
-        <v>2025-09-16T05:30:00.000Z</v>
+        <v>2025-09-16T00:00:00.000Z</v>
       </c>
       <c r="C293" t="str">
         <v>Iyer Retail</v>
@@ -9782,7 +9782,7 @@
         <v>SO-10293</v>
       </c>
       <c r="B294" s="1" t="d">
-        <v>2025-09-15T05:30:00.000Z</v>
+        <v>2025-09-15T00:00:00.000Z</v>
       </c>
       <c r="C294" t="str">
         <v>Joshi Retail</v>
@@ -9814,7 +9814,7 @@
         <v>SO-10294</v>
       </c>
       <c r="B295" s="1" t="d">
-        <v>2025-09-18T05:30:00.000Z</v>
+        <v>2025-09-18T00:00:00.000Z</v>
       </c>
       <c r="C295" t="str">
         <v>Patil Stores</v>
@@ -9846,7 +9846,7 @@
         <v>SO-10295</v>
       </c>
       <c r="B296" s="1" t="d">
-        <v>2025-09-17T05:30:00.000Z</v>
+        <v>2025-09-17T00:00:00.000Z</v>
       </c>
       <c r="C296" t="str">
         <v>Rao Stores</v>
@@ -9878,7 +9878,7 @@
         <v>SO-10296</v>
       </c>
       <c r="B297" s="1" t="d">
-        <v>2025-09-17T05:30:00.000Z</v>
+        <v>2025-09-17T00:00:00.000Z</v>
       </c>
       <c r="C297" t="str">
         <v>Sharma Solutions</v>
@@ -9910,7 +9910,7 @@
         <v>SO-10297</v>
       </c>
       <c r="B298" s="1" t="d">
-        <v>2025-09-18T05:30:00.000Z</v>
+        <v>2025-09-18T00:00:00.000Z</v>
       </c>
       <c r="C298" t="str">
         <v>Mehta Enterprises</v>
@@ -9942,7 +9942,7 @@
         <v>SO-10298</v>
       </c>
       <c r="B299" s="1" t="d">
-        <v>2025-09-19T05:30:00.000Z</v>
+        <v>2025-09-19T00:00:00.000Z</v>
       </c>
       <c r="C299" t="str">
         <v>Pillai Retail</v>
@@ -9974,7 +9974,7 @@
         <v>SO-10299</v>
       </c>
       <c r="B300" s="1" t="d">
-        <v>2025-09-18T05:30:00.000Z</v>
+        <v>2025-09-18T00:00:00.000Z</v>
       </c>
       <c r="C300" t="str">
         <v>Joshi Retail</v>
@@ -10006,7 +10006,7 @@
         <v>SO-10300</v>
       </c>
       <c r="B301" s="1" t="d">
-        <v>2025-09-20T05:30:00.000Z</v>
+        <v>2025-09-20T00:00:00.000Z</v>
       </c>
       <c r="C301" t="str">
         <v>Patil Retail</v>
@@ -10038,7 +10038,7 @@
         <v>SO-10301</v>
       </c>
       <c r="B302" s="1" t="d">
-        <v>2025-09-19T05:30:00.000Z</v>
+        <v>2025-09-19T00:00:00.000Z</v>
       </c>
       <c r="C302" t="str">
         <v>Desai Solutions</v>
@@ -10070,7 +10070,7 @@
         <v>SO-10302</v>
       </c>
       <c r="B303" s="1" t="d">
-        <v>2025-09-21T05:30:00.000Z</v>
+        <v>2025-09-21T00:00:00.000Z</v>
       </c>
       <c r="C303" t="str">
         <v>Kulkarni Traders</v>
@@ -10102,7 +10102,7 @@
         <v>SO-10303</v>
       </c>
       <c r="B304" s="1" t="d">
-        <v>2025-09-20T05:30:00.000Z</v>
+        <v>2025-09-20T00:00:00.000Z</v>
       </c>
       <c r="C304" t="str">
         <v>Sharma Retail</v>
@@ -10134,7 +10134,7 @@
         <v>SO-10304</v>
       </c>
       <c r="B305" s="1" t="d">
-        <v>2025-09-22T05:30:00.000Z</v>
+        <v>2025-09-22T00:00:00.000Z</v>
       </c>
       <c r="C305" t="str">
         <v>Rao Stores</v>
@@ -10166,7 +10166,7 @@
         <v>SO-10305</v>
       </c>
       <c r="B306" s="1" t="d">
-        <v>2025-09-22T05:30:00.000Z</v>
+        <v>2025-09-22T00:00:00.000Z</v>
       </c>
       <c r="C306" t="str">
         <v>Pillai Solutions</v>
@@ -10198,7 +10198,7 @@
         <v>SO-10306</v>
       </c>
       <c r="B307" s="1" t="d">
-        <v>2025-09-24T05:30:00.000Z</v>
+        <v>2025-09-24T00:00:00.000Z</v>
       </c>
       <c r="C307" t="str">
         <v>Rao Labs</v>
@@ -10230,7 +10230,7 @@
         <v>SO-10307</v>
       </c>
       <c r="B308" s="1" t="d">
-        <v>2025-09-23T05:30:00.000Z</v>
+        <v>2025-09-23T00:00:00.000Z</v>
       </c>
       <c r="C308" t="str">
         <v>Kulkarni Traders</v>
@@ -10262,7 +10262,7 @@
         <v>SO-10308</v>
       </c>
       <c r="B309" s="1" t="d">
-        <v>2025-09-25T05:30:00.000Z</v>
+        <v>2025-09-25T00:00:00.000Z</v>
       </c>
       <c r="C309" t="str">
         <v>Rao Traders</v>
@@ -10294,7 +10294,7 @@
         <v>SO-10309</v>
       </c>
       <c r="B310" s="1" t="d">
-        <v>2025-09-25T05:30:00.000Z</v>
+        <v>2025-09-25T00:00:00.000Z</v>
       </c>
       <c r="C310" t="str">
         <v>Nair Labs</v>
@@ -10326,7 +10326,7 @@
         <v>SO-10310</v>
       </c>
       <c r="B311" s="1" t="d">
-        <v>2025-09-24T05:30:00.000Z</v>
+        <v>2025-09-24T00:00:00.000Z</v>
       </c>
       <c r="C311" t="str">
         <v>Kulkarni Traders</v>
@@ -10358,7 +10358,7 @@
         <v>SO-10311</v>
       </c>
       <c r="B312" s="1" t="d">
-        <v>2025-09-26T05:30:00.000Z</v>
+        <v>2025-09-26T00:00:00.000Z</v>
       </c>
       <c r="C312" t="str">
         <v>Pillai Retail</v>
@@ -10390,7 +10390,7 @@
         <v>SO-10312</v>
       </c>
       <c r="B313" s="1" t="d">
-        <v>2025-09-27T05:30:00.000Z</v>
+        <v>2025-09-27T00:00:00.000Z</v>
       </c>
       <c r="C313" t="str">
         <v>Mehta Traders</v>
@@ -10422,7 +10422,7 @@
         <v>SO-10313</v>
       </c>
       <c r="B314" s="1" t="d">
-        <v>2025-09-27T05:30:00.000Z</v>
+        <v>2025-09-27T00:00:00.000Z</v>
       </c>
       <c r="C314" t="str">
         <v>Rao Enterprises</v>
@@ -10454,7 +10454,7 @@
         <v>SO-10314</v>
       </c>
       <c r="B315" s="1" t="d">
-        <v>2025-09-27T05:30:00.000Z</v>
+        <v>2025-09-27T00:00:00.000Z</v>
       </c>
       <c r="C315" t="str">
         <v>Patil Stores</v>
@@ -10486,7 +10486,7 @@
         <v>SO-10315</v>
       </c>
       <c r="B316" s="1" t="d">
-        <v>2025-09-29T05:30:00.000Z</v>
+        <v>2025-09-29T00:00:00.000Z</v>
       </c>
       <c r="C316" t="str">
         <v>Gupta Stores</v>
@@ -10518,7 +10518,7 @@
         <v>SO-10316</v>
       </c>
       <c r="B317" s="1" t="d">
-        <v>2025-09-27T05:30:00.000Z</v>
+        <v>2025-09-27T00:00:00.000Z</v>
       </c>
       <c r="C317" t="str">
         <v>Rao Solutions</v>
@@ -10550,7 +10550,7 @@
         <v>SO-10317</v>
       </c>
       <c r="B318" s="1" t="d">
-        <v>2025-09-28T05:30:00.000Z</v>
+        <v>2025-09-28T00:00:00.000Z</v>
       </c>
       <c r="C318" t="str">
         <v>Patil Traders</v>
@@ -10582,7 +10582,7 @@
         <v>SO-10318</v>
       </c>
       <c r="B319" s="1" t="d">
-        <v>2025-09-29T05:30:00.000Z</v>
+        <v>2025-09-29T00:00:00.000Z</v>
       </c>
       <c r="C319" t="str">
         <v>Desai Enterprises</v>
@@ -10614,7 +10614,7 @@
         <v>SO-10319</v>
       </c>
       <c r="B320" s="1" t="d">
-        <v>2025-09-29T05:30:00.000Z</v>
+        <v>2025-09-29T00:00:00.000Z</v>
       </c>
       <c r="C320" t="str">
         <v>Sharma Retail</v>
@@ -10646,7 +10646,7 @@
         <v>SO-10320</v>
       </c>
       <c r="B321" s="1" t="d">
-        <v>2025-10-01T05:30:00.000Z</v>
+        <v>2025-10-01T00:00:00.000Z</v>
       </c>
       <c r="C321" t="str">
         <v>Sharma Enterprises</v>
@@ -10678,7 +10678,7 @@
         <v>SO-10321</v>
       </c>
       <c r="B322" s="1" t="d">
-        <v>2025-10-01T05:30:00.000Z</v>
+        <v>2025-10-01T00:00:00.000Z</v>
       </c>
       <c r="C322" t="str">
         <v>Joshi Stores</v>
@@ -10710,7 +10710,7 @@
         <v>SO-10322</v>
       </c>
       <c r="B323" s="1" t="d">
-        <v>2025-10-02T05:30:00.000Z</v>
+        <v>2025-10-02T00:00:00.000Z</v>
       </c>
       <c r="C323" t="str">
         <v>Iyer Traders</v>
@@ -10742,7 +10742,7 @@
         <v>SO-10323</v>
       </c>
       <c r="B324" s="1" t="d">
-        <v>2025-10-02T05:30:00.000Z</v>
+        <v>2025-10-02T00:00:00.000Z</v>
       </c>
       <c r="C324" t="str">
         <v>Pillai Labs</v>
@@ -10774,7 +10774,7 @@
         <v>SO-10324</v>
       </c>
       <c r="B325" s="1" t="d">
-        <v>2025-10-05T05:30:00.000Z</v>
+        <v>2025-10-05T00:00:00.000Z</v>
       </c>
       <c r="C325" t="str">
         <v>Pillai Retail</v>
@@ -10806,7 +10806,7 @@
         <v>SO-10325</v>
       </c>
       <c r="B326" s="1" t="d">
-        <v>2025-10-05T05:30:00.000Z</v>
+        <v>2025-10-05T00:00:00.000Z</v>
       </c>
       <c r="C326" t="str">
         <v>Iyer Labs</v>
@@ -10838,7 +10838,7 @@
         <v>SO-10326</v>
       </c>
       <c r="B327" s="1" t="d">
-        <v>2025-10-04T05:30:00.000Z</v>
+        <v>2025-10-04T00:00:00.000Z</v>
       </c>
       <c r="C327" t="str">
         <v>Sharma Enterprises</v>
@@ -10870,7 +10870,7 @@
         <v>SO-10327</v>
       </c>
       <c r="B328" s="1" t="d">
-        <v>2025-10-04T05:30:00.000Z</v>
+        <v>2025-10-04T00:00:00.000Z</v>
       </c>
       <c r="C328" t="str">
         <v>Patil Stores</v>
@@ -10902,7 +10902,7 @@
         <v>SO-10328</v>
       </c>
       <c r="B329" s="1" t="d">
-        <v>2025-10-05T05:30:00.000Z</v>
+        <v>2025-10-05T00:00:00.000Z</v>
       </c>
       <c r="C329" t="str">
         <v>Kulkarni Traders</v>
@@ -10934,7 +10934,7 @@
         <v>SO-10329</v>
       </c>
       <c r="B330" s="1" t="d">
-        <v>2025-10-05T05:30:00.000Z</v>
+        <v>2025-10-05T00:00:00.000Z</v>
       </c>
       <c r="C330" t="str">
         <v>Iyer Retail</v>
@@ -10966,7 +10966,7 @@
         <v>SO-10330</v>
       </c>
       <c r="B331" s="1" t="d">
-        <v>2025-10-05T05:30:00.000Z</v>
+        <v>2025-10-05T00:00:00.000Z</v>
       </c>
       <c r="C331" t="str">
         <v>Rao Labs</v>
@@ -10998,7 +10998,7 @@
         <v>SO-10331</v>
       </c>
       <c r="B332" s="1" t="d">
-        <v>2025-10-08T05:30:00.000Z</v>
+        <v>2025-10-08T00:00:00.000Z</v>
       </c>
       <c r="C332" t="str">
         <v>Rao Stores</v>
@@ -11030,7 +11030,7 @@
         <v>SO-10332</v>
       </c>
       <c r="B333" s="1" t="d">
-        <v>2025-10-07T05:30:00.000Z</v>
+        <v>2025-10-07T00:00:00.000Z</v>
       </c>
       <c r="C333" t="str">
         <v>Kulkarni Traders</v>
@@ -11062,7 +11062,7 @@
         <v>SO-10333</v>
       </c>
       <c r="B334" s="1" t="d">
-        <v>2025-10-10T05:30:00.000Z</v>
+        <v>2025-10-10T00:00:00.000Z</v>
       </c>
       <c r="C334" t="str">
         <v>Patil Traders</v>
@@ -11094,7 +11094,7 @@
         <v>SO-10334</v>
       </c>
       <c r="B335" s="1" t="d">
-        <v>2025-10-09T05:30:00.000Z</v>
+        <v>2025-10-09T00:00:00.000Z</v>
       </c>
       <c r="C335" t="str">
         <v>Gupta Enterprises</v>
@@ -11126,7 +11126,7 @@
         <v>SO-10335</v>
       </c>
       <c r="B336" s="1" t="d">
-        <v>2025-10-08T05:30:00.000Z</v>
+        <v>2025-10-08T00:00:00.000Z</v>
       </c>
       <c r="C336" t="str">
         <v>Patil Labs</v>
@@ -11158,7 +11158,7 @@
         <v>SO-10336</v>
       </c>
       <c r="B337" s="1" t="d">
-        <v>2025-10-11T05:30:00.000Z</v>
+        <v>2025-10-11T00:00:00.000Z</v>
       </c>
       <c r="C337" t="str">
         <v>Pillai Traders</v>
@@ -11190,7 +11190,7 @@
         <v>SO-10337</v>
       </c>
       <c r="B338" s="1" t="d">
-        <v>2025-10-10T05:30:00.000Z</v>
+        <v>2025-10-10T00:00:00.000Z</v>
       </c>
       <c r="C338" t="str">
         <v>Rao Enterprises</v>
@@ -11222,7 +11222,7 @@
         <v>SO-10338</v>
       </c>
       <c r="B339" s="1" t="d">
-        <v>2025-10-10T05:30:00.000Z</v>
+        <v>2025-10-10T00:00:00.000Z</v>
       </c>
       <c r="C339" t="str">
         <v>Kulkarni Enterprises</v>
@@ -11254,7 +11254,7 @@
         <v>SO-10339</v>
       </c>
       <c r="B340" s="1" t="d">
-        <v>2025-10-12T05:30:00.000Z</v>
+        <v>2025-10-12T00:00:00.000Z</v>
       </c>
       <c r="C340" t="str">
         <v>Patil Retail</v>
@@ -11286,7 +11286,7 @@
         <v>SO-10340</v>
       </c>
       <c r="B341" s="1" t="d">
-        <v>2025-10-14T05:30:00.000Z</v>
+        <v>2025-10-14T00:00:00.000Z</v>
       </c>
       <c r="C341" t="str">
         <v>Patil Labs</v>
@@ -11318,7 +11318,7 @@
         <v>SO-10341</v>
       </c>
       <c r="B342" s="1" t="d">
-        <v>2025-10-12T05:30:00.000Z</v>
+        <v>2025-10-12T00:00:00.000Z</v>
       </c>
       <c r="C342" t="str">
         <v>Joshi Stores</v>
@@ -11350,7 +11350,7 @@
         <v>SO-10342</v>
       </c>
       <c r="B343" s="1" t="d">
-        <v>2025-10-13T05:30:00.000Z</v>
+        <v>2025-10-13T00:00:00.000Z</v>
       </c>
       <c r="C343" t="str">
         <v>Mehta Retail</v>
@@ -11382,7 +11382,7 @@
         <v>SO-10343</v>
       </c>
       <c r="B344" s="1" t="d">
-        <v>2025-10-14T05:30:00.000Z</v>
+        <v>2025-10-14T00:00:00.000Z</v>
       </c>
       <c r="C344" t="str">
         <v>Pillai Stores</v>
@@ -11414,7 +11414,7 @@
         <v>SO-10344</v>
       </c>
       <c r="B345" s="1" t="d">
-        <v>2025-10-14T05:30:00.000Z</v>
+        <v>2025-10-14T00:00:00.000Z</v>
       </c>
       <c r="C345" t="str">
         <v>Pillai Retail</v>
@@ -11446,7 +11446,7 @@
         <v>SO-10345</v>
       </c>
       <c r="B346" s="1" t="d">
-        <v>2025-10-15T05:30:00.000Z</v>
+        <v>2025-10-15T00:00:00.000Z</v>
       </c>
       <c r="C346" t="str">
         <v>Kulkarni Enterprises</v>
@@ -11478,7 +11478,7 @@
         <v>SO-10346</v>
       </c>
       <c r="B347" s="1" t="d">
-        <v>2025-10-16T05:30:00.000Z</v>
+        <v>2025-10-16T00:00:00.000Z</v>
       </c>
       <c r="C347" t="str">
         <v>Rao Traders</v>
@@ -11510,7 +11510,7 @@
         <v>SO-10347</v>
       </c>
       <c r="B348" s="1" t="d">
-        <v>2025-10-15T05:30:00.000Z</v>
+        <v>2025-10-15T00:00:00.000Z</v>
       </c>
       <c r="C348" t="str">
         <v>Sharma Retail</v>
@@ -11542,7 +11542,7 @@
         <v>SO-10348</v>
       </c>
       <c r="B349" s="1" t="d">
-        <v>2025-10-17T05:30:00.000Z</v>
+        <v>2025-10-17T00:00:00.000Z</v>
       </c>
       <c r="C349" t="str">
         <v>Gupta Enterprises</v>
@@ -11574,7 +11574,7 @@
         <v>SO-10349</v>
       </c>
       <c r="B350" s="1" t="d">
-        <v>2025-10-17T05:30:00.000Z</v>
+        <v>2025-10-17T00:00:00.000Z</v>
       </c>
       <c r="C350" t="str">
         <v>Khan Stores</v>
@@ -11606,7 +11606,7 @@
         <v>SO-10350</v>
       </c>
       <c r="B351" s="1" t="d">
-        <v>2025-10-19T05:30:00.000Z</v>
+        <v>2025-10-19T00:00:00.000Z</v>
       </c>
       <c r="C351" t="str">
         <v>Joshi Solutions</v>
@@ -11638,7 +11638,7 @@
         <v>SO-10351</v>
       </c>
       <c r="B352" s="1" t="d">
-        <v>2025-10-18T05:30:00.000Z</v>
+        <v>2025-10-18T00:00:00.000Z</v>
       </c>
       <c r="C352" t="str">
         <v>Khan Solutions</v>
@@ -11670,7 +11670,7 @@
         <v>SO-10352</v>
       </c>
       <c r="B353" s="1" t="d">
-        <v>2025-10-18T05:30:00.000Z</v>
+        <v>2025-10-18T00:00:00.000Z</v>
       </c>
       <c r="C353" t="str">
         <v>Mehta Traders</v>
@@ -11702,7 +11702,7 @@
         <v>SO-10353</v>
       </c>
       <c r="B354" s="1" t="d">
-        <v>2025-10-18T05:30:00.000Z</v>
+        <v>2025-10-18T00:00:00.000Z</v>
       </c>
       <c r="C354" t="str">
         <v>Mehta Stores</v>
@@ -11734,7 +11734,7 @@
         <v>SO-10354</v>
       </c>
       <c r="B355" s="1" t="d">
-        <v>2025-10-21T05:30:00.000Z</v>
+        <v>2025-10-21T00:00:00.000Z</v>
       </c>
       <c r="C355" t="str">
         <v>Rao Labs</v>
@@ -11766,7 +11766,7 @@
         <v>SO-10355</v>
       </c>
       <c r="B356" s="1" t="d">
-        <v>2025-10-20T05:30:00.000Z</v>
+        <v>2025-10-20T00:00:00.000Z</v>
       </c>
       <c r="C356" t="str">
         <v>Sharma Enterprises</v>
@@ -11798,7 +11798,7 @@
         <v>SO-10356</v>
       </c>
       <c r="B357" s="1" t="d">
-        <v>2025-10-20T05:30:00.000Z</v>
+        <v>2025-10-20T00:00:00.000Z</v>
       </c>
       <c r="C357" t="str">
         <v>Rao Labs</v>
@@ -11830,7 +11830,7 @@
         <v>SO-10357</v>
       </c>
       <c r="B358" s="1" t="d">
-        <v>2025-10-22T05:30:00.000Z</v>
+        <v>2025-10-22T00:00:00.000Z</v>
       </c>
       <c r="C358" t="str">
         <v>Khan Enterprises</v>
@@ -11862,7 +11862,7 @@
         <v>SO-10358</v>
       </c>
       <c r="B359" s="1" t="d">
-        <v>2025-10-22T05:30:00.000Z</v>
+        <v>2025-10-22T00:00:00.000Z</v>
       </c>
       <c r="C359" t="str">
         <v>Nair Stores</v>
@@ -11894,7 +11894,7 @@
         <v>SO-10359</v>
       </c>
       <c r="B360" s="1" t="d">
-        <v>2025-10-24T05:30:00.000Z</v>
+        <v>2025-10-24T00:00:00.000Z</v>
       </c>
       <c r="C360" t="str">
         <v>Rao Labs</v>
@@ -11926,7 +11926,7 @@
         <v>SO-10360</v>
       </c>
       <c r="B361" s="1" t="d">
-        <v>2025-10-24T05:30:00.000Z</v>
+        <v>2025-10-24T00:00:00.000Z</v>
       </c>
       <c r="C361" t="str">
         <v>Pillai Retail</v>
@@ -11958,7 +11958,7 @@
         <v>SO-10361</v>
       </c>
       <c r="B362" s="1" t="d">
-        <v>2025-10-26T05:30:00.000Z</v>
+        <v>2025-10-26T00:00:00.000Z</v>
       </c>
       <c r="C362" t="str">
         <v>Pillai Traders</v>
@@ -11990,7 +11990,7 @@
         <v>SO-10362</v>
       </c>
       <c r="B363" s="1" t="d">
-        <v>2025-10-25T05:30:00.000Z</v>
+        <v>2025-10-25T00:00:00.000Z</v>
       </c>
       <c r="C363" t="str">
         <v>Sharma Retail</v>
@@ -12022,7 +12022,7 @@
         <v>SO-10363</v>
       </c>
       <c r="B364" s="1" t="d">
-        <v>2025-10-25T05:30:00.000Z</v>
+        <v>2025-10-25T00:00:00.000Z</v>
       </c>
       <c r="C364" t="str">
         <v>Rao Traders</v>
@@ -12054,7 +12054,7 @@
         <v>SO-10364</v>
       </c>
       <c r="B365" s="1" t="d">
-        <v>2025-10-25T05:30:00.000Z</v>
+        <v>2025-10-25T00:00:00.000Z</v>
       </c>
       <c r="C365" t="str">
         <v>Desai Enterprises</v>
@@ -12086,7 +12086,7 @@
         <v>SO-10365</v>
       </c>
       <c r="B366" s="1" t="d">
-        <v>2025-10-26T05:30:00.000Z</v>
+        <v>2025-10-26T00:00:00.000Z</v>
       </c>
       <c r="C366" t="str">
         <v>Rao Stores</v>
@@ -12118,7 +12118,7 @@
         <v>SO-10366</v>
       </c>
       <c r="B367" s="1" t="d">
-        <v>2025-10-28T05:30:00.000Z</v>
+        <v>2025-10-28T00:00:00.000Z</v>
       </c>
       <c r="C367" t="str">
         <v>Pillai Stores</v>
@@ -12150,7 +12150,7 @@
         <v>SO-10367</v>
       </c>
       <c r="B368" s="1" t="d">
-        <v>2025-10-29T05:30:00.000Z</v>
+        <v>2025-10-29T00:00:00.000Z</v>
       </c>
       <c r="C368" t="str">
         <v>Kulkarni Traders</v>
@@ -12182,7 +12182,7 @@
         <v>SO-10368</v>
       </c>
       <c r="B369" s="1" t="d">
-        <v>2025-10-29T05:30:00.000Z</v>
+        <v>2025-10-29T00:00:00.000Z</v>
       </c>
       <c r="C369" t="str">
         <v>Iyer Labs</v>
@@ -12214,7 +12214,7 @@
         <v>SO-10369</v>
       </c>
       <c r="B370" s="1" t="d">
-        <v>2025-10-28T05:30:00.000Z</v>
+        <v>2025-10-28T00:00:00.000Z</v>
       </c>
       <c r="C370" t="str">
         <v>Iyer Labs</v>
@@ -12246,7 +12246,7 @@
         <v>SO-10370</v>
       </c>
       <c r="B371" s="1" t="d">
-        <v>2025-10-29T05:30:00.000Z</v>
+        <v>2025-10-29T00:00:00.000Z</v>
       </c>
       <c r="C371" t="str">
         <v>Desai Retail</v>
@@ -12278,7 +12278,7 @@
         <v>SO-10371</v>
       </c>
       <c r="B372" s="1" t="d">
-        <v>2025-10-30T05:30:00.000Z</v>
+        <v>2025-10-30T00:00:00.000Z</v>
       </c>
       <c r="C372" t="str">
         <v>Rao Stores</v>
@@ -12310,7 +12310,7 @@
         <v>SO-10372</v>
       </c>
       <c r="B373" s="1" t="d">
-        <v>2025-11-01T05:30:00.000Z</v>
+        <v>2025-11-01T00:00:00.000Z</v>
       </c>
       <c r="C373" t="str">
         <v>Rao Retail</v>
@@ -12342,7 +12342,7 @@
         <v>SO-10373</v>
       </c>
       <c r="B374" s="1" t="d">
-        <v>2025-10-30T05:30:00.000Z</v>
+        <v>2025-10-30T00:00:00.000Z</v>
       </c>
       <c r="C374" t="str">
         <v>Nair Solutions</v>
@@ -12374,7 +12374,7 @@
         <v>SO-10374</v>
       </c>
       <c r="B375" s="1" t="d">
-        <v>2025-11-01T05:30:00.000Z</v>
+        <v>2025-11-01T00:00:00.000Z</v>
       </c>
       <c r="C375" t="str">
         <v>Patil Traders</v>
@@ -12406,7 +12406,7 @@
         <v>SO-10375</v>
       </c>
       <c r="B376" s="1" t="d">
-        <v>2025-10-31T05:30:00.000Z</v>
+        <v>2025-10-31T00:00:00.000Z</v>
       </c>
       <c r="C376" t="str">
         <v>Sharma Enterprises</v>
@@ -12438,7 +12438,7 @@
         <v>SO-10376</v>
       </c>
       <c r="B377" s="1" t="d">
-        <v>2025-11-01T05:30:00.000Z</v>
+        <v>2025-11-01T00:00:00.000Z</v>
       </c>
       <c r="C377" t="str">
         <v>Rao Labs</v>
@@ -12470,7 +12470,7 @@
         <v>SO-10377</v>
       </c>
       <c r="B378" s="1" t="d">
-        <v>2025-11-03T05:30:00.000Z</v>
+        <v>2025-11-03T00:00:00.000Z</v>
       </c>
       <c r="C378" t="str">
         <v>Sharma Traders</v>
@@ -12502,7 +12502,7 @@
         <v>SO-10378</v>
       </c>
       <c r="B379" s="1" t="d">
-        <v>2025-11-02T05:30:00.000Z</v>
+        <v>2025-11-02T00:00:00.000Z</v>
       </c>
       <c r="C379" t="str">
         <v>Patil Labs</v>
@@ -12534,7 +12534,7 @@
         <v>SO-10379</v>
       </c>
       <c r="B380" s="1" t="d">
-        <v>2025-11-05T05:30:00.000Z</v>
+        <v>2025-11-05T00:00:00.000Z</v>
       </c>
       <c r="C380" t="str">
         <v>Desai Stores</v>
@@ -12566,7 +12566,7 @@
         <v>SO-10380</v>
       </c>
       <c r="B381" s="1" t="d">
-        <v>2025-11-04T05:30:00.000Z</v>
+        <v>2025-11-04T00:00:00.000Z</v>
       </c>
       <c r="C381" t="str">
         <v>Kulkarni Retail</v>
@@ -12598,7 +12598,7 @@
         <v>SO-10381</v>
       </c>
       <c r="B382" s="1" t="d">
-        <v>2025-11-05T05:30:00.000Z</v>
+        <v>2025-11-05T00:00:00.000Z</v>
       </c>
       <c r="C382" t="str">
         <v>Khan Traders</v>
@@ -12630,7 +12630,7 @@
         <v>SO-10382</v>
       </c>
       <c r="B383" s="1" t="d">
-        <v>2025-11-05T05:30:00.000Z</v>
+        <v>2025-11-05T00:00:00.000Z</v>
       </c>
       <c r="C383" t="str">
         <v>Patil Solutions</v>
@@ -12662,7 +12662,7 @@
         <v>SO-10383</v>
       </c>
       <c r="B384" s="1" t="d">
-        <v>2025-11-05T05:30:00.000Z</v>
+        <v>2025-11-05T00:00:00.000Z</v>
       </c>
       <c r="C384" t="str">
         <v>Rao Stores</v>
@@ -12694,7 +12694,7 @@
         <v>SO-10384</v>
       </c>
       <c r="B385" s="1" t="d">
-        <v>2025-11-07T05:30:00.000Z</v>
+        <v>2025-11-07T00:00:00.000Z</v>
       </c>
       <c r="C385" t="str">
         <v>Joshi Solutions</v>
@@ -12726,7 +12726,7 @@
         <v>SO-10385</v>
       </c>
       <c r="B386" s="1" t="d">
-        <v>2025-11-08T05:30:00.000Z</v>
+        <v>2025-11-08T00:00:00.000Z</v>
       </c>
       <c r="C386" t="str">
         <v>Pillai Traders</v>
@@ -12758,7 +12758,7 @@
         <v>SO-10386</v>
       </c>
       <c r="B387" s="1" t="d">
-        <v>2025-11-06T05:30:00.000Z</v>
+        <v>2025-11-06T00:00:00.000Z</v>
       </c>
       <c r="C387" t="str">
         <v>Mehta Stores</v>
@@ -12790,7 +12790,7 @@
         <v>SO-10387</v>
       </c>
       <c r="B388" s="1" t="d">
-        <v>2025-11-07T05:30:00.000Z</v>
+        <v>2025-11-07T00:00:00.000Z</v>
       </c>
       <c r="C388" t="str">
         <v>Patil Traders</v>
@@ -12822,7 +12822,7 @@
         <v>SO-10388</v>
       </c>
       <c r="B389" s="1" t="d">
-        <v>2025-11-08T05:30:00.000Z</v>
+        <v>2025-11-08T00:00:00.000Z</v>
       </c>
       <c r="C389" t="str">
         <v>Desai Stores</v>
@@ -12854,7 +12854,7 @@
         <v>SO-10389</v>
       </c>
       <c r="B390" s="1" t="d">
-        <v>2025-11-11T05:30:00.000Z</v>
+        <v>2025-11-11T00:00:00.000Z</v>
       </c>
       <c r="C390" t="str">
         <v>Nair Enterprises</v>
@@ -12886,7 +12886,7 @@
         <v>SO-10390</v>
       </c>
       <c r="B391" s="1" t="d">
-        <v>2025-11-10T05:30:00.000Z</v>
+        <v>2025-11-10T00:00:00.000Z</v>
       </c>
       <c r="C391" t="str">
         <v>Nair Labs</v>
@@ -12918,7 +12918,7 @@
         <v>SO-10391</v>
       </c>
       <c r="B392" s="1" t="d">
-        <v>2025-11-10T05:30:00.000Z</v>
+        <v>2025-11-10T00:00:00.000Z</v>
       </c>
       <c r="C392" t="str">
         <v>Kulkarni Stores</v>
@@ -12950,7 +12950,7 @@
         <v>SO-10392</v>
       </c>
       <c r="B393" s="1" t="d">
-        <v>2025-11-11T05:30:00.000Z</v>
+        <v>2025-11-11T00:00:00.000Z</v>
       </c>
       <c r="C393" t="str">
         <v>Patil Retail</v>
@@ -12982,7 +12982,7 @@
         <v>SO-10393</v>
       </c>
       <c r="B394" s="1" t="d">
-        <v>2025-11-10T05:30:00.000Z</v>
+        <v>2025-11-10T00:00:00.000Z</v>
       </c>
       <c r="C394" t="str">
         <v>Nair Labs</v>
@@ -13014,7 +13014,7 @@
         <v>SO-10394</v>
       </c>
       <c r="B395" s="1" t="d">
-        <v>2025-11-13T05:30:00.000Z</v>
+        <v>2025-11-13T00:00:00.000Z</v>
       </c>
       <c r="C395" t="str">
         <v>Patil Retail</v>
@@ -13046,7 +13046,7 @@
         <v>SO-10395</v>
       </c>
       <c r="B396" s="1" t="d">
-        <v>2025-11-12T05:30:00.000Z</v>
+        <v>2025-11-12T00:00:00.000Z</v>
       </c>
       <c r="C396" t="str">
         <v>Desai Enterprises</v>
@@ -13078,7 +13078,7 @@
         <v>SO-10396</v>
       </c>
       <c r="B397" s="1" t="d">
-        <v>2025-11-14T05:30:00.000Z</v>
+        <v>2025-11-14T00:00:00.000Z</v>
       </c>
       <c r="C397" t="str">
         <v>Sharma Traders</v>
@@ -13110,7 +13110,7 @@
         <v>SO-10397</v>
       </c>
       <c r="B398" s="1" t="d">
-        <v>2025-11-13T05:30:00.000Z</v>
+        <v>2025-11-13T00:00:00.000Z</v>
       </c>
       <c r="C398" t="str">
         <v>Desai Retail</v>
@@ -13142,7 +13142,7 @@
         <v>SO-10398</v>
       </c>
       <c r="B399" s="1" t="d">
-        <v>2025-11-15T05:30:00.000Z</v>
+        <v>2025-11-15T00:00:00.000Z</v>
       </c>
       <c r="C399" t="str">
         <v>Nair Labs</v>
@@ -13174,7 +13174,7 @@
         <v>SO-10399</v>
       </c>
       <c r="B400" s="1" t="d">
-        <v>2025-11-15T05:30:00.000Z</v>
+        <v>2025-11-15T00:00:00.000Z</v>
       </c>
       <c r="C400" t="str">
         <v>Patil Stores</v>
@@ -13206,7 +13206,7 @@
         <v>SO-10400</v>
       </c>
       <c r="B401" s="1" t="d">
-        <v>2025-11-15T05:30:00.000Z</v>
+        <v>2025-11-15T00:00:00.000Z</v>
       </c>
       <c r="C401" t="str">
         <v>Khan Traders</v>
@@ -13238,7 +13238,7 @@
         <v>SO-10401</v>
       </c>
       <c r="B402" s="1" t="d">
-        <v>2025-11-17T05:30:00.000Z</v>
+        <v>2025-11-17T00:00:00.000Z</v>
       </c>
       <c r="C402" t="str">
         <v>Iyer Labs</v>
@@ -13270,7 +13270,7 @@
         <v>SO-10402</v>
       </c>
       <c r="B403" s="1" t="d">
-        <v>2025-11-16T05:30:00.000Z</v>
+        <v>2025-11-16T00:00:00.000Z</v>
       </c>
       <c r="C403" t="str">
         <v>Desai Solutions</v>
@@ -13302,7 +13302,7 @@
         <v>SO-10403</v>
       </c>
       <c r="B404" s="1" t="d">
-        <v>2025-11-18T05:30:00.000Z</v>
+        <v>2025-11-18T00:00:00.000Z</v>
       </c>
       <c r="C404" t="str">
         <v>Desai Labs</v>
@@ -13334,7 +13334,7 @@
         <v>SO-10404</v>
       </c>
       <c r="B405" s="1" t="d">
-        <v>2025-11-18T05:30:00.000Z</v>
+        <v>2025-11-18T00:00:00.000Z</v>
       </c>
       <c r="C405" t="str">
         <v>Nair Solutions</v>
@@ -13366,7 +13366,7 @@
         <v>SO-10405</v>
       </c>
       <c r="B406" s="1" t="d">
-        <v>2025-11-18T05:30:00.000Z</v>
+        <v>2025-11-18T00:00:00.000Z</v>
       </c>
       <c r="C406" t="str">
         <v>Pillai Traders</v>
@@ -13398,7 +13398,7 @@
         <v>SO-10406</v>
       </c>
       <c r="B407" s="1" t="d">
-        <v>2025-11-19T05:30:00.000Z</v>
+        <v>2025-11-19T00:00:00.000Z</v>
       </c>
       <c r="C407" t="str">
         <v>Kulkarni Traders</v>
@@ -13430,7 +13430,7 @@
         <v>SO-10407</v>
       </c>
       <c r="B408" s="1" t="d">
-        <v>2025-11-20T05:30:00.000Z</v>
+        <v>2025-11-20T00:00:00.000Z</v>
       </c>
       <c r="C408" t="str">
         <v>Pillai Solutions</v>
@@ -13462,7 +13462,7 @@
         <v>SO-10408</v>
       </c>
       <c r="B409" s="1" t="d">
-        <v>2025-11-21T05:30:00.000Z</v>
+        <v>2025-11-21T00:00:00.000Z</v>
       </c>
       <c r="C409" t="str">
         <v>Sharma Solutions</v>
@@ -13494,7 +13494,7 @@
         <v>SO-10409</v>
       </c>
       <c r="B410" s="1" t="d">
-        <v>2025-11-21T05:30:00.000Z</v>
+        <v>2025-11-21T00:00:00.000Z</v>
       </c>
       <c r="C410" t="str">
         <v>Mehta Traders</v>
@@ -13526,7 +13526,7 @@
         <v>SO-10410</v>
       </c>
       <c r="B411" s="1" t="d">
-        <v>2025-11-22T05:30:00.000Z</v>
+        <v>2025-11-22T00:00:00.000Z</v>
       </c>
       <c r="C411" t="str">
         <v>Sharma Labs</v>
@@ -13558,7 +13558,7 @@
         <v>SO-10411</v>
       </c>
       <c r="B412" s="1" t="d">
-        <v>2025-11-23T05:30:00.000Z</v>
+        <v>2025-11-23T00:00:00.000Z</v>
       </c>
       <c r="C412" t="str">
         <v>Patil Retail</v>
@@ -13590,7 +13590,7 @@
         <v>SO-10412</v>
       </c>
       <c r="B413" s="1" t="d">
-        <v>2025-11-23T05:30:00.000Z</v>
+        <v>2025-11-23T00:00:00.000Z</v>
       </c>
       <c r="C413" t="str">
         <v>Rao Stores</v>
@@ -13622,7 +13622,7 @@
         <v>SO-10413</v>
       </c>
       <c r="B414" s="1" t="d">
-        <v>2025-11-23T05:30:00.000Z</v>
+        <v>2025-11-23T00:00:00.000Z</v>
       </c>
       <c r="C414" t="str">
         <v>Kulkarni Traders</v>
@@ -13654,7 +13654,7 @@
         <v>SO-10414</v>
       </c>
       <c r="B415" s="1" t="d">
-        <v>2025-11-24T05:30:00.000Z</v>
+        <v>2025-11-24T00:00:00.000Z</v>
       </c>
       <c r="C415" t="str">
         <v>Pillai Retail</v>
@@ -13686,7 +13686,7 @@
         <v>SO-10415</v>
       </c>
       <c r="B416" s="1" t="d">
-        <v>2025-11-25T05:30:00.000Z</v>
+        <v>2025-11-25T00:00:00.000Z</v>
       </c>
       <c r="C416" t="str">
         <v>Patil Traders</v>
@@ -13718,7 +13718,7 @@
         <v>SO-10416</v>
       </c>
       <c r="B417" s="1" t="d">
-        <v>2025-11-26T05:30:00.000Z</v>
+        <v>2025-11-26T00:00:00.000Z</v>
       </c>
       <c r="C417" t="str">
         <v>Khan Traders</v>
@@ -13750,7 +13750,7 @@
         <v>SO-10417</v>
       </c>
       <c r="B418" s="1" t="d">
-        <v>2025-11-24T05:30:00.000Z</v>
+        <v>2025-11-24T00:00:00.000Z</v>
       </c>
       <c r="C418" t="str">
         <v>Pillai Retail</v>
@@ -13782,7 +13782,7 @@
         <v>SO-10418</v>
       </c>
       <c r="B419" s="1" t="d">
-        <v>2025-11-27T05:30:00.000Z</v>
+        <v>2025-11-27T00:00:00.000Z</v>
       </c>
       <c r="C419" t="str">
         <v>Rao Enterprises</v>
@@ -13814,7 +13814,7 @@
         <v>SO-10419</v>
       </c>
       <c r="B420" s="1" t="d">
-        <v>2025-11-26T05:30:00.000Z</v>
+        <v>2025-11-26T00:00:00.000Z</v>
       </c>
       <c r="C420" t="str">
         <v>Sharma Retail</v>
@@ -13846,7 +13846,7 @@
         <v>SO-10420</v>
       </c>
       <c r="B421" s="1" t="d">
-        <v>2025-11-28T05:30:00.000Z</v>
+        <v>2025-11-28T00:00:00.000Z</v>
       </c>
       <c r="C421" t="str">
         <v>Iyer Labs</v>
@@ -13878,7 +13878,7 @@
         <v>SO-10421</v>
       </c>
       <c r="B422" s="1" t="d">
-        <v>2025-11-26T05:30:00.000Z</v>
+        <v>2025-11-26T00:00:00.000Z</v>
       </c>
       <c r="C422" t="str">
         <v>Sharma Labs</v>
@@ -13910,7 +13910,7 @@
         <v>SO-10422</v>
       </c>
       <c r="B423" s="1" t="d">
-        <v>2025-11-29T05:30:00.000Z</v>
+        <v>2025-11-29T00:00:00.000Z</v>
       </c>
       <c r="C423" t="str">
         <v>Joshi Solutions</v>
@@ -13942,7 +13942,7 @@
         <v>SO-10423</v>
       </c>
       <c r="B424" s="1" t="d">
-        <v>2025-11-30T05:30:00.000Z</v>
+        <v>2025-11-30T00:00:00.000Z</v>
       </c>
       <c r="C424" t="str">
         <v>Iyer Traders</v>
@@ -13974,7 +13974,7 @@
         <v>SO-10424</v>
       </c>
       <c r="B425" s="1" t="d">
-        <v>2025-11-29T05:30:00.000Z</v>
+        <v>2025-11-29T00:00:00.000Z</v>
       </c>
       <c r="C425" t="str">
         <v>Patil Retail</v>
@@ -14006,7 +14006,7 @@
         <v>SO-10425</v>
       </c>
       <c r="B426" s="1" t="d">
-        <v>2025-11-29T05:30:00.000Z</v>
+        <v>2025-11-29T00:00:00.000Z</v>
       </c>
       <c r="C426" t="str">
         <v>Nair Labs</v>
@@ -14038,7 +14038,7 @@
         <v>SO-10426</v>
       </c>
       <c r="B427" s="1" t="d">
-        <v>2025-12-02T05:30:00.000Z</v>
+        <v>2025-12-02T00:00:00.000Z</v>
       </c>
       <c r="C427" t="str">
         <v>Pillai Stores</v>
@@ -14070,7 +14070,7 @@
         <v>SO-10427</v>
       </c>
       <c r="B428" s="1" t="d">
-        <v>2025-11-30T05:30:00.000Z</v>
+        <v>2025-11-30T00:00:00.000Z</v>
       </c>
       <c r="C428" t="str">
         <v>Joshi Stores</v>
@@ -14102,7 +14102,7 @@
         <v>SO-10428</v>
       </c>
       <c r="B429" s="1" t="d">
-        <v>2025-12-02T05:30:00.000Z</v>
+        <v>2025-12-02T00:00:00.000Z</v>
       </c>
       <c r="C429" t="str">
         <v>Rao Labs</v>
@@ -14134,7 +14134,7 @@
         <v>SO-10429</v>
       </c>
       <c r="B430" s="1" t="d">
-        <v>2025-12-03T05:30:00.000Z</v>
+        <v>2025-12-03T00:00:00.000Z</v>
       </c>
       <c r="C430" t="str">
         <v>Khan Retail</v>
@@ -14166,7 +14166,7 @@
         <v>SO-10430</v>
       </c>
       <c r="B431" s="1" t="d">
-        <v>2025-12-03T05:30:00.000Z</v>
+        <v>2025-12-03T00:00:00.000Z</v>
       </c>
       <c r="C431" t="str">
         <v>Sharma Enterprises</v>
@@ -14198,7 +14198,7 @@
         <v>SO-10431</v>
       </c>
       <c r="B432" s="1" t="d">
-        <v>2025-12-03T05:30:00.000Z</v>
+        <v>2025-12-03T00:00:00.000Z</v>
       </c>
       <c r="C432" t="str">
         <v>Kulkarni Traders</v>
@@ -14230,7 +14230,7 @@
         <v>SO-10432</v>
       </c>
       <c r="B433" s="1" t="d">
-        <v>2025-12-04T05:30:00.000Z</v>
+        <v>2025-12-04T00:00:00.000Z</v>
       </c>
       <c r="C433" t="str">
         <v>Sharma Enterprises</v>
@@ -14262,7 +14262,7 @@
         <v>SO-10433</v>
       </c>
       <c r="B434" s="1" t="d">
-        <v>2025-12-05T05:30:00.000Z</v>
+        <v>2025-12-05T00:00:00.000Z</v>
       </c>
       <c r="C434" t="str">
         <v>Sharma Enterprises</v>
@@ -14294,7 +14294,7 @@
         <v>SO-10434</v>
       </c>
       <c r="B435" s="1" t="d">
-        <v>2025-12-05T05:30:00.000Z</v>
+        <v>2025-12-05T00:00:00.000Z</v>
       </c>
       <c r="C435" t="str">
         <v>Patil Stores</v>
@@ -14326,7 +14326,7 @@
         <v>SO-10435</v>
       </c>
       <c r="B436" s="1" t="d">
-        <v>2025-12-05T05:30:00.000Z</v>
+        <v>2025-12-05T00:00:00.000Z</v>
       </c>
       <c r="C436" t="str">
         <v>Desai Retail</v>
@@ -14358,7 +14358,7 @@
         <v>SO-10436</v>
       </c>
       <c r="B437" s="1" t="d">
-        <v>2025-12-06T05:30:00.000Z</v>
+        <v>2025-12-06T00:00:00.000Z</v>
       </c>
       <c r="C437" t="str">
         <v>Nair Traders</v>
@@ -14390,7 +14390,7 @@
         <v>SO-10437</v>
       </c>
       <c r="B438" s="1" t="d">
-        <v>2025-12-06T05:30:00.000Z</v>
+        <v>2025-12-06T00:00:00.000Z</v>
       </c>
       <c r="C438" t="str">
         <v>Iyer Enterprises</v>
@@ -14422,7 +14422,7 @@
         <v>SO-10438</v>
       </c>
       <c r="B439" s="1" t="d">
-        <v>2025-12-06T05:30:00.000Z</v>
+        <v>2025-12-06T00:00:00.000Z</v>
       </c>
       <c r="C439" t="str">
         <v>Kulkarni Traders</v>
@@ -14454,7 +14454,7 @@
         <v>SO-10439</v>
       </c>
       <c r="B440" s="1" t="d">
-        <v>2025-12-09T05:30:00.000Z</v>
+        <v>2025-12-09T00:00:00.000Z</v>
       </c>
       <c r="C440" t="str">
         <v>Khan Solutions</v>
@@ -14486,7 +14486,7 @@
         <v>SO-10440</v>
       </c>
       <c r="B441" s="1" t="d">
-        <v>2025-12-09T05:30:00.000Z</v>
+        <v>2025-12-09T00:00:00.000Z</v>
       </c>
       <c r="C441" t="str">
         <v>Patil Labs</v>
@@ -14518,7 +14518,7 @@
         <v>SO-10441</v>
       </c>
       <c r="B442" s="1" t="d">
-        <v>2025-12-09T05:30:00.000Z</v>
+        <v>2025-12-09T00:00:00.000Z</v>
       </c>
       <c r="C442" t="str">
         <v>Patil Retail</v>
@@ -14550,7 +14550,7 @@
         <v>SO-10442</v>
       </c>
       <c r="B443" s="1" t="d">
-        <v>2025-12-11T05:30:00.000Z</v>
+        <v>2025-12-11T00:00:00.000Z</v>
       </c>
       <c r="C443" t="str">
         <v>Mehta Stores</v>
@@ -14582,7 +14582,7 @@
         <v>SO-10443</v>
       </c>
       <c r="B444" s="1" t="d">
-        <v>2025-12-10T05:30:00.000Z</v>
+        <v>2025-12-10T00:00:00.000Z</v>
       </c>
       <c r="C444" t="str">
         <v>Kulkarni Stores</v>
@@ -14614,7 +14614,7 @@
         <v>SO-10444</v>
       </c>
       <c r="B445" s="1" t="d">
-        <v>2025-12-11T05:30:00.000Z</v>
+        <v>2025-12-11T00:00:00.000Z</v>
       </c>
       <c r="C445" t="str">
         <v>Patil Stores</v>
@@ -14646,7 +14646,7 @@
         <v>SO-10445</v>
       </c>
       <c r="B446" s="1" t="d">
-        <v>2025-12-10T05:30:00.000Z</v>
+        <v>2025-12-10T00:00:00.000Z</v>
       </c>
       <c r="C446" t="str">
         <v>Nair Solutions</v>
@@ -14678,7 +14678,7 @@
         <v>SO-10446</v>
       </c>
       <c r="B447" s="1" t="d">
-        <v>2025-12-11T05:30:00.000Z</v>
+        <v>2025-12-11T00:00:00.000Z</v>
       </c>
       <c r="C447" t="str">
         <v>Pillai Solutions</v>
@@ -14710,7 +14710,7 @@
         <v>SO-10447</v>
       </c>
       <c r="B448" s="1" t="d">
-        <v>2025-12-11T05:30:00.000Z</v>
+        <v>2025-12-11T00:00:00.000Z</v>
       </c>
       <c r="C448" t="str">
         <v>Kulkarni Traders</v>
@@ -14742,7 +14742,7 @@
         <v>SO-10448</v>
       </c>
       <c r="B449" s="1" t="d">
-        <v>2025-12-14T05:30:00.000Z</v>
+        <v>2025-12-14T00:00:00.000Z</v>
       </c>
       <c r="C449" t="str">
         <v>Iyer Enterprises</v>
@@ -14774,7 +14774,7 @@
         <v>SO-10449</v>
       </c>
       <c r="B450" s="1" t="d">
-        <v>2025-12-15T05:30:00.000Z</v>
+        <v>2025-12-15T00:00:00.000Z</v>
       </c>
       <c r="C450" t="str">
         <v>Sharma Solutions</v>
@@ -14806,7 +14806,7 @@
         <v>SO-10450</v>
       </c>
       <c r="B451" s="1" t="d">
-        <v>2025-12-14T05:30:00.000Z</v>
+        <v>2025-12-14T00:00:00.000Z</v>
       </c>
       <c r="C451" t="str">
         <v>Patil Traders</v>
@@ -14838,7 +14838,7 @@
         <v>SO-10451</v>
       </c>
       <c r="B452" s="1" t="d">
-        <v>2025-12-13T05:30:00.000Z</v>
+        <v>2025-12-13T00:00:00.000Z</v>
       </c>
       <c r="C452" t="str">
         <v>Pillai Enterprises</v>
@@ -14870,7 +14870,7 @@
         <v>SO-10452</v>
       </c>
       <c r="B453" s="1" t="d">
-        <v>2025-12-16T05:30:00.000Z</v>
+        <v>2025-12-16T00:00:00.000Z</v>
       </c>
       <c r="C453" t="str">
         <v>Nair Enterprises</v>
@@ -14902,7 +14902,7 @@
         <v>SO-10453</v>
       </c>
       <c r="B454" s="1" t="d">
-        <v>2025-12-17T05:30:00.000Z</v>
+        <v>2025-12-17T00:00:00.000Z</v>
       </c>
       <c r="C454" t="str">
         <v>Nair Solutions</v>
@@ -14934,7 +14934,7 @@
         <v>SO-10454</v>
       </c>
       <c r="B455" s="1" t="d">
-        <v>2025-12-18T05:30:00.000Z</v>
+        <v>2025-12-18T00:00:00.000Z</v>
       </c>
       <c r="C455" t="str">
         <v>Patil Stores</v>
@@ -14966,7 +14966,7 @@
         <v>SO-10455</v>
       </c>
       <c r="B456" s="1" t="d">
-        <v>2025-12-16T05:30:00.000Z</v>
+        <v>2025-12-16T00:00:00.000Z</v>
       </c>
       <c r="C456" t="str">
         <v>Patil Labs</v>
@@ -14998,7 +14998,7 @@
         <v>SO-10456</v>
       </c>
       <c r="B457" s="1" t="d">
-        <v>2025-12-18T05:30:00.000Z</v>
+        <v>2025-12-18T00:00:00.000Z</v>
       </c>
       <c r="C457" t="str">
         <v>Joshi Solutions</v>
@@ -15030,7 +15030,7 @@
         <v>SO-10457</v>
       </c>
       <c r="B458" s="1" t="d">
-        <v>2025-12-17T05:30:00.000Z</v>
+        <v>2025-12-17T00:00:00.000Z</v>
       </c>
       <c r="C458" t="str">
         <v>Rao Labs</v>
@@ -15062,7 +15062,7 @@
         <v>SO-10458</v>
       </c>
       <c r="B459" s="1" t="d">
-        <v>2025-12-18T05:30:00.000Z</v>
+        <v>2025-12-18T00:00:00.000Z</v>
       </c>
       <c r="C459" t="str">
         <v>Desai Solutions</v>
@@ -15094,7 +15094,7 @@
         <v>SO-10459</v>
       </c>
       <c r="B460" s="1" t="d">
-        <v>2025-12-18T05:30:00.000Z</v>
+        <v>2025-12-18T00:00:00.000Z</v>
       </c>
       <c r="C460" t="str">
         <v>Pillai Retail</v>
@@ -15126,7 +15126,7 @@
         <v>SO-10460</v>
       </c>
       <c r="B461" s="1" t="d">
-        <v>2025-12-21T05:30:00.000Z</v>
+        <v>2025-12-21T00:00:00.000Z</v>
       </c>
       <c r="C461" t="str">
         <v>Desai Labs</v>
@@ -15158,7 +15158,7 @@
         <v>SO-10461</v>
       </c>
       <c r="B462" s="1" t="d">
-        <v>2025-12-19T05:30:00.000Z</v>
+        <v>2025-12-19T00:00:00.000Z</v>
       </c>
       <c r="C462" t="str">
         <v>Desai Enterprises</v>
@@ -15190,7 +15190,7 @@
         <v>SO-10462</v>
       </c>
       <c r="B463" s="1" t="d">
-        <v>2025-12-21T05:30:00.000Z</v>
+        <v>2025-12-21T00:00:00.000Z</v>
       </c>
       <c r="C463" t="str">
         <v>Patil Retail</v>
@@ -15222,7 +15222,7 @@
         <v>SO-10463</v>
       </c>
       <c r="B464" s="1" t="d">
-        <v>2025-12-22T05:30:00.000Z</v>
+        <v>2025-12-22T00:00:00.000Z</v>
       </c>
       <c r="C464" t="str">
         <v>Pillai Traders</v>
@@ -15254,7 +15254,7 @@
         <v>SO-10464</v>
       </c>
       <c r="B465" s="1" t="d">
-        <v>2025-12-21T05:30:00.000Z</v>
+        <v>2025-12-21T00:00:00.000Z</v>
       </c>
       <c r="C465" t="str">
         <v>Rao Traders</v>
@@ -15286,7 +15286,7 @@
         <v>SO-10465</v>
       </c>
       <c r="B466" s="1" t="d">
-        <v>2025-12-22T05:30:00.000Z</v>
+        <v>2025-12-22T00:00:00.000Z</v>
       </c>
       <c r="C466" t="str">
         <v>Sharma Labs</v>
@@ -15318,7 +15318,7 @@
         <v>SO-10466</v>
       </c>
       <c r="B467" s="1" t="d">
-        <v>2025-12-23T05:30:00.000Z</v>
+        <v>2025-12-23T00:00:00.000Z</v>
       </c>
       <c r="C467" t="str">
         <v>Sharma Enterprises</v>
@@ -15350,7 +15350,7 @@
         <v>SO-10467</v>
       </c>
       <c r="B468" s="1" t="d">
-        <v>2025-12-24T05:30:00.000Z</v>
+        <v>2025-12-24T00:00:00.000Z</v>
       </c>
       <c r="C468" t="str">
         <v>Pillai Solutions</v>
@@ -15382,7 +15382,7 @@
         <v>SO-10468</v>
       </c>
       <c r="B469" s="1" t="d">
-        <v>2025-12-24T05:30:00.000Z</v>
+        <v>2025-12-24T00:00:00.000Z</v>
       </c>
       <c r="C469" t="str">
         <v>Pillai Retail</v>
@@ -15414,7 +15414,7 @@
         <v>SO-10469</v>
       </c>
       <c r="B470" s="1" t="d">
-        <v>2025-12-25T05:30:00.000Z</v>
+        <v>2025-12-25T00:00:00.000Z</v>
       </c>
       <c r="C470" t="str">
         <v>Rao Enterprises</v>
@@ -15446,7 +15446,7 @@
         <v>SO-10470</v>
       </c>
       <c r="B471" s="1" t="d">
-        <v>2025-12-27T05:30:00.000Z</v>
+        <v>2025-12-27T00:00:00.000Z</v>
       </c>
       <c r="C471" t="str">
         <v>Patil Enterprises</v>
@@ -15478,7 +15478,7 @@
         <v>SO-10471</v>
       </c>
       <c r="B472" s="1" t="d">
-        <v>2025-12-27T05:30:00.000Z</v>
+        <v>2025-12-27T00:00:00.000Z</v>
       </c>
       <c r="C472" t="str">
         <v>Patil Enterprises</v>
@@ -15510,7 +15510,7 @@
         <v>SO-10472</v>
       </c>
       <c r="B473" s="1" t="d">
-        <v>2025-12-26T05:30:00.000Z</v>
+        <v>2025-12-26T00:00:00.000Z</v>
       </c>
       <c r="C473" t="str">
         <v>Patil Retail</v>
@@ -15542,7 +15542,7 @@
         <v>SO-10473</v>
       </c>
       <c r="B474" s="1" t="d">
-        <v>2025-12-26T05:30:00.000Z</v>
+        <v>2025-12-26T00:00:00.000Z</v>
       </c>
       <c r="C474" t="str">
         <v>Patil Enterprises</v>
@@ -15574,7 +15574,7 @@
         <v>SO-10474</v>
       </c>
       <c r="B475" s="1" t="d">
-        <v>2025-12-28T05:30:00.000Z</v>
+        <v>2025-12-28T00:00:00.000Z</v>
       </c>
       <c r="C475" t="str">
         <v>Sharma Retail</v>
@@ -15606,7 +15606,7 @@
         <v>SO-10475</v>
       </c>
       <c r="B476" s="1" t="d">
-        <v>2025-12-29T05:30:00.000Z</v>
+        <v>2025-12-29T00:00:00.000Z</v>
       </c>
       <c r="C476" t="str">
         <v>Nair Retail</v>
@@ -15638,7 +15638,7 @@
         <v>SO-10476</v>
       </c>
       <c r="B477" s="1" t="d">
-        <v>2025-12-28T05:30:00.000Z</v>
+        <v>2025-12-28T00:00:00.000Z</v>
       </c>
       <c r="C477" t="str">
         <v>Nair Labs</v>
@@ -15670,7 +15670,7 @@
         <v>SO-10477</v>
       </c>
       <c r="B478" s="1" t="d">
-        <v>2025-12-28T05:30:00.000Z</v>
+        <v>2025-12-28T00:00:00.000Z</v>
       </c>
       <c r="C478" t="str">
         <v>Pillai Stores</v>
@@ -15702,7 +15702,7 @@
         <v>SO-10478</v>
       </c>
       <c r="B479" s="1" t="d">
-        <v>2025-12-29T05:30:00.000Z</v>
+        <v>2025-12-29T00:00:00.000Z</v>
       </c>
       <c r="C479" t="str">
         <v>Sharma Enterprises</v>
@@ -15734,7 +15734,7 @@
         <v>SO-10479</v>
       </c>
       <c r="B480" s="1" t="d">
-        <v>2025-12-31T05:30:00.000Z</v>
+        <v>2025-12-31T00:00:00.000Z</v>
       </c>
       <c r="C480" t="str">
         <v>Sharma Solutions</v>
@@ -15766,7 +15766,7 @@
         <v>SO-10480</v>
       </c>
       <c r="B481" s="1" t="d">
-        <v>2026-01-01T05:30:00.000Z</v>
+        <v>2026-01-01T00:00:00.000Z</v>
       </c>
       <c r="C481" t="str">
         <v>Sharma Enterprises</v>
@@ -15798,7 +15798,7 @@
         <v>SO-10481</v>
       </c>
       <c r="B482" s="1" t="d">
-        <v>2025-12-30T05:30:00.000Z</v>
+        <v>2025-12-30T00:00:00.000Z</v>
       </c>
       <c r="C482" t="str">
         <v>Sharma Retail</v>
@@ -15830,7 +15830,7 @@
         <v>SO-10482</v>
       </c>
       <c r="B483" s="1" t="d">
-        <v>2025-12-31T05:30:00.000Z</v>
+        <v>2025-12-31T00:00:00.000Z</v>
       </c>
       <c r="C483" t="str">
         <v>Nair Traders</v>
@@ -15862,7 +15862,7 @@
         <v>SO-10483</v>
       </c>
       <c r="B484" s="1" t="d">
-        <v>2026-01-02T05:30:00.000Z</v>
+        <v>2026-01-02T00:00:00.000Z</v>
       </c>
       <c r="C484" t="str">
         <v>Joshi Solutions</v>
@@ -15894,7 +15894,7 @@
         <v>SO-10484</v>
       </c>
       <c r="B485" s="1" t="d">
-        <v>2026-01-03T05:30:00.000Z</v>
+        <v>2026-01-03T00:00:00.000Z</v>
       </c>
       <c r="C485" t="str">
         <v>Rao Enterprises</v>
@@ -15926,7 +15926,7 @@
         <v>SO-10485</v>
       </c>
       <c r="B486" s="1" t="d">
-        <v>2026-01-04T05:30:00.000Z</v>
+        <v>2026-01-04T00:00:00.000Z</v>
       </c>
       <c r="C486" t="str">
         <v>Rao Retail</v>
@@ -15958,7 +15958,7 @@
         <v>SO-10486</v>
       </c>
       <c r="B487" s="1" t="d">
-        <v>2026-01-02T05:30:00.000Z</v>
+        <v>2026-01-02T00:00:00.000Z</v>
       </c>
       <c r="C487" t="str">
         <v>Patil Retail</v>
@@ -15990,7 +15990,7 @@
         <v>SO-10487</v>
       </c>
       <c r="B488" s="1" t="d">
-        <v>2026-01-05T05:30:00.000Z</v>
+        <v>2026-01-05T00:00:00.000Z</v>
       </c>
       <c r="C488" t="str">
         <v>Sharma Retail</v>
@@ -16022,7 +16022,7 @@
         <v>SO-10488</v>
       </c>
       <c r="B489" s="1" t="d">
-        <v>2026-01-06T05:30:00.000Z</v>
+        <v>2026-01-06T00:00:00.000Z</v>
       </c>
       <c r="C489" t="str">
         <v>Joshi Stores</v>
@@ -16054,7 +16054,7 @@
         <v>SO-10489</v>
       </c>
       <c r="B490" s="1" t="d">
-        <v>2026-01-04T05:30:00.000Z</v>
+        <v>2026-01-04T00:00:00.000Z</v>
       </c>
       <c r="C490" t="str">
         <v>Desai Solutions</v>
@@ -16086,7 +16086,7 @@
         <v>SO-10490</v>
       </c>
       <c r="B491" s="1" t="d">
-        <v>2026-01-06T05:30:00.000Z</v>
+        <v>2026-01-06T00:00:00.000Z</v>
       </c>
       <c r="C491" t="str">
         <v>Iyer Traders</v>
@@ -16118,7 +16118,7 @@
         <v>SO-10491</v>
       </c>
       <c r="B492" s="1" t="d">
-        <v>2026-01-06T05:30:00.000Z</v>
+        <v>2026-01-06T00:00:00.000Z</v>
       </c>
       <c r="C492" t="str">
         <v>Nair Solutions</v>
@@ -16150,7 +16150,7 @@
         <v>SO-10492</v>
       </c>
       <c r="B493" s="1" t="d">
-        <v>2026-01-06T05:30:00.000Z</v>
+        <v>2026-01-06T00:00:00.000Z</v>
       </c>
       <c r="C493" t="str">
         <v>Kulkarni Stores</v>
@@ -16182,7 +16182,7 @@
         <v>SO-10493</v>
       </c>
       <c r="B494" s="1" t="d">
-        <v>2026-01-07T05:30:00.000Z</v>
+        <v>2026-01-07T00:00:00.000Z</v>
       </c>
       <c r="C494" t="str">
         <v>Pillai Traders</v>
@@ -16214,7 +16214,7 @@
         <v>SO-10494</v>
       </c>
       <c r="B495" s="1" t="d">
-        <v>2026-01-09T05:30:00.000Z</v>
+        <v>2026-01-09T00:00:00.000Z</v>
       </c>
       <c r="C495" t="str">
         <v>Nair Labs</v>
@@ -16246,7 +16246,7 @@
         <v>SO-10495</v>
       </c>
       <c r="B496" s="1" t="d">
-        <v>2026-01-09T05:30:00.000Z</v>
+        <v>2026-01-09T00:00:00.000Z</v>
       </c>
       <c r="C496" t="str">
         <v>Iyer Enterprises</v>
@@ -16278,7 +16278,7 @@
         <v>SO-10496</v>
       </c>
       <c r="B497" s="1" t="d">
-        <v>2026-01-08T05:30:00.000Z</v>
+        <v>2026-01-08T00:00:00.000Z</v>
       </c>
       <c r="C497" t="str">
         <v>Joshi Traders</v>
@@ -16310,7 +16310,7 @@
         <v>SO-10497</v>
       </c>
       <c r="B498" s="1" t="d">
-        <v>2026-01-10T05:30:00.000Z</v>
+        <v>2026-01-10T00:00:00.000Z</v>
       </c>
       <c r="C498" t="str">
         <v>Rao Labs</v>
@@ -16342,7 +16342,7 @@
         <v>SO-10498</v>
       </c>
       <c r="B499" s="1" t="d">
-        <v>2026-01-09T05:30:00.000Z</v>
+        <v>2026-01-09T00:00:00.000Z</v>
       </c>
       <c r="C499" t="str">
         <v>Nair Traders</v>
@@ -16374,7 +16374,7 @@
         <v>SO-10499</v>
       </c>
       <c r="B500" s="1" t="d">
-        <v>2026-01-12T05:30:00.000Z</v>
+        <v>2026-01-12T00:00:00.000Z</v>
       </c>
       <c r="C500" t="str">
         <v>Desai Retail</v>
@@ -16406,7 +16406,7 @@
         <v>SO-10500</v>
       </c>
       <c r="B501" s="1" t="d">
-        <v>2026-01-12T05:30:00.000Z</v>
+        <v>2026-01-12T00:00:00.000Z</v>
       </c>
       <c r="C501" t="str">
         <v>Sharma Solutions</v>
@@ -16438,7 +16438,7 @@
         <v>SO-10501</v>
       </c>
       <c r="B502" s="1" t="d">
-        <v>2026-01-13T05:30:00.000Z</v>
+        <v>2026-01-13T00:00:00.000Z</v>
       </c>
       <c r="C502" t="str">
         <v>Sharma Traders</v>
@@ -16470,7 +16470,7 @@
         <v>SO-10502</v>
       </c>
       <c r="B503" s="1" t="d">
-        <v>2026-01-13T05:30:00.000Z</v>
+        <v>2026-01-13T00:00:00.000Z</v>
       </c>
       <c r="C503" t="str">
         <v>Sharma Retail</v>
@@ -16502,7 +16502,7 @@
         <v>SO-10503</v>
       </c>
       <c r="B504" s="1" t="d">
-        <v>2026-01-13T05:30:00.000Z</v>
+        <v>2026-01-13T00:00:00.000Z</v>
       </c>
       <c r="C504" t="str">
         <v>Pillai Retail</v>
@@ -16534,7 +16534,7 @@
         <v>SO-10504</v>
       </c>
       <c r="B505" s="1" t="d">
-        <v>2026-01-13T05:30:00.000Z</v>
+        <v>2026-01-13T00:00:00.000Z</v>
       </c>
       <c r="C505" t="str">
         <v>Kulkarni Traders</v>
@@ -16566,7 +16566,7 @@
         <v>SO-10505</v>
       </c>
       <c r="B506" s="1" t="d">
-        <v>2026-01-15T05:30:00.000Z</v>
+        <v>2026-01-15T00:00:00.000Z</v>
       </c>
       <c r="C506" t="str">
         <v>Pillai Traders</v>
@@ -16598,7 +16598,7 @@
         <v>SO-10506</v>
       </c>
       <c r="B507" s="1" t="d">
-        <v>2026-01-15T05:30:00.000Z</v>
+        <v>2026-01-15T00:00:00.000Z</v>
       </c>
       <c r="C507" t="str">
         <v>Joshi Solutions</v>
@@ -16630,7 +16630,7 @@
         <v>SO-10507</v>
       </c>
       <c r="B508" s="1" t="d">
-        <v>2026-01-15T05:30:00.000Z</v>
+        <v>2026-01-15T00:00:00.000Z</v>
       </c>
       <c r="C508" t="str">
         <v>Sharma Labs</v>
@@ -16662,7 +16662,7 @@
         <v>SO-10508</v>
       </c>
       <c r="B509" s="1" t="d">
-        <v>2026-01-15T05:30:00.000Z</v>
+        <v>2026-01-15T00:00:00.000Z</v>
       </c>
       <c r="C509" t="str">
         <v>Nair Traders</v>
@@ -16694,7 +16694,7 @@
         <v>SO-10509</v>
       </c>
       <c r="B510" s="1" t="d">
-        <v>2026-01-15T05:30:00.000Z</v>
+        <v>2026-01-15T00:00:00.000Z</v>
       </c>
       <c r="C510" t="str">
         <v>Khan Retail</v>
@@ -16726,7 +16726,7 @@
         <v>SO-10510</v>
       </c>
       <c r="B511" s="1" t="d">
-        <v>2026-01-17T05:30:00.000Z</v>
+        <v>2026-01-17T00:00:00.000Z</v>
       </c>
       <c r="C511" t="str">
         <v>Patil Retail</v>
@@ -16758,7 +16758,7 @@
         <v>SO-10511</v>
       </c>
       <c r="B512" s="1" t="d">
-        <v>2026-01-19T05:30:00.000Z</v>
+        <v>2026-01-19T00:00:00.000Z</v>
       </c>
       <c r="C512" t="str">
         <v>Nair Retail</v>
@@ -16790,7 +16790,7 @@
         <v>SO-10512</v>
       </c>
       <c r="B513" s="1" t="d">
-        <v>2026-01-20T05:30:00.000Z</v>
+        <v>2026-01-20T00:00:00.000Z</v>
       </c>
       <c r="C513" t="str">
         <v>Kulkarni Retail</v>
@@ -16822,7 +16822,7 @@
         <v>SO-10513</v>
       </c>
       <c r="B514" s="1" t="d">
-        <v>2026-01-20T05:30:00.000Z</v>
+        <v>2026-01-20T00:00:00.000Z</v>
       </c>
       <c r="C514" t="str">
         <v>Iyer Labs</v>
@@ -16854,7 +16854,7 @@
         <v>SO-10514</v>
       </c>
       <c r="B515" s="1" t="d">
-        <v>2026-01-21T05:30:00.000Z</v>
+        <v>2026-01-21T00:00:00.000Z</v>
       </c>
       <c r="C515" t="str">
         <v>Rao Stores</v>
@@ -16886,7 +16886,7 @@
         <v>SO-10515</v>
       </c>
       <c r="B516" s="1" t="d">
-        <v>2026-01-20T05:30:00.000Z</v>
+        <v>2026-01-20T00:00:00.000Z</v>
       </c>
       <c r="C516" t="str">
         <v>Rao Labs</v>
@@ -16918,7 +16918,7 @@
         <v>SO-10516</v>
       </c>
       <c r="B517" s="1" t="d">
-        <v>2026-01-20T05:30:00.000Z</v>
+        <v>2026-01-20T00:00:00.000Z</v>
       </c>
       <c r="C517" t="str">
         <v>Desai Retail</v>
@@ -16950,7 +16950,7 @@
         <v>SO-10517</v>
       </c>
       <c r="B518" s="1" t="d">
-        <v>2026-01-20T05:30:00.000Z</v>
+        <v>2026-01-20T00:00:00.000Z</v>
       </c>
       <c r="C518" t="str">
         <v>Desai Labs</v>
@@ -16982,7 +16982,7 @@
         <v>SO-10518</v>
       </c>
       <c r="B519" s="1" t="d">
-        <v>2026-01-21T05:30:00.000Z</v>
+        <v>2026-01-21T00:00:00.000Z</v>
       </c>
       <c r="C519" t="str">
         <v>Joshi Stores</v>
@@ -17014,7 +17014,7 @@
         <v>SO-10519</v>
       </c>
       <c r="B520" s="1" t="d">
-        <v>2026-01-21T05:30:00.000Z</v>
+        <v>2026-01-21T00:00:00.000Z</v>
       </c>
       <c r="C520" t="str">
         <v>Patil Stores</v>
@@ -17046,7 +17046,7 @@
         <v>SO-10520</v>
       </c>
       <c r="B521" s="1" t="d">
-        <v>2026-01-21T05:30:00.000Z</v>
+        <v>2026-01-21T00:00:00.000Z</v>
       </c>
       <c r="C521" t="str">
         <v>Joshi Traders</v>
@@ -17078,7 +17078,7 @@
         <v>SO-10521</v>
       </c>
       <c r="B522" s="1" t="d">
-        <v>2026-01-24T05:30:00.000Z</v>
+        <v>2026-01-24T00:00:00.000Z</v>
       </c>
       <c r="C522" t="str">
         <v>Kulkarni Stores</v>
@@ -17110,7 +17110,7 @@
         <v>SO-10522</v>
       </c>
       <c r="B523" s="1" t="d">
-        <v>2026-01-24T05:30:00.000Z</v>
+        <v>2026-01-24T00:00:00.000Z</v>
       </c>
       <c r="C523" t="str">
         <v>Rao Stores</v>
@@ -17142,7 +17142,7 @@
         <v>SO-10523</v>
       </c>
       <c r="B524" s="1" t="d">
-        <v>2026-01-24T05:30:00.000Z</v>
+        <v>2026-01-24T00:00:00.000Z</v>
       </c>
       <c r="C524" t="str">
         <v>Sharma Enterprises</v>
@@ -17174,7 +17174,7 @@
         <v>SO-10524</v>
       </c>
       <c r="B525" s="1" t="d">
-        <v>2026-01-24T05:30:00.000Z</v>
+        <v>2026-01-24T00:00:00.000Z</v>
       </c>
       <c r="C525" t="str">
         <v>Rao Retail</v>
@@ -17206,7 +17206,7 @@
         <v>SO-10525</v>
       </c>
       <c r="B526" s="1" t="d">
-        <v>2026-01-25T05:30:00.000Z</v>
+        <v>2026-01-25T00:00:00.000Z</v>
       </c>
       <c r="C526" t="str">
         <v>Rao Traders</v>
@@ -17238,7 +17238,7 @@
         <v>SO-10526</v>
       </c>
       <c r="B527" s="1" t="d">
-        <v>2026-01-26T05:30:00.000Z</v>
+        <v>2026-01-26T00:00:00.000Z</v>
       </c>
       <c r="C527" t="str">
         <v>Desai Stores</v>
@@ -17270,7 +17270,7 @@
         <v>SO-10527</v>
       </c>
       <c r="B528" s="1" t="d">
-        <v>2026-01-28T05:30:00.000Z</v>
+        <v>2026-01-28T00:00:00.000Z</v>
       </c>
       <c r="C528" t="str">
         <v>Sharma Solutions</v>
@@ -17302,7 +17302,7 @@
         <v>SO-10528</v>
       </c>
       <c r="B529" s="1" t="d">
-        <v>2026-01-27T05:30:00.000Z</v>
+        <v>2026-01-27T00:00:00.000Z</v>
       </c>
       <c r="C529" t="str">
         <v>Kulkarni Retail</v>
@@ -17334,7 +17334,7 @@
         <v>SO-10529</v>
       </c>
       <c r="B530" s="1" t="d">
-        <v>2026-01-28T05:30:00.000Z</v>
+        <v>2026-01-28T00:00:00.000Z</v>
       </c>
       <c r="C530" t="str">
         <v>Mehta Stores</v>
@@ -17366,7 +17366,7 @@
         <v>SO-10530</v>
       </c>
       <c r="B531" s="1" t="d">
-        <v>2026-01-28T05:30:00.000Z</v>
+        <v>2026-01-28T00:00:00.000Z</v>
       </c>
       <c r="C531" t="str">
         <v>Sharma Enterprises</v>
@@ -17398,7 +17398,7 @@
         <v>SO-10531</v>
       </c>
       <c r="B532" s="1" t="d">
-        <v>2026-01-28T05:30:00.000Z</v>
+        <v>2026-01-28T00:00:00.000Z</v>
       </c>
       <c r="C532" t="str">
         <v>Rao Retail</v>
@@ -17430,7 +17430,7 @@
         <v>SO-10532</v>
       </c>
       <c r="B533" s="1" t="d">
-        <v>2026-01-30T05:30:00.000Z</v>
+        <v>2026-01-30T00:00:00.000Z</v>
       </c>
       <c r="C533" t="str">
         <v>Iyer Stores</v>
@@ -17462,7 +17462,7 @@
         <v>SO-10533</v>
       </c>
       <c r="B534" s="1" t="d">
-        <v>2026-01-31T05:30:00.000Z</v>
+        <v>2026-01-31T00:00:00.000Z</v>
       </c>
       <c r="C534" t="str">
         <v>Rao Traders</v>
@@ -17494,7 +17494,7 @@
         <v>SO-10534</v>
       </c>
       <c r="B535" s="1" t="d">
-        <v>2026-02-01T05:30:00.000Z</v>
+        <v>2026-02-01T00:00:00.000Z</v>
       </c>
       <c r="C535" t="str">
         <v>Desai Retail</v>
@@ -17526,7 +17526,7 @@
         <v>SO-10535</v>
       </c>
       <c r="B536" s="1" t="d">
-        <v>2026-01-30T05:30:00.000Z</v>
+        <v>2026-01-30T00:00:00.000Z</v>
       </c>
       <c r="C536" t="str">
         <v>Sharma Enterprises</v>
@@ -17558,7 +17558,7 @@
         <v>SO-10536</v>
       </c>
       <c r="B537" s="1" t="d">
-        <v>2026-02-01T05:30:00.000Z</v>
+        <v>2026-02-01T00:00:00.000Z</v>
       </c>
       <c r="C537" t="str">
         <v>Mehta Stores</v>
@@ -17590,7 +17590,7 @@
         <v>SO-10537</v>
       </c>
       <c r="B538" s="1" t="d">
-        <v>2026-02-01T05:30:00.000Z</v>
+        <v>2026-02-01T00:00:00.000Z</v>
       </c>
       <c r="C538" t="str">
         <v>Kulkarni Stores</v>
@@ -17622,7 +17622,7 @@
         <v>SO-10538</v>
       </c>
       <c r="B539" s="1" t="d">
-        <v>2026-02-02T05:30:00.000Z</v>
+        <v>2026-02-02T00:00:00.000Z</v>
       </c>
       <c r="C539" t="str">
         <v>Gupta Stores</v>
@@ -17654,7 +17654,7 @@
         <v>SO-10539</v>
       </c>
       <c r="B540" s="1" t="d">
-        <v>2026-02-02T05:30:00.000Z</v>
+        <v>2026-02-02T00:00:00.000Z</v>
       </c>
       <c r="C540" t="str">
         <v>Patil Labs</v>
@@ -17686,7 +17686,7 @@
         <v>SO-10540</v>
       </c>
       <c r="B541" s="1" t="d">
-        <v>2026-02-04T05:30:00.000Z</v>
+        <v>2026-02-04T00:00:00.000Z</v>
       </c>
       <c r="C541" t="str">
         <v>Patil Retail</v>
@@ -17718,7 +17718,7 @@
         <v>SO-10541</v>
       </c>
       <c r="B542" s="1" t="d">
-        <v>2026-02-05T05:30:00.000Z</v>
+        <v>2026-02-05T00:00:00.000Z</v>
       </c>
       <c r="C542" t="str">
         <v>Joshi Labs</v>
@@ -17750,7 +17750,7 @@
         <v>SO-10542</v>
       </c>
       <c r="B543" s="1" t="d">
-        <v>2026-02-05T05:30:00.000Z</v>
+        <v>2026-02-05T00:00:00.000Z</v>
       </c>
       <c r="C543" t="str">
         <v>Rao Solutions</v>
@@ -17782,7 +17782,7 @@
         <v>SO-10543</v>
       </c>
       <c r="B544" s="1" t="d">
-        <v>2026-02-04T05:30:00.000Z</v>
+        <v>2026-02-04T00:00:00.000Z</v>
       </c>
       <c r="C544" t="str">
         <v>Gupta Stores</v>
@@ -17814,7 +17814,7 @@
         <v>SO-10544</v>
       </c>
       <c r="B545" s="1" t="d">
-        <v>2026-02-05T05:30:00.000Z</v>
+        <v>2026-02-05T00:00:00.000Z</v>
       </c>
       <c r="C545" t="str">
         <v>Sharma Traders</v>
@@ -17846,7 +17846,7 @@
         <v>SO-10545</v>
       </c>
       <c r="B546" s="1" t="d">
-        <v>2026-02-06T05:30:00.000Z</v>
+        <v>2026-02-06T00:00:00.000Z</v>
       </c>
       <c r="C546" t="str">
         <v>Kulkarni Retail</v>
@@ -17878,7 +17878,7 @@
         <v>SO-10546</v>
       </c>
       <c r="B547" s="1" t="d">
-        <v>2026-02-06T05:30:00.000Z</v>
+        <v>2026-02-06T00:00:00.000Z</v>
       </c>
       <c r="C547" t="str">
         <v>Rao Stores</v>
@@ -17910,7 +17910,7 @@
         <v>SO-10547</v>
       </c>
       <c r="B548" s="1" t="d">
-        <v>2026-02-08T05:30:00.000Z</v>
+        <v>2026-02-08T00:00:00.000Z</v>
       </c>
       <c r="C548" t="str">
         <v>Patil Retail</v>
@@ -17942,7 +17942,7 @@
         <v>SO-10548</v>
       </c>
       <c r="B549" s="1" t="d">
-        <v>2026-02-09T05:30:00.000Z</v>
+        <v>2026-02-09T00:00:00.000Z</v>
       </c>
       <c r="C549" t="str">
         <v>Desai Retail</v>
@@ -17974,7 +17974,7 @@
         <v>SO-10549</v>
       </c>
       <c r="B550" s="1" t="d">
-        <v>2026-02-10T05:30:00.000Z</v>
+        <v>2026-02-10T00:00:00.000Z</v>
       </c>
       <c r="C550" t="str">
         <v>Iyer Traders</v>
@@ -18006,7 +18006,7 @@
         <v>SO-10550</v>
       </c>
       <c r="B551" s="1" t="d">
-        <v>2026-02-09T05:30:00.000Z</v>
+        <v>2026-02-09T00:00:00.000Z</v>
       </c>
       <c r="C551" t="str">
         <v>Kulkarni Enterprises</v>
@@ -18038,7 +18038,7 @@
         <v>SO-10551</v>
       </c>
       <c r="B552" s="1" t="d">
-        <v>2026-02-09T05:30:00.000Z</v>
+        <v>2026-02-09T00:00:00.000Z</v>
       </c>
       <c r="C552" t="str">
         <v>Patil Labs</v>
@@ -18070,7 +18070,7 @@
         <v>SO-10552</v>
       </c>
       <c r="B553" s="1" t="d">
-        <v>2026-02-11T05:30:00.000Z</v>
+        <v>2026-02-11T00:00:00.000Z</v>
       </c>
       <c r="C553" t="str">
         <v>Patil Traders</v>
@@ -18102,7 +18102,7 @@
         <v>SO-10553</v>
       </c>
       <c r="B554" s="1" t="d">
-        <v>2026-02-09T05:30:00.000Z</v>
+        <v>2026-02-09T00:00:00.000Z</v>
       </c>
       <c r="C554" t="str">
         <v>Pillai Stores</v>
@@ -18134,7 +18134,7 @@
         <v>SO-10554</v>
       </c>
       <c r="B555" s="1" t="d">
-        <v>2026-02-12T05:30:00.000Z</v>
+        <v>2026-02-12T00:00:00.000Z</v>
       </c>
       <c r="C555" t="str">
         <v>Nair Stores</v>
@@ -18166,7 +18166,7 @@
         <v>SO-10555</v>
       </c>
       <c r="B556" s="1" t="d">
-        <v>2026-02-12T05:30:00.000Z</v>
+        <v>2026-02-12T00:00:00.000Z</v>
       </c>
       <c r="C556" t="str">
         <v>Joshi Enterprises</v>
@@ -18198,7 +18198,7 @@
         <v>SO-10556</v>
       </c>
       <c r="B557" s="1" t="d">
-        <v>2026-02-13T05:30:00.000Z</v>
+        <v>2026-02-13T00:00:00.000Z</v>
       </c>
       <c r="C557" t="str">
         <v>Sharma Solutions</v>
@@ -18230,7 +18230,7 @@
         <v>SO-10557</v>
       </c>
       <c r="B558" s="1" t="d">
-        <v>2026-02-13T05:30:00.000Z</v>
+        <v>2026-02-13T00:00:00.000Z</v>
       </c>
       <c r="C558" t="str">
         <v>Sharma Solutions</v>
@@ -18262,7 +18262,7 @@
         <v>SO-10558</v>
       </c>
       <c r="B559" s="1" t="d">
-        <v>2026-02-14T05:30:00.000Z</v>
+        <v>2026-02-14T00:00:00.000Z</v>
       </c>
       <c r="C559" t="str">
         <v>Khan Traders</v>
@@ -18294,7 +18294,7 @@
         <v>SO-10559</v>
       </c>
       <c r="B560" s="1" t="d">
-        <v>2026-02-15T05:30:00.000Z</v>
+        <v>2026-02-15T00:00:00.000Z</v>
       </c>
       <c r="C560" t="str">
         <v>Desai Retail</v>
@@ -18326,7 +18326,7 @@
         <v>SO-10560</v>
       </c>
       <c r="B561" s="1" t="d">
-        <v>2026-02-15T05:30:00.000Z</v>
+        <v>2026-02-15T00:00:00.000Z</v>
       </c>
       <c r="C561" t="str">
         <v>Joshi Labs</v>
@@ -18358,7 +18358,7 @@
         <v>SO-10561</v>
       </c>
       <c r="B562" s="1" t="d">
-        <v>2026-02-16T05:30:00.000Z</v>
+        <v>2026-02-16T00:00:00.000Z</v>
       </c>
       <c r="C562" t="str">
         <v>Joshi Solutions</v>
@@ -18390,7 +18390,7 @@
         <v>SO-10562</v>
       </c>
       <c r="B563" s="1" t="d">
-        <v>2026-02-16T05:30:00.000Z</v>
+        <v>2026-02-16T00:00:00.000Z</v>
       </c>
       <c r="C563" t="str">
         <v>Mehta Enterprises</v>
@@ -18422,7 +18422,7 @@
         <v>SO-10563</v>
       </c>
       <c r="B564" s="1" t="d">
-        <v>2026-02-17T05:30:00.000Z</v>
+        <v>2026-02-17T00:00:00.000Z</v>
       </c>
       <c r="C564" t="str">
         <v>Desai Labs</v>
@@ -18454,7 +18454,7 @@
         <v>SO-10564</v>
       </c>
       <c r="B565" s="1" t="d">
-        <v>2026-02-17T05:30:00.000Z</v>
+        <v>2026-02-17T00:00:00.000Z</v>
       </c>
       <c r="C565" t="str">
         <v>Patil Enterprises</v>
@@ -18486,7 +18486,7 @@
         <v>SO-10565</v>
       </c>
       <c r="B566" s="1" t="d">
-        <v>2026-02-17T05:30:00.000Z</v>
+        <v>2026-02-17T00:00:00.000Z</v>
       </c>
       <c r="C566" t="str">
         <v>Pillai Retail</v>
@@ -18518,7 +18518,7 @@
         <v>SO-10566</v>
       </c>
       <c r="B567" s="1" t="d">
-        <v>2026-02-18T05:30:00.000Z</v>
+        <v>2026-02-18T00:00:00.000Z</v>
       </c>
       <c r="C567" t="str">
         <v>Iyer Traders</v>
@@ -18550,7 +18550,7 @@
         <v>SO-10567</v>
       </c>
       <c r="B568" s="1" t="d">
-        <v>2026-02-17T05:30:00.000Z</v>
+        <v>2026-02-17T00:00:00.000Z</v>
       </c>
       <c r="C568" t="str">
         <v>Sharma Retail</v>
@@ -18582,7 +18582,7 @@
         <v>SO-10568</v>
       </c>
       <c r="B569" s="1" t="d">
-        <v>2026-02-19T05:30:00.000Z</v>
+        <v>2026-02-19T00:00:00.000Z</v>
       </c>
       <c r="C569" t="str">
         <v>Desai Stores</v>
@@ -18614,7 +18614,7 @@
         <v>SO-10569</v>
       </c>
       <c r="B570" s="1" t="d">
-        <v>2026-02-19T05:30:00.000Z</v>
+        <v>2026-02-19T00:00:00.000Z</v>
       </c>
       <c r="C570" t="str">
         <v>Joshi Traders</v>
@@ -18646,7 +18646,7 @@
         <v>SO-10570</v>
       </c>
       <c r="B571" s="1" t="d">
-        <v>2026-02-22T05:30:00.000Z</v>
+        <v>2026-02-22T00:00:00.000Z</v>
       </c>
       <c r="C571" t="str">
         <v>Sharma Traders</v>
@@ -18678,7 +18678,7 @@
         <v>SO-10571</v>
       </c>
       <c r="B572" s="1" t="d">
-        <v>2026-02-21T05:30:00.000Z</v>
+        <v>2026-02-21T00:00:00.000Z</v>
       </c>
       <c r="C572" t="str">
         <v>Joshi Stores</v>
@@ -18710,7 +18710,7 @@
         <v>SO-10572</v>
       </c>
       <c r="B573" s="1" t="d">
-        <v>2026-02-21T05:30:00.000Z</v>
+        <v>2026-02-21T00:00:00.000Z</v>
       </c>
       <c r="C573" t="str">
         <v>Khan Stores</v>
@@ -18742,7 +18742,7 @@
         <v>SO-10573</v>
       </c>
       <c r="B574" s="1" t="d">
-        <v>2026-02-22T05:30:00.000Z</v>
+        <v>2026-02-22T00:00:00.000Z</v>
       </c>
       <c r="C574" t="str">
         <v>Sharma Enterprises</v>
@@ -18774,7 +18774,7 @@
         <v>SO-10574</v>
       </c>
       <c r="B575" s="1" t="d">
-        <v>2026-02-22T05:30:00.000Z</v>
+        <v>2026-02-22T00:00:00.000Z</v>
       </c>
       <c r="C575" t="str">
         <v>Patil Stores</v>
@@ -18806,7 +18806,7 @@
         <v>SO-10575</v>
       </c>
       <c r="B576" s="1" t="d">
-        <v>2026-02-25T05:30:00.000Z</v>
+        <v>2026-02-25T00:00:00.000Z</v>
       </c>
       <c r="C576" t="str">
         <v>Sharma Retail</v>
@@ -18838,7 +18838,7 @@
         <v>SO-10576</v>
       </c>
       <c r="B577" s="1" t="d">
-        <v>2026-02-25T05:30:00.000Z</v>
+        <v>2026-02-25T00:00:00.000Z</v>
       </c>
       <c r="C577" t="str">
         <v>Joshi Retail</v>
@@ -18870,7 +18870,7 @@
         <v>SO-10577</v>
       </c>
       <c r="B578" s="1" t="d">
-        <v>2026-02-25T05:30:00.000Z</v>
+        <v>2026-02-25T00:00:00.000Z</v>
       </c>
       <c r="C578" t="str">
         <v>Desai Solutions</v>
@@ -18902,7 +18902,7 @@
         <v>SO-10578</v>
       </c>
       <c r="B579" s="1" t="d">
-        <v>2026-02-24T05:30:00.000Z</v>
+        <v>2026-02-24T00:00:00.000Z</v>
       </c>
       <c r="C579" t="str">
         <v>Rao Solutions</v>
@@ -18934,7 +18934,7 @@
         <v>SO-10579</v>
       </c>
       <c r="B580" s="1" t="d">
-        <v>2026-02-25T05:30:00.000Z</v>
+        <v>2026-02-25T00:00:00.000Z</v>
       </c>
       <c r="C580" t="str">
         <v>Nair Labs</v>
@@ -18966,7 +18966,7 @@
         <v>SO-10580</v>
       </c>
       <c r="B581" s="1" t="d">
-        <v>2026-02-28T05:30:00.000Z</v>
+        <v>2026-02-28T00:00:00.000Z</v>
       </c>
       <c r="C581" t="str">
         <v>Desai Labs</v>
@@ -18998,7 +18998,7 @@
         <v>SO-10581</v>
       </c>
       <c r="B582" s="1" t="d">
-        <v>2026-02-28T05:30:00.000Z</v>
+        <v>2026-02-28T00:00:00.000Z</v>
       </c>
       <c r="C582" t="str">
         <v>Desai Stores</v>
@@ -19030,7 +19030,7 @@
         <v>SO-10582</v>
       </c>
       <c r="B583" s="1" t="d">
-        <v>2026-02-26T05:30:00.000Z</v>
+        <v>2026-02-26T00:00:00.000Z</v>
       </c>
       <c r="C583" t="str">
         <v>Sharma Solutions</v>
@@ -19062,7 +19062,7 @@
         <v>SO-10583</v>
       </c>
       <c r="B584" s="1" t="d">
-        <v>2026-03-01T05:30:00.000Z</v>
+        <v>2026-03-01T00:00:00.000Z</v>
       </c>
       <c r="C584" t="str">
         <v>Kulkarni Labs</v>
@@ -19094,7 +19094,7 @@
         <v>SO-10584</v>
       </c>
       <c r="B585" s="1" t="d">
-        <v>2026-02-28T05:30:00.000Z</v>
+        <v>2026-02-28T00:00:00.000Z</v>
       </c>
       <c r="C585" t="str">
         <v>Kulkarni Labs</v>
@@ -19126,7 +19126,7 @@
         <v>SO-10585</v>
       </c>
       <c r="B586" s="1" t="d">
-        <v>2026-03-02T05:30:00.000Z</v>
+        <v>2026-03-02T00:00:00.000Z</v>
       </c>
       <c r="C586" t="str">
         <v>Rao Labs</v>
@@ -19158,7 +19158,7 @@
         <v>SO-10586</v>
       </c>
       <c r="B587" s="1" t="d">
-        <v>2026-03-01T05:30:00.000Z</v>
+        <v>2026-03-01T00:00:00.000Z</v>
       </c>
       <c r="C587" t="str">
         <v>Rao Labs</v>
@@ -19190,7 +19190,7 @@
         <v>SO-10587</v>
       </c>
       <c r="B588" s="1" t="d">
-        <v>2026-03-03T05:30:00.000Z</v>
+        <v>2026-03-03T00:00:00.000Z</v>
       </c>
       <c r="C588" t="str">
         <v>Nair Stores</v>
@@ -19222,7 +19222,7 @@
         <v>SO-10588</v>
       </c>
       <c r="B589" s="1" t="d">
-        <v>2026-03-04T05:30:00.000Z</v>
+        <v>2026-03-04T00:00:00.000Z</v>
       </c>
       <c r="C589" t="str">
         <v>Kulkarni Traders</v>
@@ -19254,7 +19254,7 @@
         <v>SO-10589</v>
       </c>
       <c r="B590" s="1" t="d">
-        <v>2026-03-04T05:30:00.000Z</v>
+        <v>2026-03-04T00:00:00.000Z</v>
       </c>
       <c r="C590" t="str">
         <v>Joshi Traders</v>
@@ -19286,7 +19286,7 @@
         <v>SO-10590</v>
       </c>
       <c r="B591" s="1" t="d">
-        <v>2026-03-03T05:30:00.000Z</v>
+        <v>2026-03-03T00:00:00.000Z</v>
       </c>
       <c r="C591" t="str">
         <v>Rao Enterprises</v>
@@ -19318,7 +19318,7 @@
         <v>SO-10591</v>
       </c>
       <c r="B592" s="1" t="d">
-        <v>2026-03-05T05:30:00.000Z</v>
+        <v>2026-03-05T00:00:00.000Z</v>
       </c>
       <c r="C592" t="str">
         <v>Joshi Solutions</v>
@@ -19350,7 +19350,7 @@
         <v>SO-10592</v>
       </c>
       <c r="B593" s="1" t="d">
-        <v>2026-03-06T05:30:00.000Z</v>
+        <v>2026-03-06T00:00:00.000Z</v>
       </c>
       <c r="C593" t="str">
         <v>Patil Traders</v>
@@ -19382,7 +19382,7 @@
         <v>SO-10593</v>
       </c>
       <c r="B594" s="1" t="d">
-        <v>2026-03-04T05:30:00.000Z</v>
+        <v>2026-03-04T00:00:00.000Z</v>
       </c>
       <c r="C594" t="str">
         <v>Joshi Traders</v>
@@ -19414,7 +19414,7 @@
         <v>SO-10594</v>
       </c>
       <c r="B595" s="1" t="d">
-        <v>2026-03-05T05:30:00.000Z</v>
+        <v>2026-03-05T00:00:00.000Z</v>
       </c>
       <c r="C595" t="str">
         <v>Desai Labs</v>
@@ -19446,7 +19446,7 @@
         <v>SO-10595</v>
       </c>
       <c r="B596" s="1" t="d">
-        <v>2026-03-07T05:30:00.000Z</v>
+        <v>2026-03-07T00:00:00.000Z</v>
       </c>
       <c r="C596" t="str">
         <v>Kulkarni Stores</v>
@@ -19478,7 +19478,7 @@
         <v>SO-10596</v>
       </c>
       <c r="B597" s="1" t="d">
-        <v>2026-03-07T05:30:00.000Z</v>
+        <v>2026-03-07T00:00:00.000Z</v>
       </c>
       <c r="C597" t="str">
         <v>Khan Retail</v>
@@ -19510,7 +19510,7 @@
         <v>SO-10597</v>
       </c>
       <c r="B598" s="1" t="d">
-        <v>2026-03-08T05:30:00.000Z</v>
+        <v>2026-03-08T00:00:00.000Z</v>
       </c>
       <c r="C598" t="str">
         <v>Mehta Stores</v>
@@ -19542,7 +19542,7 @@
         <v>SO-10598</v>
       </c>
       <c r="B599" s="1" t="d">
-        <v>2026-03-08T05:30:00.000Z</v>
+        <v>2026-03-08T00:00:00.000Z</v>
       </c>
       <c r="C599" t="str">
         <v>Sharma Enterprises</v>
@@ -19574,7 +19574,7 @@
         <v>SO-10599</v>
       </c>
       <c r="B600" s="1" t="d">
-        <v>2026-03-09T05:30:00.000Z</v>
+        <v>2026-03-09T00:00:00.000Z</v>
       </c>
       <c r="C600" t="str">
         <v>Nair Retail</v>
@@ -19606,7 +19606,7 @@
         <v>SO-10600</v>
       </c>
       <c r="B601" s="1" t="d">
-        <v>2026-03-10T05:30:00.000Z</v>
+        <v>2026-03-10T00:00:00.000Z</v>
       </c>
       <c r="C601" t="str">
         <v>Sharma Solutions</v>
@@ -19638,7 +19638,7 @@
         <v>SO-10601</v>
       </c>
       <c r="B602" s="1" t="d">
-        <v>2026-03-11T05:30:00.000Z</v>
+        <v>2026-03-11T00:00:00.000Z</v>
       </c>
       <c r="C602" t="str">
         <v>Desai Enterprises</v>
@@ -19670,7 +19670,7 @@
         <v>SO-10602</v>
       </c>
       <c r="B603" s="1" t="d">
-        <v>2026-03-11T05:30:00.000Z</v>
+        <v>2026-03-11T00:00:00.000Z</v>
       </c>
       <c r="C603" t="str">
         <v>Rao Traders</v>
@@ -19702,7 +19702,7 @@
         <v>SO-10603</v>
       </c>
       <c r="B604" s="1" t="d">
-        <v>2026-03-10T05:30:00.000Z</v>
+        <v>2026-03-10T00:00:00.000Z</v>
       </c>
       <c r="C604" t="str">
         <v>Nair Traders</v>
@@ -19734,7 +19734,7 @@
         <v>SO-10604</v>
       </c>
       <c r="B605" s="1" t="d">
-        <v>2026-03-12T05:30:00.000Z</v>
+        <v>2026-03-12T00:00:00.000Z</v>
       </c>
       <c r="C605" t="str">
         <v>Sharma Labs</v>
@@ -19766,7 +19766,7 @@
         <v>SO-10605</v>
       </c>
       <c r="B606" s="1" t="d">
-        <v>2026-03-13T05:30:00.000Z</v>
+        <v>2026-03-13T00:00:00.000Z</v>
       </c>
       <c r="C606" t="str">
         <v>Patil Enterprises</v>
@@ -19798,7 +19798,7 @@
         <v>SO-10606</v>
       </c>
       <c r="B607" s="1" t="d">
-        <v>2026-03-12T05:30:00.000Z</v>
+        <v>2026-03-12T00:00:00.000Z</v>
       </c>
       <c r="C607" t="str">
         <v>Desai Labs</v>
@@ -19830,7 +19830,7 @@
         <v>SO-10607</v>
       </c>
       <c r="B608" s="1" t="d">
-        <v>2026-03-15T05:30:00.000Z</v>
+        <v>2026-03-15T00:00:00.000Z</v>
       </c>
       <c r="C608" t="str">
         <v>Khan Retail</v>
@@ -19862,7 +19862,7 @@
         <v>SO-10608</v>
       </c>
       <c r="B609" s="1" t="d">
-        <v>2026-03-14T05:30:00.000Z</v>
+        <v>2026-03-14T00:00:00.000Z</v>
       </c>
       <c r="C609" t="str">
         <v>Patil Retail</v>
@@ -19894,7 +19894,7 @@
         <v>SO-10609</v>
       </c>
       <c r="B610" s="1" t="d">
-        <v>2026-03-14T05:30:00.000Z</v>
+        <v>2026-03-14T00:00:00.000Z</v>
       </c>
       <c r="C610" t="str">
         <v>Joshi Labs</v>
@@ -19926,7 +19926,7 @@
         <v>SO-10610</v>
       </c>
       <c r="B611" s="1" t="d">
-        <v>2026-03-15T05:30:00.000Z</v>
+        <v>2026-03-15T00:00:00.000Z</v>
       </c>
       <c r="C611" t="str">
         <v>Gupta Stores</v>
@@ -19958,7 +19958,7 @@
         <v>SO-10611</v>
       </c>
       <c r="B612" s="1" t="d">
-        <v>2026-03-15T05:30:00.000Z</v>
+        <v>2026-03-15T00:00:00.000Z</v>
       </c>
       <c r="C612" t="str">
         <v>Sharma Traders</v>
@@ -19990,7 +19990,7 @@
         <v>SO-10612</v>
       </c>
       <c r="B613" s="1" t="d">
-        <v>2026-03-17T05:30:00.000Z</v>
+        <v>2026-03-17T00:00:00.000Z</v>
       </c>
       <c r="C613" t="str">
         <v>Patil Stores</v>
@@ -20022,7 +20022,7 @@
         <v>SO-10613</v>
       </c>
       <c r="B614" s="1" t="d">
-        <v>2026-03-17T05:30:00.000Z</v>
+        <v>2026-03-17T00:00:00.000Z</v>
       </c>
       <c r="C614" t="str">
         <v>Patil Traders</v>
@@ -20054,7 +20054,7 @@
         <v>SO-10614</v>
       </c>
       <c r="B615" s="1" t="d">
-        <v>2026-03-19T05:30:00.000Z</v>
+        <v>2026-03-19T00:00:00.000Z</v>
       </c>
       <c r="C615" t="str">
         <v>Sharma Traders</v>
@@ -20086,7 +20086,7 @@
         <v>SO-10615</v>
       </c>
       <c r="B616" s="1" t="d">
-        <v>2026-03-17T05:30:00.000Z</v>
+        <v>2026-03-17T00:00:00.000Z</v>
       </c>
       <c r="C616" t="str">
         <v>Sharma Retail</v>
@@ -20118,7 +20118,7 @@
         <v>SO-10616</v>
       </c>
       <c r="B617" s="1" t="d">
-        <v>2026-03-19T05:30:00.000Z</v>
+        <v>2026-03-19T00:00:00.000Z</v>
       </c>
       <c r="C617" t="str">
         <v>Sharma Solutions</v>
@@ -20150,7 +20150,7 @@
         <v>SO-10617</v>
       </c>
       <c r="B618" s="1" t="d">
-        <v>2026-03-20T05:30:00.000Z</v>
+        <v>2026-03-20T00:00:00.000Z</v>
       </c>
       <c r="C618" t="str">
         <v>Iyer Stores</v>
@@ -20182,7 +20182,7 @@
         <v>SO-10618</v>
       </c>
       <c r="B619" s="1" t="d">
-        <v>2026-03-20T05:30:00.000Z</v>
+        <v>2026-03-20T00:00:00.000Z</v>
       </c>
       <c r="C619" t="str">
         <v>Pillai Stores</v>
@@ -20214,7 +20214,7 @@
         <v>SO-10619</v>
       </c>
       <c r="B620" s="1" t="d">
-        <v>2026-03-19T05:30:00.000Z</v>
+        <v>2026-03-19T00:00:00.000Z</v>
       </c>
       <c r="C620" t="str">
         <v>Nair Enterprises</v>
@@ -20246,7 +20246,7 @@
         <v>SO-10620</v>
       </c>
       <c r="B621" s="1" t="d">
-        <v>2026-03-22T05:30:00.000Z</v>
+        <v>2026-03-22T00:00:00.000Z</v>
       </c>
       <c r="C621" t="str">
         <v>Sharma Retail</v>
@@ -20278,7 +20278,7 @@
         <v>SO-10621</v>
       </c>
       <c r="B622" s="1" t="d">
-        <v>2026-03-20T05:30:00.000Z</v>
+        <v>2026-03-20T00:00:00.000Z</v>
       </c>
       <c r="C622" t="str">
         <v>Pillai Solutions</v>
@@ -20310,7 +20310,7 @@
         <v>SO-10622</v>
       </c>
       <c r="B623" s="1" t="d">
-        <v>2026-03-22T05:30:00.000Z</v>
+        <v>2026-03-22T00:00:00.000Z</v>
       </c>
       <c r="C623" t="str">
         <v>Rao Enterprises</v>
@@ -20342,7 +20342,7 @@
         <v>SO-10623</v>
       </c>
       <c r="B624" s="1" t="d">
-        <v>2026-03-23T05:30:00.000Z</v>
+        <v>2026-03-23T00:00:00.000Z</v>
       </c>
       <c r="C624" t="str">
         <v>Kulkarni Stores</v>
@@ -20374,7 +20374,7 @@
         <v>SO-10624</v>
       </c>
       <c r="B625" s="1" t="d">
-        <v>2026-03-23T05:30:00.000Z</v>
+        <v>2026-03-23T00:00:00.000Z</v>
       </c>
       <c r="C625" t="str">
         <v>Khan Enterprises</v>
@@ -20406,7 +20406,7 @@
         <v>SO-10625</v>
       </c>
       <c r="B626" s="1" t="d">
-        <v>2026-03-23T05:30:00.000Z</v>
+        <v>2026-03-23T00:00:00.000Z</v>
       </c>
       <c r="C626" t="str">
         <v>Patil Stores</v>
@@ -20438,7 +20438,7 @@
         <v>SO-10626</v>
       </c>
       <c r="B627" s="1" t="d">
-        <v>2026-03-25T05:30:00.000Z</v>
+        <v>2026-03-25T00:00:00.000Z</v>
       </c>
       <c r="C627" t="str">
         <v>Khan Enterprises</v>
@@ -20470,7 +20470,7 @@
         <v>SO-10627</v>
       </c>
       <c r="B628" s="1" t="d">
-        <v>2026-03-25T05:30:00.000Z</v>
+        <v>2026-03-25T00:00:00.000Z</v>
       </c>
       <c r="C628" t="str">
         <v>Joshi Retail</v>
@@ -20502,7 +20502,7 @@
         <v>SO-10628</v>
       </c>
       <c r="B629" s="1" t="d">
-        <v>2026-03-25T05:30:00.000Z</v>
+        <v>2026-03-25T00:00:00.000Z</v>
       </c>
       <c r="C629" t="str">
         <v>Joshi Stores</v>
@@ -20534,7 +20534,7 @@
         <v>SO-10629</v>
       </c>
       <c r="B630" s="1" t="d">
-        <v>2026-03-26T05:30:00.000Z</v>
+        <v>2026-03-26T00:00:00.000Z</v>
       </c>
       <c r="C630" t="str">
         <v>Sharma Enterprises</v>
@@ -20566,7 +20566,7 @@
         <v>SO-10630</v>
       </c>
       <c r="B631" s="1" t="d">
-        <v>2026-03-27T05:30:00.000Z</v>
+        <v>2026-03-27T00:00:00.000Z</v>
       </c>
       <c r="C631" t="str">
         <v>Iyer Traders</v>
@@ -20598,7 +20598,7 @@
         <v>SO-10631</v>
       </c>
       <c r="B632" s="1" t="d">
-        <v>2026-03-26T05:30:00.000Z</v>
+        <v>2026-03-26T00:00:00.000Z</v>
       </c>
       <c r="C632" t="str">
         <v>Nair Enterprises</v>
@@ -20630,7 +20630,7 @@
         <v>SO-10632</v>
       </c>
       <c r="B633" s="1" t="d">
-        <v>2026-03-29T05:30:00.000Z</v>
+        <v>2026-03-29T00:00:00.000Z</v>
       </c>
       <c r="C633" t="str">
         <v>Iyer Traders</v>
@@ -20662,7 +20662,7 @@
         <v>SO-10633</v>
       </c>
       <c r="B634" s="1" t="d">
-        <v>2026-03-29T05:30:00.000Z</v>
+        <v>2026-03-29T00:00:00.000Z</v>
       </c>
       <c r="C634" t="str">
         <v>Patil Stores</v>
@@ -20694,7 +20694,7 @@
         <v>SO-10634</v>
       </c>
       <c r="B635" s="1" t="d">
-        <v>2026-03-30T05:30:00.000Z</v>
+        <v>2026-03-30T00:00:00.000Z</v>
       </c>
       <c r="C635" t="str">
         <v>Iyer Enterprises</v>
@@ -20726,7 +20726,7 @@
         <v>SO-10635</v>
       </c>
       <c r="B636" s="1" t="d">
-        <v>2026-03-29T05:30:00.000Z</v>
+        <v>2026-03-29T00:00:00.000Z</v>
       </c>
       <c r="C636" t="str">
         <v>Khan Solutions</v>
@@ -20758,7 +20758,7 @@
         <v>SO-10636</v>
       </c>
       <c r="B637" s="1" t="d">
-        <v>2026-03-31T05:30:00.000Z</v>
+        <v>2026-03-31T00:00:00.000Z</v>
       </c>
       <c r="C637" t="str">
         <v>Pillai Traders</v>
@@ -20790,7 +20790,7 @@
         <v>SO-10637</v>
       </c>
       <c r="B638" s="1" t="d">
-        <v>2026-03-29T05:30:00.000Z</v>
+        <v>2026-03-29T00:00:00.000Z</v>
       </c>
       <c r="C638" t="str">
         <v>Iyer Traders</v>
@@ -20822,7 +20822,7 @@
         <v>SO-10638</v>
       </c>
       <c r="B639" s="1" t="d">
-        <v>2026-03-31T05:30:00.000Z</v>
+        <v>2026-03-31T00:00:00.000Z</v>
       </c>
       <c r="C639" t="str">
         <v>Mehta Traders</v>
@@ -20854,7 +20854,7 @@
         <v>SO-10639</v>
       </c>
       <c r="B640" s="1" t="d">
-        <v>2026-03-31T05:30:00.000Z</v>
+        <v>2026-03-31T00:00:00.000Z</v>
       </c>
       <c r="C640" t="str">
         <v>Desai Solutions</v>
@@ -20886,7 +20886,7 @@
         <v>SO-10640</v>
       </c>
       <c r="B641" s="1" t="d">
-        <v>2026-03-31T05:30:00.000Z</v>
+        <v>2026-03-31T00:00:00.000Z</v>
       </c>
       <c r="C641" t="str">
         <v>Patil Traders</v>
